--- a/db/A7XLK-4401-DepartmentStore.xlsx
+++ b/db/A7XLK-4401-DepartmentStore.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10808"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou2/db/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA9F0E26-71C0-4147-9E22-4FFD3F2169F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E7A8296-312B-0C43-B0D9-E95689BA6864}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2580" yWindow="4560" windowWidth="37900" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1380" yWindow="1960" windowWidth="37900" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Shopping" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="699">
   <si>
     <t>title</t>
   </si>
@@ -1361,9 +1361,6 @@
     <t>fig/XLK-411-Shopping/AiCity-913-立欣汽車檢驗有限公司.jpg</t>
   </si>
   <si>
-    <t>fig/XLK-411-Shopping/AiCity-913-原總汽車有限公司.jpg</t>
-  </si>
-  <si>
     <t>fig/XLK-411-Shopping/AiCity-913-toyota.png</t>
   </si>
   <si>
@@ -2347,6 +2344,119 @@
   </si>
   <si>
     <t>fig/XLK-411-Shopping/AiCity-913-Carrefour3.jpeg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嘉實多-嘉輝店</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新北市林口區文化二路一段68巷43號</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-2608-6119</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-411-Shopping/AiCity-913-原總汽車有限公司.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-411-Shopping/AiCity-913-嘉實多.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/Bmw%E7%9B%8A%E9%B5%AC%E6%B1%BD%E8%BB%8A-%E5%8E%9F%E5%BB%A0%E6%8A%80%E5%B8%AB-100926551551277/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BMW 益鵬汽車</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新北市林口區文化北路一段269號</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-2600-2580</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>09:00 - 19:00 週日公休</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-411-Shopping/AiCity-913-益鵬汽車.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/%E9%A0%86%E8%BC%BE%E6%B1%BD%E8%BB%8A%E5%B0%88%E6%A5%AD%E7%B6%AD%E4%BF%AE%E5%BB%A0-604048946326232/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+0913-863-873</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>順輾汽車</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃園市龜山區復興一路365號</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>外故障24小時服務</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-411-Shopping/AiCity-913-順輾汽車.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/%E5%BB%BA%E7%AB%8B%E6%B1%BD%E8%BB%8A%E4%BF%9D%E4%BF%AE%E5%BB%A0-100140188920456/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>建立汽車</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-411-Shopping/AiCity-913-建立汽車.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-328-6993</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃園市龜山區文明路101號</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-411-Shopping/AiCity-913-車得適.jpeg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>車得適</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新北市林口區文化二路10-3號</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-318-4297</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://www.tttrust.com.tw/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>09:00 - 20:00 週日公休</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2411,7 +2521,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
@@ -2422,6 +2532,10 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -2725,7 +2839,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K102"/>
+  <dimension ref="A1:K107"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="4.6640625" style="1" customWidth="1"/>
@@ -2768,13 +2882,13 @@
         <v>3</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>587</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -2782,10 +2896,10 @@
         <v>89</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>515</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>516</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>155</v>
@@ -2794,19 +2908,19 @@
         <v>198</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>608</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -2814,10 +2928,10 @@
         <v>61</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>455</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>456</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>135</v>
@@ -2826,22 +2940,22 @@
         <v>135</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J3" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>608</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -2849,10 +2963,10 @@
         <v>88</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>513</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>514</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>154</v>
@@ -2861,22 +2975,22 @@
         <v>197</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J4" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>608</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -2887,7 +3001,7 @@
         <v>225</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>228</v>
@@ -2896,22 +3010,22 @@
         <v>227</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>226</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J5" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>608</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -2919,10 +3033,10 @@
         <v>64</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>135</v>
@@ -2931,22 +3045,22 @@
         <v>186</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>241</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J6" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>608</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -2954,10 +3068,10 @@
         <v>63</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>460</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>461</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>135</v>
@@ -2966,22 +3080,22 @@
         <v>185</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J7" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="K7" s="1" t="s">
         <v>608</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2992,7 +3106,7 @@
         <v>303</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>304</v>
@@ -3001,22 +3115,22 @@
         <v>305</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>306</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J8" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>608</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="34">
@@ -3036,22 +3150,22 @@
         <v>233</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>234</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J9" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>608</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -3059,10 +3173,10 @@
         <v>62</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>458</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>459</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>135</v>
@@ -3071,22 +3185,22 @@
         <v>184</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J10" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>608</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -3094,10 +3208,10 @@
         <v>84</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>508</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>509</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>152</v>
@@ -3106,22 +3220,22 @@
         <v>195</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -3129,10 +3243,10 @@
         <v>85</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>135</v>
@@ -3141,22 +3255,22 @@
         <v>135</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -3167,7 +3281,7 @@
         <v>336</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>337</v>
@@ -3179,16 +3293,16 @@
         <v>335</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -3196,10 +3310,10 @@
         <v>82</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>503</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>504</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>150</v>
@@ -3214,16 +3328,16 @@
         <v>25</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J14" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="K14" s="1" t="s">
         <v>617</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -3231,10 +3345,10 @@
         <v>83</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>506</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>507</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>151</v>
@@ -3249,16 +3363,16 @@
         <v>26</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J15" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="K15" s="1" t="s">
         <v>617</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -3266,10 +3380,10 @@
         <v>87</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>511</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>512</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>153</v>
@@ -3284,16 +3398,16 @@
         <v>27</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -3301,10 +3415,10 @@
         <v>73</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>481</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>482</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>144</v>
@@ -3319,16 +3433,16 @@
         <v>21</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J17" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="K17" s="1" t="s">
         <v>613</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -3336,10 +3450,10 @@
         <v>74</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>483</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>484</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>145</v>
@@ -3354,16 +3468,16 @@
         <v>21</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J18" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="K18" s="1" t="s">
         <v>613</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -3371,10 +3485,10 @@
         <v>70</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>474</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>475</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>141</v>
@@ -3389,16 +3503,16 @@
         <v>19</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J19" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="K19" s="1" t="s">
         <v>613</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -3406,10 +3520,10 @@
         <v>72</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>479</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>480</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>143</v>
@@ -3424,16 +3538,16 @@
         <v>20</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J20" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="K20" s="1" t="s">
         <v>613</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -3441,10 +3555,10 @@
         <v>71</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>477</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>478</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>142</v>
@@ -3459,16 +3573,16 @@
         <v>20</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J21" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="K21" s="1" t="s">
         <v>613</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -3488,22 +3602,22 @@
         <v>273</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>274</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -3514,7 +3628,7 @@
         <v>258</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>259</v>
@@ -3523,27 +3637,27 @@
         <v>260</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>261</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>294</v>
@@ -3558,22 +3672,22 @@
         <v>297</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>298</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -3593,27 +3707,27 @@
         <v>278</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>279</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>299</v>
@@ -3628,33 +3742,33 @@
         <v>297</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>302</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>283</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>280</v>
@@ -3663,27 +3777,27 @@
         <v>281</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>282</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>284</v>
@@ -3698,22 +3812,22 @@
         <v>273</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>285</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -3733,27 +3847,27 @@
         <v>265</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>266</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>291</v>
@@ -3768,27 +3882,27 @@
         <v>273</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>292</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>286</v>
@@ -3803,22 +3917,22 @@
         <v>273</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>287</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -3829,28 +3943,28 @@
         <v>267</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>268</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>269</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -3858,10 +3972,10 @@
         <v>79</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>494</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>495</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>135</v>
@@ -3876,16 +3990,16 @@
         <v>12</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -3893,16 +4007,16 @@
         <v>80</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>497</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>498</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>135</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>363</v>
@@ -3911,16 +4025,16 @@
         <v>12</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -3928,16 +4042,16 @@
         <v>81</v>
       </c>
       <c r="B35" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>500</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>501</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>135</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>364</v>
@@ -3946,16 +4060,16 @@
         <v>12</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -3963,10 +4077,10 @@
         <v>109</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>552</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>553</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>135</v>
@@ -3981,16 +4095,16 @@
         <v>12</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I36" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="J36" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="J36" s="1" t="s">
-        <v>603</v>
-      </c>
       <c r="K36" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -3998,10 +4112,10 @@
         <v>103</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>163</v>
@@ -4016,16 +4130,16 @@
         <v>37</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I37" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="J37" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="J37" s="1" t="s">
-        <v>603</v>
-      </c>
       <c r="K37" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -4033,10 +4147,10 @@
         <v>104</v>
       </c>
       <c r="B38" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>544</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>545</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>164</v>
@@ -4051,16 +4165,16 @@
         <v>38</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I38" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="J38" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="J38" s="1" t="s">
-        <v>603</v>
-      </c>
       <c r="K38" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -4068,10 +4182,10 @@
         <v>101</v>
       </c>
       <c r="B39" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>539</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>540</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>162</v>
@@ -4086,16 +4200,16 @@
         <v>35</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I39" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="J39" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="J39" s="1" t="s">
-        <v>603</v>
-      </c>
       <c r="K39" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -4115,22 +4229,22 @@
         <v>239</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>240</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -4138,10 +4252,10 @@
         <v>50</v>
       </c>
       <c r="B41" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>433</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>434</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>125</v>
@@ -4156,16 +4270,16 @@
         <v>9</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -4173,16 +4287,16 @@
         <v>251</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="D42" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>669</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>670</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>346</v>
@@ -4191,16 +4305,16 @@
         <v>9</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -4208,10 +4322,10 @@
         <v>51</v>
       </c>
       <c r="B43" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>436</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>437</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>126</v>
@@ -4226,16 +4340,16 @@
         <v>9</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -4243,10 +4357,10 @@
         <v>52</v>
       </c>
       <c r="B44" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>438</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>439</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>127</v>
@@ -4261,16 +4375,16 @@
         <v>9</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -4278,10 +4392,10 @@
         <v>53</v>
       </c>
       <c r="B45" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>440</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>441</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>128</v>
@@ -4296,16 +4410,16 @@
         <v>9</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -4313,10 +4427,10 @@
         <v>54</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>129</v>
@@ -4325,22 +4439,22 @@
         <v>181</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -4348,34 +4462,34 @@
         <v>55</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>130</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -4383,10 +4497,10 @@
         <v>107</v>
       </c>
       <c r="B48" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>550</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>551</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>167</v>
@@ -4401,16 +4515,16 @@
         <v>12</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I48" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="J48" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="J48" s="1" t="s">
-        <v>603</v>
-      </c>
       <c r="K48" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -4421,7 +4535,7 @@
         <v>332</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>333</v>
@@ -4436,16 +4550,16 @@
         <v>335</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I49" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="J49" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="J49" s="1" t="s">
-        <v>603</v>
-      </c>
       <c r="K49" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -4453,10 +4567,10 @@
         <v>106</v>
       </c>
       <c r="B50" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>548</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>549</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>166</v>
@@ -4471,16 +4585,16 @@
         <v>39</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I50" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="J50" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="J50" s="1" t="s">
-        <v>603</v>
-      </c>
       <c r="K50" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -4488,10 +4602,10 @@
         <v>75</v>
       </c>
       <c r="B51" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>485</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>486</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>146</v>
@@ -4506,16 +4620,16 @@
         <v>22</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="I51" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="J51" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="J51" s="1" t="s">
-        <v>603</v>
-      </c>
       <c r="K51" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -4523,10 +4637,10 @@
         <v>76</v>
       </c>
       <c r="B52" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>488</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>489</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>147</v>
@@ -4541,16 +4655,16 @@
         <v>22</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="I52" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="J52" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="J52" s="1" t="s">
-        <v>603</v>
-      </c>
       <c r="K52" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -4558,10 +4672,10 @@
         <v>78</v>
       </c>
       <c r="B53" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="C53" s="1" t="s">
         <v>492</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>493</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>149</v>
@@ -4576,16 +4690,16 @@
         <v>24</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="I53" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="J53" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="J53" s="1" t="s">
-        <v>603</v>
-      </c>
       <c r="K53" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -4593,10 +4707,10 @@
         <v>77</v>
       </c>
       <c r="B54" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="C54" s="1" t="s">
         <v>490</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>491</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>148</v>
@@ -4611,16 +4725,16 @@
         <v>23</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="I54" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="J54" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="J54" s="1" t="s">
-        <v>603</v>
-      </c>
       <c r="K54" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -4628,10 +4742,10 @@
         <v>59</v>
       </c>
       <c r="B55" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C55" s="1" t="s">
         <v>451</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>452</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>134</v>
@@ -4646,16 +4760,16 @@
         <v>13</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="I55" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="J55" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="J55" s="1" t="s">
-        <v>603</v>
-      </c>
       <c r="K55" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -4663,10 +4777,10 @@
         <v>60</v>
       </c>
       <c r="B56" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>453</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>454</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>134</v>
@@ -4681,16 +4795,16 @@
         <v>13</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="I56" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="J56" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="J56" s="1" t="s">
-        <v>603</v>
-      </c>
       <c r="K56" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -4698,16 +4812,16 @@
         <v>57</v>
       </c>
       <c r="B57" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>446</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>447</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>132</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>348</v>
@@ -4716,16 +4830,16 @@
         <v>11</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="I57" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="J57" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="J57" s="1" t="s">
-        <v>603</v>
-      </c>
       <c r="K57" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -4733,10 +4847,10 @@
         <v>58</v>
       </c>
       <c r="B58" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="C58" s="1" t="s">
         <v>449</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>450</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>133</v>
@@ -4751,16 +4865,16 @@
         <v>12</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="I58" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="J58" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="J58" s="1" t="s">
-        <v>603</v>
-      </c>
       <c r="K58" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -4768,10 +4882,10 @@
         <v>56</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>131</v>
@@ -4786,16 +4900,16 @@
         <v>10</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="I59" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="J59" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="J59" s="1" t="s">
-        <v>603</v>
-      </c>
       <c r="K59" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -4803,10 +4917,10 @@
         <v>102</v>
       </c>
       <c r="B60" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="C60" s="1" t="s">
         <v>541</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>542</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>163</v>
@@ -4821,16 +4935,16 @@
         <v>36</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I60" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="J60" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="J60" s="1" t="s">
-        <v>603</v>
-      </c>
       <c r="K60" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -4838,10 +4952,10 @@
         <v>98</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>160</v>
@@ -4856,16 +4970,16 @@
         <v>33</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="I61" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="J61" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="J61" s="1" t="s">
-        <v>603</v>
-      </c>
       <c r="K61" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -4873,10 +4987,10 @@
         <v>46</v>
       </c>
       <c r="B62" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C62" s="1" t="s">
         <v>423</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>424</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>121</v>
@@ -4891,16 +5005,16 @@
         <v>5</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="I62" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="J62" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="J62" s="1" t="s">
-        <v>603</v>
-      </c>
       <c r="K62" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -4908,10 +5022,10 @@
         <v>45</v>
       </c>
       <c r="B63" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>420</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>421</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>120</v>
@@ -4926,16 +5040,16 @@
         <v>4</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="I63" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="J63" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="J63" s="1" t="s">
+      <c r="K63" s="1" t="s">
         <v>603</v>
-      </c>
-      <c r="K63" s="1" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -4943,10 +5057,10 @@
         <v>47</v>
       </c>
       <c r="B64" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>426</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>427</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>122</v>
@@ -4961,27 +5075,27 @@
         <v>6</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="I64" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="J64" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="J64" s="1" t="s">
+      <c r="K64" s="1" t="s">
         <v>603</v>
-      </c>
-      <c r="K64" s="1" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="65" spans="1:11">
       <c r="A65" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B65" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="C65" s="1" t="s">
         <v>561</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>562</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>172</v>
@@ -4996,16 +5110,16 @@
         <v>43</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="I65" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="J65" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="J65" s="1" t="s">
+      <c r="K65" s="1" t="s">
         <v>603</v>
-      </c>
-      <c r="K65" s="1" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -5013,16 +5127,16 @@
         <v>48</v>
       </c>
       <c r="B66" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>428</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>429</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>123</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>344</v>
@@ -5031,16 +5145,16 @@
         <v>7</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="I66" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="J66" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="J66" s="1" t="s">
+      <c r="K66" s="1" t="s">
         <v>603</v>
-      </c>
-      <c r="K66" s="1" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -5048,16 +5162,16 @@
         <v>49</v>
       </c>
       <c r="B67" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C67" s="1" t="s">
         <v>431</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>432</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>124</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>345</v>
@@ -5066,16 +5180,16 @@
         <v>8</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="I67" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="J67" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="J67" s="1" t="s">
+      <c r="K67" s="1" t="s">
         <v>603</v>
-      </c>
-      <c r="K67" s="1" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -5083,10 +5197,10 @@
         <v>114</v>
       </c>
       <c r="B68" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="C68" s="1" t="s">
         <v>559</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>560</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>171</v>
@@ -5101,16 +5215,16 @@
         <v>42</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="I68" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="J68" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="J68" s="1" t="s">
+      <c r="K68" s="1" t="s">
         <v>603</v>
-      </c>
-      <c r="K68" s="1" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -5118,10 +5232,10 @@
         <v>113</v>
       </c>
       <c r="B69" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="C69" s="1" t="s">
         <v>557</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>558</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>170</v>
@@ -5136,16 +5250,16 @@
         <v>41</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="I69" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="J69" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="J69" s="1" t="s">
+      <c r="K69" s="1" t="s">
         <v>603</v>
-      </c>
-      <c r="K69" s="1" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -5153,10 +5267,10 @@
         <v>69</v>
       </c>
       <c r="B70" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="C70" s="1" t="s">
         <v>472</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>473</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>140</v>
@@ -5171,16 +5285,16 @@
         <v>18</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -5188,10 +5302,10 @@
         <v>68</v>
       </c>
       <c r="B71" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="C71" s="1" t="s">
         <v>470</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>471</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>139</v>
@@ -5206,16 +5320,16 @@
         <v>17</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -5223,10 +5337,10 @@
         <v>65</v>
       </c>
       <c r="B72" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="C72" s="1" t="s">
         <v>463</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>464</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>136</v>
@@ -5241,16 +5355,16 @@
         <v>14</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J72" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="K72" s="1" t="s">
         <v>610</v>
-      </c>
-      <c r="K72" s="1" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -5258,10 +5372,10 @@
         <v>66</v>
       </c>
       <c r="B73" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C73" s="1" t="s">
         <v>466</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>467</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>137</v>
@@ -5276,16 +5390,16 @@
         <v>15</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J73" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="K73" s="1" t="s">
         <v>610</v>
-      </c>
-      <c r="K73" s="1" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -5293,10 +5407,10 @@
         <v>67</v>
       </c>
       <c r="B74" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="C74" s="1" t="s">
         <v>468</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>469</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>138</v>
@@ -5311,16 +5425,16 @@
         <v>16</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J74" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="K74" s="1" t="s">
         <v>610</v>
-      </c>
-      <c r="K74" s="1" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -5328,10 +5442,10 @@
         <v>99</v>
       </c>
       <c r="B75" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="C75" s="1" t="s">
         <v>533</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>534</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>135</v>
@@ -5346,16 +5460,16 @@
         <v>12</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I75" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="J75" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="J75" s="1" t="s">
+      <c r="K75" s="1" t="s">
         <v>626</v>
-      </c>
-      <c r="K75" s="1" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -5366,7 +5480,7 @@
         <v>328</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>329</v>
@@ -5381,16 +5495,16 @@
         <v>331</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I76" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="J76" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="J76" s="1" t="s">
-        <v>626</v>
-      </c>
       <c r="K76" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -5398,10 +5512,10 @@
         <v>105</v>
       </c>
       <c r="B77" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="C77" s="1" t="s">
         <v>546</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>547</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>165</v>
@@ -5416,16 +5530,16 @@
         <v>12</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I77" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="J77" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="J77" s="1" t="s">
+      <c r="K77" s="1" t="s">
         <v>632</v>
-      </c>
-      <c r="K77" s="1" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -5433,10 +5547,10 @@
         <v>242</v>
       </c>
       <c r="B78" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="C78" s="1" t="s">
         <v>577</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>578</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>338</v>
@@ -5445,22 +5559,22 @@
         <v>339</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G78" s="5" t="s">
         <v>340</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="I78" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="J78" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="J78" s="1" t="s">
-        <v>632</v>
-      </c>
       <c r="K78" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -5471,7 +5585,7 @@
         <v>217</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D79" s="6" t="s">
         <v>219</v>
@@ -5480,33 +5594,33 @@
         <v>221</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="G79" s="4" t="s">
         <v>218</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="I79" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="J79" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="J79" s="1" t="s">
-        <v>632</v>
-      </c>
       <c r="K79" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="80" spans="1:11">
       <c r="A80" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>215</v>
@@ -5521,16 +5635,16 @@
         <v>214</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="I80" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="J80" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="J80" s="1" t="s">
-        <v>632</v>
-      </c>
       <c r="K80" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -5541,759 +5655,932 @@
         <v>224</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D81" s="6" t="s">
         <v>220</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>393</v>
+        <v>674</v>
       </c>
       <c r="G81" s="4" t="s">
         <v>213</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="I81" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="J81" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="J81" s="1" t="s">
-        <v>632</v>
-      </c>
       <c r="K81" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="82" spans="1:11">
       <c r="A82" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>568</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="E82" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>672</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>673</v>
+      </c>
+      <c r="E82" s="6"/>
+      <c r="F82" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H82" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="F82" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="G82" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="H82" s="1" t="s">
-        <v>570</v>
-      </c>
       <c r="I82" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="J82" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="J82" s="1" t="s">
-        <v>632</v>
-      </c>
       <c r="K82" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="83" spans="1:11">
       <c r="A83" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>391</v>
+        <v>242</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>677</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>678</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>679</v>
+      </c>
+      <c r="E83" s="6" t="s">
+        <v>680</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>681</v>
+      </c>
+      <c r="G83" s="8" t="s">
+        <v>676</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="I83" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="J83" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="J83" s="1" t="s">
-        <v>632</v>
-      </c>
       <c r="K83" s="1" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" ht="34">
       <c r="A84" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="G84" s="2" t="s">
-        <v>324</v>
+        <v>247</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>684</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>685</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>683</v>
+      </c>
+      <c r="E84" s="6" t="s">
+        <v>686</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>687</v>
+      </c>
+      <c r="G84" s="8" t="s">
+        <v>682</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>307</v>
+        <v>569</v>
       </c>
       <c r="I84" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="J84" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="J84" s="1" t="s">
-        <v>640</v>
-      </c>
       <c r="K84" s="1" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
     </row>
     <row r="85" spans="1:11">
       <c r="A85" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="F85" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="G85" s="2" t="s">
-        <v>312</v>
+        <v>248</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>689</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>692</v>
+      </c>
+      <c r="D85" s="6" t="s">
+        <v>691</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>680</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="G85" s="8" t="s">
+        <v>688</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>307</v>
+        <v>569</v>
       </c>
       <c r="I85" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="J85" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="J85" s="1" t="s">
-        <v>640</v>
-      </c>
       <c r="K85" s="1" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
     </row>
     <row r="86" spans="1:11">
       <c r="A86" s="1" t="s">
-        <v>599</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="G86" s="2" t="s">
-        <v>317</v>
+        <v>249</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>696</v>
+      </c>
+      <c r="E86" s="6" t="s">
+        <v>698</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>693</v>
+      </c>
+      <c r="G86" s="8" t="s">
+        <v>697</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>307</v>
+        <v>569</v>
       </c>
       <c r="I86" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="J86" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="J86" s="1" t="s">
-        <v>640</v>
-      </c>
       <c r="K86" s="1" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" ht="34">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11">
       <c r="A87" s="1" t="s">
-        <v>600</v>
+        <v>222</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>320</v>
+        <v>566</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>567</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>321</v>
+        <v>210</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>322</v>
+        <v>568</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="G87" s="2" t="s">
-        <v>318</v>
+        <v>390</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>211</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>307</v>
+        <v>569</v>
       </c>
       <c r="I87" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="J87" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="J87" s="1" t="s">
-        <v>640</v>
-      </c>
       <c r="K87" s="1" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
     </row>
     <row r="88" spans="1:11">
       <c r="A88" s="1" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>116</v>
+        <v>570</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="G88" s="2" t="s">
-        <v>208</v>
+        <v>391</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="I88" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="J88" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="J88" s="1" t="s">
+      <c r="K88" s="1" t="s">
         <v>637</v>
-      </c>
-      <c r="K88" s="1" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="89" spans="1:11">
       <c r="A89" s="1" t="s">
-        <v>590</v>
+        <v>600</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>115</v>
+        <v>323</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>429</v>
+        <v>327</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>326</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>563</v>
+        <v>325</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="G89" s="1" t="s">
-        <v>117</v>
+        <v>413</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>324</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>564</v>
+        <v>307</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="J89" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>564</v>
+        <v>640</v>
       </c>
     </row>
     <row r="90" spans="1:11">
       <c r="A90" s="1" t="s">
-        <v>90</v>
+        <v>597</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>654</v>
+        <v>308</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>517</v>
+        <v>310</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>135</v>
+        <v>309</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>135</v>
+        <v>311</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>656</v>
-      </c>
-      <c r="G90" s="1" t="s">
-        <v>12</v>
+        <v>410</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>312</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>518</v>
+        <v>307</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>616</v>
+        <v>630</v>
       </c>
       <c r="J90" s="1" t="s">
-        <v>621</v>
+        <v>639</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>622</v>
+        <v>640</v>
       </c>
     </row>
     <row r="91" spans="1:11">
       <c r="A91" s="1" t="s">
-        <v>91</v>
+        <v>598</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>519</v>
+        <v>313</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>520</v>
+        <v>314</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>135</v>
+        <v>315</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>199</v>
+        <v>316</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="G91" s="1" t="s">
-        <v>12</v>
+        <v>411</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>317</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>518</v>
+        <v>307</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>616</v>
+        <v>630</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>621</v>
+        <v>639</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" ht="34">
       <c r="A92" s="1" t="s">
-        <v>96</v>
+        <v>599</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>529</v>
+        <v>319</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>320</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>135</v>
+        <v>321</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>201</v>
+        <v>322</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="G92" s="1" t="s">
-        <v>524</v>
+        <v>412</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>318</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>518</v>
+        <v>307</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>616</v>
+        <v>630</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>621</v>
+        <v>639</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>622</v>
+        <v>640</v>
       </c>
     </row>
     <row r="93" spans="1:11">
       <c r="A93" s="1" t="s">
-        <v>92</v>
+        <v>212</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>521</v>
+        <v>116</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>522</v>
+        <v>564</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>156</v>
+        <v>209</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>200</v>
+        <v>565</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>655</v>
-      </c>
-      <c r="G93" s="1" t="s">
-        <v>29</v>
+        <v>389</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>208</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>518</v>
+        <v>563</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>616</v>
+        <v>630</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>621</v>
+        <v>636</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>622</v>
+        <v>563</v>
       </c>
     </row>
     <row r="94" spans="1:11">
       <c r="A94" s="1" t="s">
-        <v>95</v>
+        <v>589</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>158</v>
+        <v>428</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>177</v>
+        <v>562</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>369</v>
+        <v>388</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>31</v>
+        <v>117</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>518</v>
+        <v>563</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>616</v>
+        <v>630</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>621</v>
+        <v>636</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>622</v>
+        <v>563</v>
       </c>
     </row>
     <row r="95" spans="1:11">
       <c r="A95" s="1" t="s">
-        <v>252</v>
+        <v>90</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>243</v>
+        <v>653</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>582</v>
+        <v>516</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>246</v>
+        <v>135</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>244</v>
+        <v>135</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="G95" s="2" t="s">
-        <v>245</v>
+        <v>655</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="J95" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="K95" s="1" t="s">
         <v>621</v>
-      </c>
-      <c r="K95" s="1" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="96" spans="1:11">
       <c r="A96" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>135</v>
+        <v>199</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>524</v>
+        <v>12</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="J96" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="K96" s="1" t="s">
         <v>621</v>
-      </c>
-      <c r="K96" s="1" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="97" spans="1:11">
       <c r="A97" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>657</v>
+        <v>527</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>135</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>135</v>
+        <v>201</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="J97" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="K97" s="1" t="s">
         <v>621</v>
-      </c>
-      <c r="K97" s="1" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="98" spans="1:11">
       <c r="A98" s="1" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>536</v>
+        <v>520</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>537</v>
+        <v>521</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>538</v>
+        <v>200</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>373</v>
+        <v>654</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>535</v>
+        <v>517</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="J98" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="K98" s="1" t="s">
         <v>621</v>
-      </c>
-      <c r="K98" s="1" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="99" spans="1:11">
       <c r="A99" s="1" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>554</v>
+        <v>30</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>555</v>
+        <v>526</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>206</v>
+        <v>177</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>663</v>
+        <v>369</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>535</v>
+        <v>517</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="J99" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="K99" s="1" t="s">
         <v>621</v>
-      </c>
-      <c r="K99" s="1" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="100" spans="1:11">
       <c r="A100" s="1" t="s">
-        <v>111</v>
+        <v>252</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>556</v>
+        <v>243</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>417</v>
+        <v>581</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>169</v>
+        <v>246</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>135</v>
+        <v>244</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="G100" s="1" t="s">
-        <v>524</v>
+        <v>398</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>535</v>
+        <v>517</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="J100" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="K100" s="1" t="s">
         <v>621</v>
-      </c>
-      <c r="K100" s="1" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="101" spans="1:11">
       <c r="A101" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>198</v>
+        <v>135</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>370</v>
+        <v>647</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>32</v>
+        <v>523</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>425</v>
+        <v>517</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="J101" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="K101" s="1" t="s">
         <v>621</v>
-      </c>
-      <c r="K101" s="1" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="102" spans="1:11">
       <c r="A102" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="J102" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="K102" s="1" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11">
+      <c r="A103" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="I103" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="J103" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11">
+      <c r="A104" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="F104" s="1" t="s">
         <v>662</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="G104" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="I104" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="J104" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="K104" s="1" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11">
+      <c r="A105" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="I105" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="J105" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="K105" s="1" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11">
+      <c r="A106" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="J106" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="K106" s="1" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11">
+      <c r="A107" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="C107" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="C102" s="1" t="s">
+      <c r="D107" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="D102" s="1" t="s">
-        <v>668</v>
-      </c>
-      <c r="F102" s="1" t="s">
+      <c r="F107" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="G107" s="7" t="s">
         <v>664</v>
       </c>
-      <c r="G102" s="7" t="s">
-        <v>665</v>
-      </c>
-      <c r="H102" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="I102" s="1" t="s">
-        <v>602</v>
-      </c>
-      <c r="J102" s="1" t="s">
-        <v>608</v>
-      </c>
-      <c r="K102" s="1" t="s">
-        <v>606</v>
+      <c r="H107" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="J107" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="K107" s="1" t="s">
+        <v>605</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K101">
-    <sortCondition ref="J2:J101"/>
-    <sortCondition ref="K2:K101"/>
-    <sortCondition ref="B2:B101"/>
-    <sortCondition ref="C2:C101"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K106">
+    <sortCondition ref="J2:J106"/>
+    <sortCondition ref="K2:K106"/>
+    <sortCondition ref="B2:B106"/>
+    <sortCondition ref="C2:C106"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="2">
@@ -6305,13 +6592,13 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="G88" r:id="rId1" xr:uid="{A39B8C40-8D45-EB49-A4FC-B32617C3743A}"/>
+    <hyperlink ref="G93" r:id="rId1" xr:uid="{A39B8C40-8D45-EB49-A4FC-B32617C3743A}"/>
     <hyperlink ref="G80" r:id="rId2" xr:uid="{B5DCC527-C34A-A84A-863F-C7614151FE6F}"/>
     <hyperlink ref="G5" r:id="rId3" xr:uid="{9F3F15C4-C0FD-AE4F-A261-C94D2C5C5CDD}"/>
     <hyperlink ref="G9" r:id="rId4" xr:uid="{57110EDF-FEA5-304D-BC8D-B61106C21880}"/>
     <hyperlink ref="G40" r:id="rId5" location="sale_active" xr:uid="{730FA5EB-C91B-144D-A783-4D831224B6A9}"/>
     <hyperlink ref="G6" r:id="rId6" xr:uid="{1F8F556A-7472-764F-A198-D7F42EFCC387}"/>
-    <hyperlink ref="G95" r:id="rId7" xr:uid="{D0E463C4-46AF-0146-87CD-46876FB5CA0D}"/>
+    <hyperlink ref="G100" r:id="rId7" xr:uid="{D0E463C4-46AF-0146-87CD-46876FB5CA0D}"/>
     <hyperlink ref="G23" r:id="rId8" xr:uid="{DF8FD8B1-A50B-9E4E-9410-150C09502DAB}"/>
     <hyperlink ref="G29" r:id="rId9" xr:uid="{FF011359-39BB-A040-AED2-D2D90A217A10}"/>
     <hyperlink ref="G32" r:id="rId10" xr:uid="{52BA0BCD-A138-3A42-93E9-9408D0B6CD41}"/>
@@ -6324,13 +6611,17 @@
     <hyperlink ref="G24" r:id="rId17" xr:uid="{645725E7-FD7F-7841-BD5D-4F55FBCDAB8D}"/>
     <hyperlink ref="G26" r:id="rId18" xr:uid="{D8E83196-8EED-474F-A39D-4B8A53066F90}"/>
     <hyperlink ref="G8" r:id="rId19" xr:uid="{D8074921-21AA-094E-B1E8-1A2B5D8215AB}"/>
-    <hyperlink ref="G85" r:id="rId20" xr:uid="{67DB94DD-4F2A-2B47-90EF-FED3ED8F2017}"/>
-    <hyperlink ref="G86" r:id="rId21" xr:uid="{F6F3D17A-11C3-804A-89D9-3C231334A22A}"/>
-    <hyperlink ref="G87" r:id="rId22" xr:uid="{D5F7639A-8FC0-444F-B0B1-291456215366}"/>
-    <hyperlink ref="G84" r:id="rId23" xr:uid="{40CF7C3F-7CEF-0245-8E88-7892E420529A}"/>
+    <hyperlink ref="G90" r:id="rId20" xr:uid="{67DB94DD-4F2A-2B47-90EF-FED3ED8F2017}"/>
+    <hyperlink ref="G91" r:id="rId21" xr:uid="{F6F3D17A-11C3-804A-89D9-3C231334A22A}"/>
+    <hyperlink ref="G92" r:id="rId22" xr:uid="{D5F7639A-8FC0-444F-B0B1-291456215366}"/>
+    <hyperlink ref="G89" r:id="rId23" xr:uid="{40CF7C3F-7CEF-0245-8E88-7892E420529A}"/>
     <hyperlink ref="G76" r:id="rId24" xr:uid="{B2FAD3F1-82CD-564A-89EB-8DE0938B2D53}"/>
     <hyperlink ref="G78" r:id="rId25" xr:uid="{1FE5A63E-4D12-4C4C-A566-E71804C9006E}"/>
-    <hyperlink ref="G102" r:id="rId26" xr:uid="{237E6794-0DAA-2340-869C-73B873A6D324}"/>
+    <hyperlink ref="G107" r:id="rId26" xr:uid="{237E6794-0DAA-2340-869C-73B873A6D324}"/>
+    <hyperlink ref="G83" r:id="rId27" xr:uid="{67CF96A7-8792-ED4D-852A-2AD878FBA0A7}"/>
+    <hyperlink ref="G84" r:id="rId28" xr:uid="{DDD41264-2363-7B4D-BE34-303C44BC64C2}"/>
+    <hyperlink ref="G85" r:id="rId29" xr:uid="{974EC1EA-84B1-4147-9488-B123C8DAB06A}"/>
+    <hyperlink ref="G86" r:id="rId30" xr:uid="{76485F94-E942-EF4C-B260-4F0E2DC7AE4C}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait"/>

--- a/db/A7XLK-4401-DepartmentStore.xlsx
+++ b/db/A7XLK-4401-DepartmentStore.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10808"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10912"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E7A8296-312B-0C43-B0D9-E95689BA6864}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAEA71ED-598B-2B4D-B873-43FD91585F8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="1960" windowWidth="37900" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6080" yWindow="1140" windowWidth="37900" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Shopping" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="699">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1179" uniqueCount="706">
   <si>
     <t>title</t>
   </si>
@@ -1262,9 +1262,6 @@
     <t>fig/XLK-411-Shopping/AiCity-913-711-2.png</t>
   </si>
   <si>
-    <t>fig/XLK-411-Shopping/AiCity-913-ok-2.png</t>
-  </si>
-  <si>
     <t>fig/XLK-411-Shopping/AiCity-913-FamilyMart-2.jpg</t>
   </si>
   <si>
@@ -2457,6 +2454,38 @@
   </si>
   <si>
     <t>09:00 - 20:00 週日公休</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>034</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蝦皮店到店 林口民族門市</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新北市林口區民族路28號</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-6636-6559</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:30 - 22:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://shopee.tw/m/spx?smtt=9&amp;deep_and_deferred=33</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-411-Shopping/AiCity-913-ok-2.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-411-Shopping/AiCity-913-蝦皮店到店.png</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2839,7 +2868,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K107"/>
+  <dimension ref="A1:K108"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="4.6640625" style="1" customWidth="1"/>
@@ -2882,13 +2911,13 @@
         <v>3</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>586</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -2896,10 +2925,10 @@
         <v>89</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>514</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>515</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>155</v>
@@ -2908,19 +2937,19 @@
         <v>198</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>607</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -2928,10 +2957,10 @@
         <v>61</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>454</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>455</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>135</v>
@@ -2940,22 +2969,22 @@
         <v>135</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J3" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>607</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -2963,10 +2992,10 @@
         <v>88</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>512</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>513</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>154</v>
@@ -2975,22 +3004,22 @@
         <v>197</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J4" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>607</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -3001,7 +3030,7 @@
         <v>225</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>228</v>
@@ -3010,22 +3039,22 @@
         <v>227</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>226</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J5" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>607</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -3033,10 +3062,10 @@
         <v>64</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>135</v>
@@ -3045,22 +3074,22 @@
         <v>186</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>241</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J6" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>607</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -3068,10 +3097,10 @@
         <v>63</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>459</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>460</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>135</v>
@@ -3080,22 +3109,22 @@
         <v>185</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J7" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="K7" s="1" t="s">
         <v>607</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -3106,7 +3135,7 @@
         <v>303</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>304</v>
@@ -3115,22 +3144,22 @@
         <v>305</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>306</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J8" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>607</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="34">
@@ -3150,22 +3179,22 @@
         <v>233</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>234</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J9" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>607</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -3173,10 +3202,10 @@
         <v>62</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>457</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>458</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>135</v>
@@ -3185,22 +3214,22 @@
         <v>184</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J10" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>607</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -3208,10 +3237,10 @@
         <v>84</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>507</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>508</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>152</v>
@@ -3220,22 +3249,22 @@
         <v>195</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -3243,10 +3272,10 @@
         <v>85</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>135</v>
@@ -3255,22 +3284,22 @@
         <v>135</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -3281,28 +3310,28 @@
         <v>336</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>337</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>335</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -3310,10 +3339,10 @@
         <v>82</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>502</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>503</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>150</v>
@@ -3322,22 +3351,22 @@
         <v>189</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>25</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J14" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="K14" s="1" t="s">
         <v>616</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -3345,10 +3374,10 @@
         <v>83</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>505</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>506</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>151</v>
@@ -3357,22 +3386,22 @@
         <v>194</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J15" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="K15" s="1" t="s">
         <v>616</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -3380,10 +3409,10 @@
         <v>87</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>510</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>511</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>153</v>
@@ -3392,22 +3421,22 @@
         <v>196</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -3415,10 +3444,10 @@
         <v>73</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>480</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>481</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>144</v>
@@ -3433,16 +3462,16 @@
         <v>21</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J17" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="K17" s="1" t="s">
         <v>612</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -3450,10 +3479,10 @@
         <v>74</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>482</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>483</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>145</v>
@@ -3468,16 +3497,16 @@
         <v>21</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J18" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="K18" s="1" t="s">
         <v>612</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -3485,10 +3514,10 @@
         <v>70</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>473</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>474</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>141</v>
@@ -3503,16 +3532,16 @@
         <v>19</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J19" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="K19" s="1" t="s">
         <v>612</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -3520,10 +3549,10 @@
         <v>72</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>478</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>479</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>143</v>
@@ -3538,16 +3567,16 @@
         <v>20</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J20" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="K20" s="1" t="s">
         <v>612</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -3555,10 +3584,10 @@
         <v>71</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>476</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>477</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>142</v>
@@ -3573,16 +3602,16 @@
         <v>20</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J21" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="K21" s="1" t="s">
         <v>612</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -3602,22 +3631,22 @@
         <v>273</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>274</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -3628,7 +3657,7 @@
         <v>258</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>259</v>
@@ -3637,27 +3666,27 @@
         <v>260</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>261</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>294</v>
@@ -3672,22 +3701,22 @@
         <v>297</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>298</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -3707,27 +3736,27 @@
         <v>278</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>279</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>299</v>
@@ -3742,33 +3771,33 @@
         <v>297</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>302</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>283</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>280</v>
@@ -3777,27 +3806,27 @@
         <v>281</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>282</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>284</v>
@@ -3812,22 +3841,22 @@
         <v>273</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>285</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -3847,27 +3876,27 @@
         <v>265</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>266</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>291</v>
@@ -3882,27 +3911,27 @@
         <v>273</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>292</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>286</v>
@@ -3917,22 +3946,22 @@
         <v>273</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>287</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -3943,28 +3972,28 @@
         <v>267</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>268</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>269</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -3972,10 +4001,10 @@
         <v>79</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>493</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>494</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>135</v>
@@ -3984,22 +4013,22 @@
         <v>193</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -4007,34 +4036,34 @@
         <v>80</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>496</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>497</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>135</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -4042,34 +4071,34 @@
         <v>81</v>
       </c>
       <c r="B35" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>499</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>500</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>135</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -4077,10 +4106,10 @@
         <v>109</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>551</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>552</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>135</v>
@@ -4089,22 +4118,22 @@
         <v>135</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I36" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="J36" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="J36" s="1" t="s">
-        <v>602</v>
-      </c>
       <c r="K36" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -4112,10 +4141,10 @@
         <v>103</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>163</v>
@@ -4124,22 +4153,22 @@
         <v>203</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>37</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I37" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="J37" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="J37" s="1" t="s">
-        <v>602</v>
-      </c>
       <c r="K37" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -4147,10 +4176,10 @@
         <v>104</v>
       </c>
       <c r="B38" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>543</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>544</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>164</v>
@@ -4159,22 +4188,22 @@
         <v>135</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>38</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I38" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="J38" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="J38" s="1" t="s">
-        <v>602</v>
-      </c>
       <c r="K38" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -4182,10 +4211,10 @@
         <v>101</v>
       </c>
       <c r="B39" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>538</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>539</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>162</v>
@@ -4194,22 +4223,22 @@
         <v>202</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>35</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I39" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="J39" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="J39" s="1" t="s">
-        <v>602</v>
-      </c>
       <c r="K39" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -4229,22 +4258,22 @@
         <v>239</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>240</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -4252,10 +4281,10 @@
         <v>50</v>
       </c>
       <c r="B41" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>432</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>433</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>125</v>
@@ -4270,16 +4299,16 @@
         <v>9</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -4287,16 +4316,16 @@
         <v>251</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D42" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>668</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>669</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>346</v>
@@ -4305,16 +4334,16 @@
         <v>9</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -4322,10 +4351,10 @@
         <v>51</v>
       </c>
       <c r="B43" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>435</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>436</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>126</v>
@@ -4340,16 +4369,16 @@
         <v>9</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -4357,10 +4386,10 @@
         <v>52</v>
       </c>
       <c r="B44" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>437</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>438</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>127</v>
@@ -4375,16 +4404,16 @@
         <v>9</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -4392,10 +4421,10 @@
         <v>53</v>
       </c>
       <c r="B45" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>439</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>440</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>128</v>
@@ -4410,16 +4439,16 @@
         <v>9</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -4427,10 +4456,10 @@
         <v>54</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>129</v>
@@ -4439,22 +4468,22 @@
         <v>181</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -4462,34 +4491,34 @@
         <v>55</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>130</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -4497,10 +4526,10 @@
         <v>107</v>
       </c>
       <c r="B48" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>549</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>550</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>167</v>
@@ -4509,22 +4538,22 @@
         <v>205</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I48" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="J48" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="J48" s="1" t="s">
-        <v>602</v>
-      </c>
       <c r="K48" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -4535,7 +4564,7 @@
         <v>332</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>333</v>
@@ -4544,22 +4573,22 @@
         <v>334</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>335</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I49" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="J49" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="J49" s="1" t="s">
-        <v>602</v>
-      </c>
       <c r="K49" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -4567,10 +4596,10 @@
         <v>106</v>
       </c>
       <c r="B50" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>547</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>548</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>166</v>
@@ -4579,22 +4608,22 @@
         <v>204</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>39</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I50" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="J50" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="J50" s="1" t="s">
-        <v>602</v>
-      </c>
       <c r="K50" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -4602,10 +4631,10 @@
         <v>75</v>
       </c>
       <c r="B51" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>484</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>485</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>146</v>
@@ -4620,16 +4649,16 @@
         <v>22</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="I51" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="J51" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="J51" s="1" t="s">
-        <v>602</v>
-      </c>
       <c r="K51" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -4637,10 +4666,10 @@
         <v>76</v>
       </c>
       <c r="B52" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>487</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>488</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>147</v>
@@ -4655,16 +4684,16 @@
         <v>22</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="I52" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="J52" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="J52" s="1" t="s">
-        <v>602</v>
-      </c>
       <c r="K52" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -4672,10 +4701,10 @@
         <v>78</v>
       </c>
       <c r="B53" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="C53" s="1" t="s">
         <v>491</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>492</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>149</v>
@@ -4684,22 +4713,22 @@
         <v>192</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="I53" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="J53" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="J53" s="1" t="s">
-        <v>602</v>
-      </c>
       <c r="K53" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -4707,10 +4736,10 @@
         <v>77</v>
       </c>
       <c r="B54" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="C54" s="1" t="s">
         <v>489</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>490</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>148</v>
@@ -4719,68 +4748,68 @@
         <v>192</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>360</v>
+        <v>704</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>23</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="I54" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="J54" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="J54" s="1" t="s">
-        <v>602</v>
-      </c>
       <c r="K54" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="55" spans="1:11">
       <c r="A55" s="1" t="s">
-        <v>59</v>
+        <v>698</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>450</v>
+        <v>699</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>451</v>
+        <v>700</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>134</v>
+        <v>701</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>183</v>
+        <v>702</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>13</v>
+        <v>705</v>
+      </c>
+      <c r="G55" s="7" t="s">
+        <v>703</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>434</v>
+        <v>485</v>
       </c>
       <c r="I55" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="J55" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="J55" s="1" t="s">
-        <v>602</v>
-      </c>
       <c r="K55" s="1" t="s">
-        <v>606</v>
+        <v>485</v>
       </c>
     </row>
     <row r="56" spans="1:11">
       <c r="A56" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>134</v>
@@ -4795,258 +4824,258 @@
         <v>13</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="I56" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="J56" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="J56" s="1" t="s">
-        <v>602</v>
-      </c>
       <c r="K56" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="57" spans="1:11">
       <c r="A57" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>447</v>
+        <v>183</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="I57" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="J57" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="J57" s="1" t="s">
-        <v>602</v>
-      </c>
       <c r="K57" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="58" spans="1:11">
       <c r="A58" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>179</v>
+        <v>446</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="I58" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="J58" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="J58" s="1" t="s">
-        <v>602</v>
-      </c>
       <c r="K58" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="59" spans="1:11">
       <c r="A59" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>658</v>
+        <v>447</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="I59" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="J59" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="J59" s="1" t="s">
-        <v>602</v>
-      </c>
       <c r="K59" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="60" spans="1:11">
       <c r="A60" s="1" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>540</v>
+        <v>657</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>541</v>
+        <v>443</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>163</v>
+        <v>131</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>375</v>
+        <v>347</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>534</v>
+        <v>433</v>
       </c>
       <c r="I60" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="J60" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="J60" s="1" t="s">
-        <v>602</v>
-      </c>
       <c r="K60" s="1" t="s">
-        <v>628</v>
+        <v>605</v>
       </c>
     </row>
     <row r="61" spans="1:11">
       <c r="A61" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>433</v>
+        <v>540</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>424</v>
+        <v>533</v>
       </c>
       <c r="I61" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="J61" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="J61" s="1" t="s">
-        <v>602</v>
-      </c>
       <c r="K61" s="1" t="s">
-        <v>604</v>
+        <v>627</v>
       </c>
     </row>
     <row r="62" spans="1:11">
       <c r="A62" s="1" t="s">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>422</v>
+        <v>530</v>
       </c>
       <c r="C62" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H62" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="D62" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H62" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="I62" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="J62" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="J62" s="1" t="s">
-        <v>602</v>
-      </c>
       <c r="K62" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="63" spans="1:11">
       <c r="A63" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="I63" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="J63" s="1" t="s">
         <v>601</v>
-      </c>
-      <c r="J63" s="1" t="s">
-        <v>602</v>
       </c>
       <c r="K63" s="1" t="s">
         <v>603</v>
@@ -5054,314 +5083,314 @@
     </row>
     <row r="64" spans="1:11">
       <c r="A64" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I64" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="J64" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="J64" s="1" t="s">
+      <c r="K64" s="1" t="s">
         <v>602</v>
-      </c>
-      <c r="K64" s="1" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="65" spans="1:11">
       <c r="A65" s="1" t="s">
-        <v>588</v>
+        <v>47</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>560</v>
+        <v>424</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>561</v>
+        <v>425</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>172</v>
+        <v>122</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>387</v>
+        <v>343</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I65" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="J65" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="J65" s="1" t="s">
+      <c r="K65" s="1" t="s">
         <v>602</v>
-      </c>
-      <c r="K65" s="1" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="66" spans="1:11">
       <c r="A66" s="1" t="s">
-        <v>48</v>
+        <v>587</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>427</v>
+        <v>559</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>428</v>
+        <v>560</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>123</v>
+        <v>172</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>429</v>
+        <v>174</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>344</v>
+        <v>386</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I66" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="J66" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="J66" s="1" t="s">
+      <c r="K66" s="1" t="s">
         <v>602</v>
-      </c>
-      <c r="K66" s="1" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="67" spans="1:11">
       <c r="A67" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I67" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="J67" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="J67" s="1" t="s">
+      <c r="K67" s="1" t="s">
         <v>602</v>
-      </c>
-      <c r="K67" s="1" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="68" spans="1:11">
       <c r="A68" s="1" t="s">
-        <v>114</v>
+        <v>49</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>558</v>
+        <v>429</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>559</v>
+        <v>430</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>171</v>
+        <v>124</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>207</v>
+        <v>428</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>386</v>
+        <v>345</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I68" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="J68" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="J68" s="1" t="s">
+      <c r="K68" s="1" t="s">
         <v>602</v>
-      </c>
-      <c r="K68" s="1" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="69" spans="1:11">
       <c r="A69" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>174</v>
+        <v>207</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>385</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I69" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="J69" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="J69" s="1" t="s">
+      <c r="K69" s="1" t="s">
         <v>602</v>
-      </c>
-      <c r="K69" s="1" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="70" spans="1:11">
       <c r="A70" s="1" t="s">
-        <v>69</v>
+        <v>113</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>471</v>
+        <v>555</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>472</v>
+        <v>556</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>355</v>
+        <v>384</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>464</v>
+        <v>420</v>
       </c>
       <c r="I70" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="J70" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="J70" s="1" t="s">
-        <v>609</v>
-      </c>
       <c r="K70" s="1" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
     </row>
     <row r="71" spans="1:11">
       <c r="A71" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="72" spans="1:11">
       <c r="A72" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="C72" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H72" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="D72" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H72" s="1" t="s">
-        <v>464</v>
-      </c>
       <c r="I72" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="K72" s="1" t="s">
         <v>610</v>
@@ -5369,1218 +5398,1253 @@
     </row>
     <row r="73" spans="1:11">
       <c r="A73" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J73" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="K73" s="1" t="s">
         <v>609</v>
-      </c>
-      <c r="K73" s="1" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="74" spans="1:11">
       <c r="A74" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J74" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="K74" s="1" t="s">
         <v>609</v>
-      </c>
-      <c r="K74" s="1" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="75" spans="1:11">
       <c r="A75" s="1" t="s">
-        <v>99</v>
+        <v>67</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>532</v>
+        <v>466</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>533</v>
+        <v>467</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>135</v>
+        <v>189</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>372</v>
+        <v>353</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>534</v>
+        <v>463</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>624</v>
+        <v>600</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>625</v>
+        <v>608</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>626</v>
+        <v>609</v>
       </c>
     </row>
     <row r="76" spans="1:11">
       <c r="A76" s="1" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>328</v>
+        <v>531</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>417</v>
+        <v>532</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>329</v>
+        <v>135</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>330</v>
+        <v>135</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>331</v>
+        <v>371</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I76" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="J76" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="J76" s="1" t="s">
+      <c r="K76" s="1" t="s">
         <v>625</v>
-      </c>
-      <c r="K76" s="1" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="77" spans="1:11">
       <c r="A77" s="1" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>545</v>
+        <v>328</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>546</v>
+        <v>416</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>165</v>
+        <v>329</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>192</v>
+        <v>330</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>12</v>
+        <v>383</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>630</v>
+        <v>623</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>631</v>
+        <v>624</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="78" spans="1:11">
       <c r="A78" s="1" t="s">
-        <v>242</v>
+        <v>105</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>576</v>
+        <v>544</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>577</v>
+        <v>545</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="E78" s="6" t="s">
-        <v>339</v>
+        <v>165</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>192</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="G78" s="5" t="s">
-        <v>340</v>
+        <v>377</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>569</v>
+        <v>533</v>
       </c>
       <c r="I78" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="J78" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="J78" s="1" t="s">
+      <c r="K78" s="1" t="s">
         <v>631</v>
-      </c>
-      <c r="K78" s="1" t="s">
-        <v>637</v>
       </c>
     </row>
     <row r="79" spans="1:11">
       <c r="A79" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="B79" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="C79" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="D79" s="6" t="s">
-        <v>219</v>
+      <c r="C79" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>338</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="F79" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="F79" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="G79" s="4" t="s">
-        <v>218</v>
+      <c r="G79" s="5" t="s">
+        <v>340</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="I79" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="J79" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="J79" s="1" t="s">
-        <v>631</v>
-      </c>
       <c r="K79" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="80" spans="1:11">
       <c r="A80" s="1" t="s">
-        <v>590</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="F80" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="E80" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="F80" s="4" t="s">
         <v>392</v>
       </c>
-      <c r="G80" s="2" t="s">
-        <v>214</v>
+      <c r="G80" s="4" t="s">
+        <v>218</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="I80" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="J80" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="J80" s="1" t="s">
-        <v>631</v>
-      </c>
       <c r="K80" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="81" spans="1:11">
       <c r="A81" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="B81" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="C81" s="4" t="s">
-        <v>573</v>
-      </c>
-      <c r="D81" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="E81" s="6" t="s">
-        <v>574</v>
-      </c>
-      <c r="F81" s="4" t="s">
-        <v>674</v>
-      </c>
-      <c r="G81" s="4" t="s">
-        <v>213</v>
+        <v>589</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>214</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="I81" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="J81" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="J81" s="1" t="s">
-        <v>631</v>
-      </c>
       <c r="K81" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="82" spans="1:11">
       <c r="A82" s="1" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>671</v>
+        <v>224</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>672</v>
+        <v>572</v>
       </c>
       <c r="D82" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>573</v>
+      </c>
+      <c r="F82" s="4" t="s">
         <v>673</v>
       </c>
-      <c r="E82" s="6"/>
-      <c r="F82" s="4" t="s">
-        <v>675</v>
-      </c>
-      <c r="G82" s="1" t="s">
-        <v>12</v>
+      <c r="G82" s="4" t="s">
+        <v>213</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="I82" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="J82" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="J82" s="1" t="s">
-        <v>631</v>
-      </c>
       <c r="K82" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="83" spans="1:11">
       <c r="A83" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>670</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>672</v>
+      </c>
+      <c r="E83" s="6"/>
+      <c r="F83" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11">
+      <c r="A84" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B83" s="4" t="s">
+      <c r="B84" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="C84" s="4" t="s">
         <v>677</v>
       </c>
-      <c r="C83" s="4" t="s">
+      <c r="D84" s="6" t="s">
         <v>678</v>
       </c>
-      <c r="D83" s="6" t="s">
+      <c r="E84" s="6" t="s">
         <v>679</v>
       </c>
-      <c r="E83" s="6" t="s">
+      <c r="F84" s="4" t="s">
         <v>680</v>
       </c>
-      <c r="F83" s="4" t="s">
+      <c r="G84" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="J84" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" ht="34">
+      <c r="A85" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>683</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>684</v>
+      </c>
+      <c r="D85" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>685</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="G85" s="8" t="s">
         <v>681</v>
       </c>
-      <c r="G83" s="8" t="s">
-        <v>676</v>
-      </c>
-      <c r="H83" s="1" t="s">
-        <v>569</v>
-      </c>
-      <c r="I83" s="1" t="s">
+      <c r="H85" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="J85" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="J83" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="K83" s="1" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11" ht="34">
-      <c r="A84" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="B84" s="4" t="s">
-        <v>684</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>685</v>
-      </c>
-      <c r="D84" s="9" t="s">
-        <v>683</v>
-      </c>
-      <c r="E84" s="6" t="s">
-        <v>686</v>
-      </c>
-      <c r="F84" s="4" t="s">
-        <v>687</v>
-      </c>
-      <c r="G84" s="8" t="s">
-        <v>682</v>
-      </c>
-      <c r="H84" s="1" t="s">
-        <v>569</v>
-      </c>
-      <c r="I84" s="1" t="s">
-        <v>630</v>
-      </c>
-      <c r="J84" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="K84" s="1" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11">
-      <c r="A85" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>689</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>692</v>
-      </c>
-      <c r="D85" s="6" t="s">
-        <v>691</v>
-      </c>
-      <c r="E85" s="6" t="s">
-        <v>680</v>
-      </c>
-      <c r="F85" s="4" t="s">
-        <v>690</v>
-      </c>
-      <c r="G85" s="8" t="s">
-        <v>688</v>
-      </c>
-      <c r="H85" s="1" t="s">
-        <v>569</v>
-      </c>
-      <c r="I85" s="1" t="s">
-        <v>630</v>
-      </c>
-      <c r="J85" s="1" t="s">
-        <v>631</v>
-      </c>
       <c r="K85" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="86" spans="1:11">
       <c r="A86" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>698</v>
+        <v>679</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="G86" s="8" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="I86" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="J86" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="J86" s="1" t="s">
-        <v>631</v>
-      </c>
       <c r="K86" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="87" spans="1:11">
       <c r="A87" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="E87" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>693</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>695</v>
+      </c>
+      <c r="E87" s="6" t="s">
+        <v>697</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>692</v>
+      </c>
+      <c r="G87" s="8" t="s">
+        <v>696</v>
+      </c>
+      <c r="H87" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="F87" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="G87" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="H87" s="1" t="s">
-        <v>569</v>
-      </c>
       <c r="I87" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="J87" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="J87" s="1" t="s">
-        <v>631</v>
-      </c>
       <c r="K87" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="88" spans="1:11">
       <c r="A88" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>571</v>
+        <v>566</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>567</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>211</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="I88" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="J88" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="J88" s="1" t="s">
-        <v>631</v>
-      </c>
       <c r="K88" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="89" spans="1:11">
       <c r="A89" s="1" t="s">
-        <v>600</v>
+        <v>223</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>323</v>
+        <v>569</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>325</v>
+        <v>570</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="G89" s="2" t="s">
-        <v>324</v>
+        <v>390</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>307</v>
+        <v>568</v>
       </c>
       <c r="I89" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="J89" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="J89" s="1" t="s">
-        <v>639</v>
-      </c>
       <c r="K89" s="1" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
     </row>
     <row r="90" spans="1:11">
       <c r="A90" s="1" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>310</v>
+        <v>327</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="H90" s="1" t="s">
         <v>307</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="J90" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="K90" s="1" t="s">
         <v>639</v>
-      </c>
-      <c r="K90" s="1" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="91" spans="1:11">
       <c r="A91" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="H91" s="1" t="s">
         <v>307</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="J91" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="K91" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="K91" s="1" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" ht="34">
+    </row>
+    <row r="92" spans="1:11">
       <c r="A92" s="1" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>320</v>
+        <v>313</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>314</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H92" s="1" t="s">
         <v>307</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="J92" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="K92" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="K92" s="1" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11">
+    </row>
+    <row r="93" spans="1:11" ht="34">
       <c r="A93" s="1" t="s">
-        <v>212</v>
+        <v>598</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>564</v>
+        <v>319</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>320</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>209</v>
+        <v>321</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>565</v>
+        <v>322</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>389</v>
+        <v>411</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>208</v>
+        <v>318</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>563</v>
+        <v>307</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>563</v>
+        <v>639</v>
       </c>
     </row>
     <row r="94" spans="1:11">
       <c r="A94" s="1" t="s">
-        <v>589</v>
+        <v>212</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>428</v>
+        <v>563</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>209</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="G94" s="1" t="s">
-        <v>117</v>
+      <c r="G94" s="2" t="s">
+        <v>208</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="95" spans="1:11">
       <c r="A95" s="1" t="s">
-        <v>90</v>
+        <v>588</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>653</v>
+        <v>115</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>135</v>
+        <v>427</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>135</v>
+        <v>561</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>655</v>
+        <v>387</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>12</v>
+        <v>117</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>517</v>
+        <v>562</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>615</v>
+        <v>629</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>620</v>
+        <v>635</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>621</v>
+        <v>562</v>
       </c>
     </row>
     <row r="96" spans="1:11">
       <c r="A96" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>518</v>
+        <v>652</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>135</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>199</v>
+        <v>135</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>647</v>
+        <v>654</v>
       </c>
       <c r="G96" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="J96" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="K96" s="1" t="s">
         <v>620</v>
-      </c>
-      <c r="K96" s="1" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="97" spans="1:11">
       <c r="A97" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>135</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>523</v>
+        <v>12</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="J97" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="K97" s="1" t="s">
         <v>620</v>
-      </c>
-      <c r="K97" s="1" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="98" spans="1:11">
       <c r="A98" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>654</v>
+        <v>646</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>29</v>
+        <v>522</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="J98" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="K98" s="1" t="s">
         <v>620</v>
-      </c>
-      <c r="K98" s="1" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="99" spans="1:11">
       <c r="A99" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>30</v>
+        <v>519</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>369</v>
+        <v>653</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="J99" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="K99" s="1" t="s">
         <v>620</v>
-      </c>
-      <c r="K99" s="1" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="100" spans="1:11">
       <c r="A100" s="1" t="s">
-        <v>252</v>
+        <v>95</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>243</v>
+        <v>30</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>581</v>
+        <v>525</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>246</v>
+        <v>158</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>244</v>
+        <v>177</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="G100" s="2" t="s">
-        <v>245</v>
+        <v>368</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="J100" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="K100" s="1" t="s">
         <v>620</v>
-      </c>
-      <c r="K100" s="1" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="101" spans="1:11">
       <c r="A101" s="1" t="s">
-        <v>94</v>
+        <v>252</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>524</v>
+        <v>243</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>525</v>
+        <v>580</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>157</v>
+        <v>246</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>135</v>
+        <v>244</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>647</v>
-      </c>
-      <c r="G101" s="1" t="s">
-        <v>523</v>
+        <v>397</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="J101" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="K101" s="1" t="s">
         <v>620</v>
-      </c>
-      <c r="K101" s="1" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="102" spans="1:11">
       <c r="A102" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>656</v>
+        <v>523</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>135</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="J102" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="K102" s="1" t="s">
         <v>620</v>
-      </c>
-      <c r="K102" s="1" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="103" spans="1:11">
       <c r="A103" s="1" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>535</v>
+        <v>655</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>536</v>
+        <v>521</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>161</v>
+        <v>135</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>537</v>
+        <v>135</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>373</v>
+        <v>646</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>34</v>
+        <v>522</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>534</v>
+        <v>516</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="J103" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="K103" s="1" t="s">
         <v>620</v>
-      </c>
-      <c r="K103" s="1" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="104" spans="1:11">
       <c r="A104" s="1" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>553</v>
+        <v>534</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>554</v>
+        <v>535</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>206</v>
+        <v>536</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>662</v>
+        <v>372</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="J104" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>634</v>
+        <v>622</v>
       </c>
     </row>
     <row r="105" spans="1:11">
       <c r="A105" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>416</v>
+        <v>553</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>135</v>
+        <v>206</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>383</v>
+        <v>661</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>523</v>
+        <v>40</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="J105" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="106" spans="1:11">
       <c r="A106" s="1" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>529</v>
+        <v>554</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>530</v>
+        <v>415</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>198</v>
+        <v>135</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>32</v>
+        <v>522</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>424</v>
+        <v>533</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="J106" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>622</v>
+        <v>633</v>
       </c>
     </row>
     <row r="107" spans="1:11">
       <c r="A107" s="1" t="s">
-        <v>661</v>
+        <v>97</v>
       </c>
       <c r="B107" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="J107" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="K107" s="1" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11">
+      <c r="A108" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="C108" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="C107" s="1" t="s">
+      <c r="D108" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="D107" s="1" t="s">
-        <v>667</v>
-      </c>
-      <c r="F107" s="1" t="s">
+      <c r="F108" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="G108" s="7" t="s">
         <v>663</v>
       </c>
-      <c r="G107" s="7" t="s">
-        <v>664</v>
-      </c>
-      <c r="H107" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="I107" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="J107" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="K107" s="1" t="s">
-        <v>605</v>
+      <c r="H108" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="J108" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="K108" s="1" t="s">
+        <v>604</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K106">
-    <sortCondition ref="J2:J106"/>
-    <sortCondition ref="K2:K106"/>
-    <sortCondition ref="B2:B106"/>
-    <sortCondition ref="C2:C106"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K107">
+    <sortCondition ref="J2:J107"/>
+    <sortCondition ref="K2:K107"/>
+    <sortCondition ref="B2:B107"/>
+    <sortCondition ref="C2:C107"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="2">
@@ -6592,13 +6656,13 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="G93" r:id="rId1" xr:uid="{A39B8C40-8D45-EB49-A4FC-B32617C3743A}"/>
-    <hyperlink ref="G80" r:id="rId2" xr:uid="{B5DCC527-C34A-A84A-863F-C7614151FE6F}"/>
+    <hyperlink ref="G94" r:id="rId1" xr:uid="{A39B8C40-8D45-EB49-A4FC-B32617C3743A}"/>
+    <hyperlink ref="G81" r:id="rId2" xr:uid="{B5DCC527-C34A-A84A-863F-C7614151FE6F}"/>
     <hyperlink ref="G5" r:id="rId3" xr:uid="{9F3F15C4-C0FD-AE4F-A261-C94D2C5C5CDD}"/>
     <hyperlink ref="G9" r:id="rId4" xr:uid="{57110EDF-FEA5-304D-BC8D-B61106C21880}"/>
     <hyperlink ref="G40" r:id="rId5" location="sale_active" xr:uid="{730FA5EB-C91B-144D-A783-4D831224B6A9}"/>
     <hyperlink ref="G6" r:id="rId6" xr:uid="{1F8F556A-7472-764F-A198-D7F42EFCC387}"/>
-    <hyperlink ref="G100" r:id="rId7" xr:uid="{D0E463C4-46AF-0146-87CD-46876FB5CA0D}"/>
+    <hyperlink ref="G101" r:id="rId7" xr:uid="{D0E463C4-46AF-0146-87CD-46876FB5CA0D}"/>
     <hyperlink ref="G23" r:id="rId8" xr:uid="{DF8FD8B1-A50B-9E4E-9410-150C09502DAB}"/>
     <hyperlink ref="G29" r:id="rId9" xr:uid="{FF011359-39BB-A040-AED2-D2D90A217A10}"/>
     <hyperlink ref="G32" r:id="rId10" xr:uid="{52BA0BCD-A138-3A42-93E9-9408D0B6CD41}"/>
@@ -6611,17 +6675,18 @@
     <hyperlink ref="G24" r:id="rId17" xr:uid="{645725E7-FD7F-7841-BD5D-4F55FBCDAB8D}"/>
     <hyperlink ref="G26" r:id="rId18" xr:uid="{D8E83196-8EED-474F-A39D-4B8A53066F90}"/>
     <hyperlink ref="G8" r:id="rId19" xr:uid="{D8074921-21AA-094E-B1E8-1A2B5D8215AB}"/>
-    <hyperlink ref="G90" r:id="rId20" xr:uid="{67DB94DD-4F2A-2B47-90EF-FED3ED8F2017}"/>
-    <hyperlink ref="G91" r:id="rId21" xr:uid="{F6F3D17A-11C3-804A-89D9-3C231334A22A}"/>
-    <hyperlink ref="G92" r:id="rId22" xr:uid="{D5F7639A-8FC0-444F-B0B1-291456215366}"/>
-    <hyperlink ref="G89" r:id="rId23" xr:uid="{40CF7C3F-7CEF-0245-8E88-7892E420529A}"/>
-    <hyperlink ref="G76" r:id="rId24" xr:uid="{B2FAD3F1-82CD-564A-89EB-8DE0938B2D53}"/>
-    <hyperlink ref="G78" r:id="rId25" xr:uid="{1FE5A63E-4D12-4C4C-A566-E71804C9006E}"/>
-    <hyperlink ref="G107" r:id="rId26" xr:uid="{237E6794-0DAA-2340-869C-73B873A6D324}"/>
-    <hyperlink ref="G83" r:id="rId27" xr:uid="{67CF96A7-8792-ED4D-852A-2AD878FBA0A7}"/>
-    <hyperlink ref="G84" r:id="rId28" xr:uid="{DDD41264-2363-7B4D-BE34-303C44BC64C2}"/>
-    <hyperlink ref="G85" r:id="rId29" xr:uid="{974EC1EA-84B1-4147-9488-B123C8DAB06A}"/>
-    <hyperlink ref="G86" r:id="rId30" xr:uid="{76485F94-E942-EF4C-B260-4F0E2DC7AE4C}"/>
+    <hyperlink ref="G91" r:id="rId20" xr:uid="{67DB94DD-4F2A-2B47-90EF-FED3ED8F2017}"/>
+    <hyperlink ref="G92" r:id="rId21" xr:uid="{F6F3D17A-11C3-804A-89D9-3C231334A22A}"/>
+    <hyperlink ref="G93" r:id="rId22" xr:uid="{D5F7639A-8FC0-444F-B0B1-291456215366}"/>
+    <hyperlink ref="G90" r:id="rId23" xr:uid="{40CF7C3F-7CEF-0245-8E88-7892E420529A}"/>
+    <hyperlink ref="G77" r:id="rId24" xr:uid="{B2FAD3F1-82CD-564A-89EB-8DE0938B2D53}"/>
+    <hyperlink ref="G79" r:id="rId25" xr:uid="{1FE5A63E-4D12-4C4C-A566-E71804C9006E}"/>
+    <hyperlink ref="G108" r:id="rId26" xr:uid="{237E6794-0DAA-2340-869C-73B873A6D324}"/>
+    <hyperlink ref="G84" r:id="rId27" xr:uid="{67CF96A7-8792-ED4D-852A-2AD878FBA0A7}"/>
+    <hyperlink ref="G85" r:id="rId28" xr:uid="{DDD41264-2363-7B4D-BE34-303C44BC64C2}"/>
+    <hyperlink ref="G86" r:id="rId29" xr:uid="{974EC1EA-84B1-4147-9488-B123C8DAB06A}"/>
+    <hyperlink ref="G87" r:id="rId30" xr:uid="{76485F94-E942-EF4C-B260-4F0E2DC7AE4C}"/>
+    <hyperlink ref="G55" r:id="rId31" xr:uid="{3F9A98AF-B9BE-D742-A02A-E7DAD28A7767}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait"/>

--- a/db/A7XLK-4401-DepartmentStore.xlsx
+++ b/db/A7XLK-4401-DepartmentStore.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10912"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11010"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAEA71ED-598B-2B4D-B873-43FD91585F8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF384651-012E-F44D-8E2D-54DC351CAFB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6080" yWindow="1140" windowWidth="37900" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4260" yWindow="1540" windowWidth="37900" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Shopping" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1179" uniqueCount="706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="714">
   <si>
     <t>title</t>
   </si>
@@ -2486,6 +2486,37 @@
   </si>
   <si>
     <t>fig/XLK-411-Shopping/AiCity-913-蝦皮店到店.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>141</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.7資訊通信</t>
+  </si>
+  <si>
+    <t>手機電腦維修</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蘋果保衛站</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃園市桃園區復興路278號</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-339-8018</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.applecarestation.com.tw/index.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-411-Shopping/AiCity-913-蘋果保衛站.png</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2868,7 +2899,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K108"/>
+  <dimension ref="A1:K109"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="4.6640625" style="1" customWidth="1"/>
@@ -6189,57 +6220,57 @@
     </row>
     <row r="96" spans="1:11">
       <c r="A96" s="1" t="s">
-        <v>90</v>
+        <v>706</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>652</v>
+        <v>709</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>515</v>
+        <v>710</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>135</v>
+        <v>711</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>135</v>
+        <v>244</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>654</v>
-      </c>
-      <c r="G96" s="1" t="s">
-        <v>12</v>
+        <v>713</v>
+      </c>
+      <c r="G96" s="7" t="s">
+        <v>712</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>516</v>
+        <v>708</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>614</v>
+        <v>629</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>619</v>
+        <v>707</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>620</v>
+        <v>708</v>
       </c>
     </row>
     <row r="97" spans="1:11">
       <c r="A97" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>517</v>
+        <v>652</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>135</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>199</v>
+        <v>135</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="G97" s="1" t="s">
         <v>12</v>
@@ -6259,25 +6290,25 @@
     </row>
     <row r="98" spans="1:11">
       <c r="A98" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>135</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>646</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>522</v>
+        <v>12</v>
       </c>
       <c r="H98" s="1" t="s">
         <v>516</v>
@@ -6294,25 +6325,25 @@
     </row>
     <row r="99" spans="1:11">
       <c r="A99" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>29</v>
+        <v>522</v>
       </c>
       <c r="H99" s="1" t="s">
         <v>516</v>
@@ -6329,25 +6360,25 @@
     </row>
     <row r="100" spans="1:11">
       <c r="A100" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>30</v>
+        <v>519</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>368</v>
+        <v>653</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H100" s="1" t="s">
         <v>516</v>
@@ -6364,25 +6395,25 @@
     </row>
     <row r="101" spans="1:11">
       <c r="A101" s="1" t="s">
-        <v>252</v>
+        <v>95</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>243</v>
+        <v>30</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>580</v>
+        <v>525</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>246</v>
+        <v>158</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>244</v>
+        <v>177</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="G101" s="2" t="s">
-        <v>245</v>
+        <v>368</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="H101" s="1" t="s">
         <v>516</v>
@@ -6399,25 +6430,25 @@
     </row>
     <row r="102" spans="1:11">
       <c r="A102" s="1" t="s">
-        <v>94</v>
+        <v>252</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>523</v>
+        <v>243</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>524</v>
+        <v>580</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>157</v>
+        <v>246</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>135</v>
+        <v>244</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>646</v>
-      </c>
-      <c r="G102" s="1" t="s">
-        <v>522</v>
+        <v>397</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H102" s="1" t="s">
         <v>516</v>
@@ -6434,16 +6465,16 @@
     </row>
     <row r="103" spans="1:11">
       <c r="A103" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>655</v>
+        <v>523</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>135</v>
@@ -6469,28 +6500,28 @@
     </row>
     <row r="104" spans="1:11">
       <c r="A104" s="1" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>534</v>
+        <v>655</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>535</v>
+        <v>521</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>161</v>
+        <v>135</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>536</v>
+        <v>135</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>372</v>
+        <v>646</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>34</v>
+        <v>522</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>533</v>
+        <v>516</v>
       </c>
       <c r="I104" s="1" t="s">
         <v>614</v>
@@ -6499,30 +6530,30 @@
         <v>619</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="105" spans="1:11">
       <c r="A105" s="1" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>552</v>
+        <v>534</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>206</v>
+        <v>536</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>661</v>
+        <v>372</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H105" s="1" t="s">
         <v>533</v>
@@ -6534,30 +6565,30 @@
         <v>619</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>633</v>
+        <v>622</v>
       </c>
     </row>
     <row r="106" spans="1:11">
       <c r="A106" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>415</v>
+        <v>553</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>135</v>
+        <v>206</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>382</v>
+        <v>661</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>522</v>
+        <v>40</v>
       </c>
       <c r="H106" s="1" t="s">
         <v>533</v>
@@ -6574,28 +6605,28 @@
     </row>
     <row r="107" spans="1:11">
       <c r="A107" s="1" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>528</v>
+        <v>554</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>529</v>
+        <v>415</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>198</v>
+        <v>135</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>32</v>
+        <v>522</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>423</v>
+        <v>533</v>
       </c>
       <c r="I107" s="1" t="s">
         <v>614</v>
@@ -6604,47 +6635,82 @@
         <v>619</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>621</v>
+        <v>633</v>
       </c>
     </row>
     <row r="108" spans="1:11">
       <c r="A108" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="J108" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="K108" s="1" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11">
+      <c r="A109" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="B108" s="1" t="s">
+      <c r="B109" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="C108" s="1" t="s">
+      <c r="C109" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="D108" s="1" t="s">
+      <c r="D109" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="F108" s="1" t="s">
+      <c r="F109" s="1" t="s">
         <v>662</v>
       </c>
-      <c r="G108" s="7" t="s">
+      <c r="G109" s="7" t="s">
         <v>663</v>
       </c>
-      <c r="H108" s="1" t="s">
+      <c r="H109" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="I108" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="J108" s="1" t="s">
+      <c r="I109" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="J109" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="K108" s="1" t="s">
+      <c r="K109" s="1" t="s">
         <v>604</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K107">
-    <sortCondition ref="J2:J107"/>
-    <sortCondition ref="K2:K107"/>
-    <sortCondition ref="B2:B107"/>
-    <sortCondition ref="C2:C107"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K108">
+    <sortCondition ref="J2:J108"/>
+    <sortCondition ref="K2:K108"/>
+    <sortCondition ref="B2:B108"/>
+    <sortCondition ref="C2:C108"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="2">
@@ -6662,7 +6728,7 @@
     <hyperlink ref="G9" r:id="rId4" xr:uid="{57110EDF-FEA5-304D-BC8D-B61106C21880}"/>
     <hyperlink ref="G40" r:id="rId5" location="sale_active" xr:uid="{730FA5EB-C91B-144D-A783-4D831224B6A9}"/>
     <hyperlink ref="G6" r:id="rId6" xr:uid="{1F8F556A-7472-764F-A198-D7F42EFCC387}"/>
-    <hyperlink ref="G101" r:id="rId7" xr:uid="{D0E463C4-46AF-0146-87CD-46876FB5CA0D}"/>
+    <hyperlink ref="G102" r:id="rId7" xr:uid="{D0E463C4-46AF-0146-87CD-46876FB5CA0D}"/>
     <hyperlink ref="G23" r:id="rId8" xr:uid="{DF8FD8B1-A50B-9E4E-9410-150C09502DAB}"/>
     <hyperlink ref="G29" r:id="rId9" xr:uid="{FF011359-39BB-A040-AED2-D2D90A217A10}"/>
     <hyperlink ref="G32" r:id="rId10" xr:uid="{52BA0BCD-A138-3A42-93E9-9408D0B6CD41}"/>
@@ -6681,12 +6747,13 @@
     <hyperlink ref="G90" r:id="rId23" xr:uid="{40CF7C3F-7CEF-0245-8E88-7892E420529A}"/>
     <hyperlink ref="G77" r:id="rId24" xr:uid="{B2FAD3F1-82CD-564A-89EB-8DE0938B2D53}"/>
     <hyperlink ref="G79" r:id="rId25" xr:uid="{1FE5A63E-4D12-4C4C-A566-E71804C9006E}"/>
-    <hyperlink ref="G108" r:id="rId26" xr:uid="{237E6794-0DAA-2340-869C-73B873A6D324}"/>
+    <hyperlink ref="G109" r:id="rId26" xr:uid="{237E6794-0DAA-2340-869C-73B873A6D324}"/>
     <hyperlink ref="G84" r:id="rId27" xr:uid="{67CF96A7-8792-ED4D-852A-2AD878FBA0A7}"/>
     <hyperlink ref="G85" r:id="rId28" xr:uid="{DDD41264-2363-7B4D-BE34-303C44BC64C2}"/>
     <hyperlink ref="G86" r:id="rId29" xr:uid="{974EC1EA-84B1-4147-9488-B123C8DAB06A}"/>
     <hyperlink ref="G87" r:id="rId30" xr:uid="{76485F94-E942-EF4C-B260-4F0E2DC7AE4C}"/>
     <hyperlink ref="G55" r:id="rId31" xr:uid="{3F9A98AF-B9BE-D742-A02A-E7DAD28A7767}"/>
+    <hyperlink ref="G96" r:id="rId32" xr:uid="{259FD402-6D0D-3E43-9F73-244A8FA24539}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait"/>

--- a/db/A7XLK-4401-DepartmentStore.xlsx
+++ b/db/A7XLK-4401-DepartmentStore.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF384651-012E-F44D-8E2D-54DC351CAFB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F4F81F9-BAF8-1A4A-80E8-31C921B1FA31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4260" yWindow="1540" windowWidth="37900" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3060" yWindow="7000" windowWidth="37900" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Shopping" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="714">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1366" uniqueCount="815">
   <si>
     <t>title</t>
   </si>
@@ -2519,12 +2519,898 @@
     <t>fig/XLK-411-Shopping/AiCity-913-蘋果保衛站.png</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>3.4金融工商</t>
+  </si>
+  <si>
+    <t>銀行證劵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金融銀行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>301</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>台新銀行 新莊副都心分行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>新北市新莊區中原路</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>150</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>號</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-8521-1388 #100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>09:00 - 15:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/A7XLK-213-台新.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.taishinbank.com.tw/TSB/personal/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>302</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>兆豐銀行桃興分行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>桃園市桃園區復興路</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>180</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>號</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-332-7126</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/A7XLK-213-兆豐銀行.jpg</t>
+  </si>
+  <si>
+    <t>https://www.megabank.com.tw/personal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>303</t>
+  </si>
+  <si>
+    <t>中國信託商業銀行林口分行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>桃園縣龜山鄉復興一路</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>233</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>號</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-396-2777</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/A7XLK-213-中國信託.jpg</t>
+  </si>
+  <si>
+    <t>https://www.ctbcbank.com/twrbo/zh_tw/dep_index.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元大商業銀行林口分行  </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>桃園縣龜山鄉文化三路</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>118</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>號</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-328-8999</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/A7XLK-213-元大.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.yuantabank.com.tw/bank/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>305</t>
+  </si>
+  <si>
+    <t>元大證劵長庚分公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>桃園市龜山區文化二路</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>38</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>之</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>號二樓</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-397-8787</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 08:30 - 16:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/A7XLK-213-元大證劵.jpg</t>
+  </si>
+  <si>
+    <t>https://www.yuanta.com.tw/eyuanta/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">遠東國際商業銀行林口分行 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>桃園縣龜山鄉復興一路</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>227</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>號</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-397-3888</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/A7XLK-213-遠東銀行.jpg</t>
+  </si>
+  <si>
+    <t>https://www.feib.com.tw/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">渣打國際商業銀行公西分行 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>桃園市龜山區復興一路</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>237</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>號</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-397-2288</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/A7XLK-213-渣打銀行.jpeg</t>
+  </si>
+  <si>
+    <t>https://service.standardchartered.com.tw/ssl/campaign/credit-cards/signature-card.asp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>308</t>
+  </si>
+  <si>
+    <t>玉山銀行 林口分行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>桃園市龜山區復興一路</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>230</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>號</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-396-1313</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/A7XLK-213-玉山銀行.png</t>
+  </si>
+  <si>
+    <t>https://www.esunbank.com.tw/bank/personal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>309</t>
+  </si>
+  <si>
+    <t>國泰世華銀行林口分行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>桃園市龜山區文化三路</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>319</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>號</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-327-1689</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/A7XLK-213-國泰世華.jpg</t>
+  </si>
+  <si>
+    <t>https://www.cathaybk.com.tw/cathaybk/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>陽信銀行林口分行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>桃園市龜山區文化三路</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>331</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>號</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>1~2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>樓</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-327-3559</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/A7XLK-213-陽信銀行.jpg</t>
+  </si>
+  <si>
+    <t>https://www.sunnybank.com.tw/net/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>臺灣銀行林口分行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>桃園市龜山區復興一路</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>368</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>號</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-327-7299</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/A7XLK-213-台灣銀行.jpg</t>
+  </si>
+  <si>
+    <t>https://www.bot.com.tw/Pages/default.aspx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>312</t>
+  </si>
+  <si>
+    <t>第一銀行林口分行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>桃園市龜山區文化二路</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>76</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>號</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-318-6611</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/A7XLK-213-第一銀行.png</t>
+  </si>
+  <si>
+    <t>https://www.firstbank.com.tw/sites/fbweb/Home</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>313</t>
+  </si>
+  <si>
+    <t>合作金庫銀行 林口分行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>桃園市龜山區文化二路</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>49</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>號</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-318-3880</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/A7XLK-213-合作金庫.png</t>
+  </si>
+  <si>
+    <t>https://www.tcb-bank.com.tw/Pages/index.aspx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>314</t>
+  </si>
+  <si>
+    <t>華南銀行林口分行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>桃園市龜山區復興一路</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>號</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-318-3456</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/A7XLK-213-華南銀行.png</t>
+  </si>
+  <si>
+    <t>https://www.hncb.com.tw/wps/portal/HNCB/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>315</t>
+  </si>
+  <si>
+    <t>彰化銀行東林口分行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>桃園市龜山區復興一路</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>235</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>號</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-397-5555</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/A7XLK-213-彰化銀行.jpg</t>
+  </si>
+  <si>
+    <t>https://www.bankchb.com/frontend/index.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>316</t>
+  </si>
+  <si>
+    <t>台灣土地銀行林口分行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>桃園市龜山區文化二路</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>109</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>號</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-318-2128</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/A7XLK-213-土地銀行.jpg</t>
+  </si>
+  <si>
+    <t>https://www.landbank.com.tw/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -2559,6 +3445,26 @@
       <family val="1"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="PMingLiU"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2581,7 +3487,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
@@ -2596,6 +3502,11 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -2899,7 +3810,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K109"/>
+  <dimension ref="A1:K125"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="4.6640625" style="1" customWidth="1"/>
@@ -6703,6 +7614,566 @@
       </c>
       <c r="K109" s="1" t="s">
         <v>604</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" ht="17">
+      <c r="A110" s="10" t="s">
+        <v>717</v>
+      </c>
+      <c r="B110" s="11" t="s">
+        <v>718</v>
+      </c>
+      <c r="C110" s="12" t="s">
+        <v>719</v>
+      </c>
+      <c r="D110" s="11" t="s">
+        <v>720</v>
+      </c>
+      <c r="E110" s="13" t="s">
+        <v>721</v>
+      </c>
+      <c r="F110" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="G110" s="14" t="s">
+        <v>723</v>
+      </c>
+      <c r="H110" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="I110" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="J110" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="K110" s="1" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" ht="17">
+      <c r="A111" s="10" t="s">
+        <v>724</v>
+      </c>
+      <c r="B111" s="11" t="s">
+        <v>725</v>
+      </c>
+      <c r="C111" s="12" t="s">
+        <v>726</v>
+      </c>
+      <c r="D111" s="11" t="s">
+        <v>727</v>
+      </c>
+      <c r="E111" s="13" t="s">
+        <v>721</v>
+      </c>
+      <c r="F111" s="11" t="s">
+        <v>728</v>
+      </c>
+      <c r="G111" s="14" t="s">
+        <v>729</v>
+      </c>
+      <c r="H111" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="I111" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="J111" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="K111" s="1" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" ht="17">
+      <c r="A112" s="10" t="s">
+        <v>730</v>
+      </c>
+      <c r="B112" s="11" t="s">
+        <v>731</v>
+      </c>
+      <c r="C112" s="12" t="s">
+        <v>732</v>
+      </c>
+      <c r="D112" s="11" t="s">
+        <v>733</v>
+      </c>
+      <c r="E112" s="13" t="s">
+        <v>721</v>
+      </c>
+      <c r="F112" s="11" t="s">
+        <v>734</v>
+      </c>
+      <c r="G112" s="14" t="s">
+        <v>735</v>
+      </c>
+      <c r="H112" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="I112" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="J112" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="K112" s="1" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" ht="17">
+      <c r="A113" s="10" t="s">
+        <v>736</v>
+      </c>
+      <c r="B113" s="11" t="s">
+        <v>737</v>
+      </c>
+      <c r="C113" s="12" t="s">
+        <v>738</v>
+      </c>
+      <c r="D113" s="11" t="s">
+        <v>739</v>
+      </c>
+      <c r="E113" s="13" t="s">
+        <v>721</v>
+      </c>
+      <c r="F113" s="11" t="s">
+        <v>740</v>
+      </c>
+      <c r="G113" s="14" t="s">
+        <v>741</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="I113" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="J113" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="K113" s="1" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" ht="17">
+      <c r="A114" s="10" t="s">
+        <v>742</v>
+      </c>
+      <c r="B114" s="11" t="s">
+        <v>743</v>
+      </c>
+      <c r="C114" s="12" t="s">
+        <v>744</v>
+      </c>
+      <c r="D114" s="11" t="s">
+        <v>745</v>
+      </c>
+      <c r="E114" s="13" t="s">
+        <v>746</v>
+      </c>
+      <c r="F114" s="11" t="s">
+        <v>747</v>
+      </c>
+      <c r="G114" s="14" t="s">
+        <v>748</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="I114" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="J114" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="K114" s="1" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" ht="17">
+      <c r="A115" s="10" t="s">
+        <v>749</v>
+      </c>
+      <c r="B115" s="11" t="s">
+        <v>750</v>
+      </c>
+      <c r="C115" s="12" t="s">
+        <v>751</v>
+      </c>
+      <c r="D115" s="11" t="s">
+        <v>752</v>
+      </c>
+      <c r="E115" s="13" t="s">
+        <v>721</v>
+      </c>
+      <c r="F115" s="11" t="s">
+        <v>753</v>
+      </c>
+      <c r="G115" s="14" t="s">
+        <v>754</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="I115" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="J115" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="K115" s="1" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" ht="17">
+      <c r="A116" s="10" t="s">
+        <v>755</v>
+      </c>
+      <c r="B116" s="11" t="s">
+        <v>756</v>
+      </c>
+      <c r="C116" s="12" t="s">
+        <v>757</v>
+      </c>
+      <c r="D116" s="11" t="s">
+        <v>758</v>
+      </c>
+      <c r="E116" s="13" t="s">
+        <v>721</v>
+      </c>
+      <c r="F116" s="11" t="s">
+        <v>759</v>
+      </c>
+      <c r="G116" s="14" t="s">
+        <v>760</v>
+      </c>
+      <c r="H116" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="I116" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="J116" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="K116" s="1" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" ht="17">
+      <c r="A117" s="10" t="s">
+        <v>761</v>
+      </c>
+      <c r="B117" s="11" t="s">
+        <v>762</v>
+      </c>
+      <c r="C117" s="12" t="s">
+        <v>763</v>
+      </c>
+      <c r="D117" s="11" t="s">
+        <v>764</v>
+      </c>
+      <c r="E117" s="13" t="s">
+        <v>721</v>
+      </c>
+      <c r="F117" s="11" t="s">
+        <v>765</v>
+      </c>
+      <c r="G117" s="14" t="s">
+        <v>766</v>
+      </c>
+      <c r="H117" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="I117" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="J117" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="K117" s="1" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" ht="17">
+      <c r="A118" s="10" t="s">
+        <v>767</v>
+      </c>
+      <c r="B118" s="11" t="s">
+        <v>768</v>
+      </c>
+      <c r="C118" s="12" t="s">
+        <v>769</v>
+      </c>
+      <c r="D118" s="11" t="s">
+        <v>770</v>
+      </c>
+      <c r="E118" s="13" t="s">
+        <v>721</v>
+      </c>
+      <c r="F118" s="11" t="s">
+        <v>771</v>
+      </c>
+      <c r="G118" s="14" t="s">
+        <v>772</v>
+      </c>
+      <c r="H118" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="I118" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="J118" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="K118" s="1" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" ht="17">
+      <c r="A119" s="10" t="s">
+        <v>773</v>
+      </c>
+      <c r="B119" s="11" t="s">
+        <v>774</v>
+      </c>
+      <c r="C119" s="12" t="s">
+        <v>775</v>
+      </c>
+      <c r="D119" s="11" t="s">
+        <v>776</v>
+      </c>
+      <c r="E119" s="13" t="s">
+        <v>721</v>
+      </c>
+      <c r="F119" s="11" t="s">
+        <v>777</v>
+      </c>
+      <c r="G119" s="14" t="s">
+        <v>778</v>
+      </c>
+      <c r="H119" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="I119" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="J119" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="K119" s="1" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" ht="17">
+      <c r="A120" s="10" t="s">
+        <v>779</v>
+      </c>
+      <c r="B120" s="11" t="s">
+        <v>780</v>
+      </c>
+      <c r="C120" s="12" t="s">
+        <v>781</v>
+      </c>
+      <c r="D120" s="11" t="s">
+        <v>782</v>
+      </c>
+      <c r="E120" s="13" t="s">
+        <v>721</v>
+      </c>
+      <c r="F120" s="11" t="s">
+        <v>783</v>
+      </c>
+      <c r="G120" s="14" t="s">
+        <v>784</v>
+      </c>
+      <c r="H120" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="I120" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="J120" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="K120" s="1" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" ht="17">
+      <c r="A121" s="10" t="s">
+        <v>785</v>
+      </c>
+      <c r="B121" s="11" t="s">
+        <v>786</v>
+      </c>
+      <c r="C121" s="12" t="s">
+        <v>787</v>
+      </c>
+      <c r="D121" s="11" t="s">
+        <v>788</v>
+      </c>
+      <c r="E121" s="13" t="s">
+        <v>721</v>
+      </c>
+      <c r="F121" s="11" t="s">
+        <v>789</v>
+      </c>
+      <c r="G121" s="14" t="s">
+        <v>790</v>
+      </c>
+      <c r="H121" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="I121" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="J121" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="K121" s="1" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" ht="17">
+      <c r="A122" s="10" t="s">
+        <v>791</v>
+      </c>
+      <c r="B122" s="11" t="s">
+        <v>792</v>
+      </c>
+      <c r="C122" s="12" t="s">
+        <v>793</v>
+      </c>
+      <c r="D122" s="11" t="s">
+        <v>794</v>
+      </c>
+      <c r="E122" s="13" t="s">
+        <v>721</v>
+      </c>
+      <c r="F122" s="11" t="s">
+        <v>795</v>
+      </c>
+      <c r="G122" s="14" t="s">
+        <v>796</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="I122" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="J122" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="K122" s="1" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" ht="17">
+      <c r="A123" s="10" t="s">
+        <v>797</v>
+      </c>
+      <c r="B123" s="11" t="s">
+        <v>798</v>
+      </c>
+      <c r="C123" s="12" t="s">
+        <v>799</v>
+      </c>
+      <c r="D123" s="11" t="s">
+        <v>800</v>
+      </c>
+      <c r="E123" s="13" t="s">
+        <v>721</v>
+      </c>
+      <c r="F123" s="11" t="s">
+        <v>801</v>
+      </c>
+      <c r="G123" s="14" t="s">
+        <v>802</v>
+      </c>
+      <c r="H123" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="I123" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="J123" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="K123" s="1" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" ht="17">
+      <c r="A124" s="10" t="s">
+        <v>803</v>
+      </c>
+      <c r="B124" s="11" t="s">
+        <v>804</v>
+      </c>
+      <c r="C124" s="12" t="s">
+        <v>805</v>
+      </c>
+      <c r="D124" s="11" t="s">
+        <v>806</v>
+      </c>
+      <c r="E124" s="13" t="s">
+        <v>721</v>
+      </c>
+      <c r="F124" s="11" t="s">
+        <v>807</v>
+      </c>
+      <c r="G124" s="14" t="s">
+        <v>808</v>
+      </c>
+      <c r="H124" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="I124" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="J124" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="K124" s="1" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" ht="17">
+      <c r="A125" s="10" t="s">
+        <v>809</v>
+      </c>
+      <c r="B125" s="11" t="s">
+        <v>810</v>
+      </c>
+      <c r="C125" s="12" t="s">
+        <v>811</v>
+      </c>
+      <c r="D125" s="11" t="s">
+        <v>812</v>
+      </c>
+      <c r="E125" s="13" t="s">
+        <v>721</v>
+      </c>
+      <c r="F125" s="11" t="s">
+        <v>813</v>
+      </c>
+      <c r="G125" s="14" t="s">
+        <v>814</v>
+      </c>
+      <c r="H125" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="I125" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="J125" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="K125" s="1" t="s">
+        <v>715</v>
       </c>
     </row>
   </sheetData>
@@ -6754,6 +8225,22 @@
     <hyperlink ref="G87" r:id="rId30" xr:uid="{76485F94-E942-EF4C-B260-4F0E2DC7AE4C}"/>
     <hyperlink ref="G55" r:id="rId31" xr:uid="{3F9A98AF-B9BE-D742-A02A-E7DAD28A7767}"/>
     <hyperlink ref="G96" r:id="rId32" xr:uid="{259FD402-6D0D-3E43-9F73-244A8FA24539}"/>
+    <hyperlink ref="G110" r:id="rId33" xr:uid="{BE1E0B79-FD19-9E4A-8C0B-4EFB65F4A3B5}"/>
+    <hyperlink ref="G112" r:id="rId34" xr:uid="{397B14D3-85A6-954F-BE73-1F87B57618F0}"/>
+    <hyperlink ref="G113" r:id="rId35" xr:uid="{2D19773D-B9E1-CC49-A7AC-090ED1865969}"/>
+    <hyperlink ref="G114" r:id="rId36" xr:uid="{E81741AB-74EC-424F-B159-9E36EA9C2AAC}"/>
+    <hyperlink ref="G115" r:id="rId37" xr:uid="{511B6FEA-C9F1-4C40-A21D-F84B63AD6C4C}"/>
+    <hyperlink ref="G116" r:id="rId38" xr:uid="{67D718D4-7BBC-B344-A4AC-9FA1105EFD84}"/>
+    <hyperlink ref="G117" r:id="rId39" xr:uid="{22680253-E256-FE4D-B393-DDB53AB3EE72}"/>
+    <hyperlink ref="G118" r:id="rId40" xr:uid="{C1737EA1-C466-B64E-BCF7-00204A0E2AD0}"/>
+    <hyperlink ref="G119" r:id="rId41" xr:uid="{6F5E12E0-00B8-584D-BC78-83622C273538}"/>
+    <hyperlink ref="G120" r:id="rId42" xr:uid="{11B1E05E-648B-564A-94BC-978D811708BD}"/>
+    <hyperlink ref="G121" r:id="rId43" xr:uid="{5A565AA0-BF10-DF4A-A6DA-36EBE05F3C2F}"/>
+    <hyperlink ref="G122" r:id="rId44" xr:uid="{5BF47FC7-067E-C842-AA61-041B27521B5A}"/>
+    <hyperlink ref="G123" r:id="rId45" xr:uid="{E0151B3C-0DF4-1744-BE37-A53C6A17645B}"/>
+    <hyperlink ref="G124" r:id="rId46" xr:uid="{AFDB64F8-3083-6742-95DC-074AE7611AA4}"/>
+    <hyperlink ref="G125" r:id="rId47" xr:uid="{BA6B83AA-D235-604B-A845-E9B8182E0D9F}"/>
+    <hyperlink ref="G111" r:id="rId48" xr:uid="{9429C133-7A04-0B4D-A5C7-B68881A3FD4F}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait"/>

--- a/db/A7XLK-4401-DepartmentStore.xlsx
+++ b/db/A7XLK-4401-DepartmentStore.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F4F81F9-BAF8-1A4A-80E8-31C921B1FA31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4C03CA4-5F3E-7048-9249-485394B653EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3060" yWindow="7000" windowWidth="37900" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2020" yWindow="4560" windowWidth="37900" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Shopping" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1366" uniqueCount="815">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1399" uniqueCount="835">
   <si>
     <t>title</t>
   </si>
@@ -1341,9 +1341,6 @@
   </si>
   <si>
     <t>fig/XLK-411-Shopping/AiCity-913-dagain.jpg</t>
-  </si>
-  <si>
-    <t>fig/XLK-411-Shopping/AiCity-913-Owndays.png</t>
   </si>
   <si>
     <t>fig/XLK-411-Shopping/AiCity-913-Jins.png</t>
@@ -2587,46 +2584,6 @@
   </si>
   <si>
     <t>302</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>兆豐銀行桃興分行</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="PMingLiU"/>
-        <family val="1"/>
-        <charset val="136"/>
-      </rPr>
-      <t>桃園市桃園區復興路</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>180</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="PMingLiU"/>
-        <family val="1"/>
-        <charset val="136"/>
-      </rPr>
-      <t>號</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>03-332-7126</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3403,6 +3360,101 @@
   </si>
   <si>
     <t>https://www.landbank.com.tw/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃園市龜山區文化二路11-39號</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>兆豐銀行林口分行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-327-2191</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>317</t>
+  </si>
+  <si>
+    <t>高雄銀行林口分行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-318-6688</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.bok.com.tw/welcome</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/A7XLK-213-高雄銀行.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>照相館</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>142</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>正先進柯達照相館</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>143</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃園市龜山區復興一路138號</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-397-0590</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:00 - 20:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-411-Shopping/AiCity-913-Owndays.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-411-Shopping/AiCity-913-正先進照相館.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://taiwan.worldorgs.com/%E7%9B%AE%E5%BD%95/guishan-district/%E7%A4%BC%E5%93%81%E5%BA%97/%E6%AD%A3%E5%85%88%E9%80%B2%E6%9F%AF%E9%81%94%E7%85%A7%E7%9B%B8%E9%A4%A8fedex%E6%8A%95%E9%81%9E%E4%BB%A3%E6%94%B6%E7%AB%99</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>柯尼卡數位影像中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃園市龜山區文化二路34巷14弄2號</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-328-8202</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>09:30 - 19:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-411-Shopping/AiCity-913-柯尼卡照相館.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://picture-frame-shop-570.business.site/</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3487,7 +3539,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
@@ -3507,6 +3559,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -3810,7 +3863,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K125"/>
+  <dimension ref="A1:K128"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="4.6640625" style="1" customWidth="1"/>
@@ -3853,13 +3906,13 @@
         <v>3</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>585</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -3867,10 +3920,10 @@
         <v>89</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>513</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>514</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>155</v>
@@ -3879,19 +3932,19 @@
         <v>198</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>606</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -3899,10 +3952,10 @@
         <v>61</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>453</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>454</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>135</v>
@@ -3911,22 +3964,22 @@
         <v>135</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J3" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>606</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -3934,10 +3987,10 @@
         <v>88</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>511</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>512</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>154</v>
@@ -3946,22 +3999,22 @@
         <v>197</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J4" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>606</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -3972,7 +4025,7 @@
         <v>225</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>228</v>
@@ -3981,22 +4034,22 @@
         <v>227</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>226</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J5" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>606</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -4004,10 +4057,10 @@
         <v>64</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>135</v>
@@ -4016,22 +4069,22 @@
         <v>186</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>241</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J6" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>606</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -4039,10 +4092,10 @@
         <v>63</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>458</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>459</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>135</v>
@@ -4051,22 +4104,22 @@
         <v>185</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J7" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="K7" s="1" t="s">
         <v>606</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -4077,7 +4130,7 @@
         <v>303</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>304</v>
@@ -4086,22 +4139,22 @@
         <v>305</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>306</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J8" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>606</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="34">
@@ -4121,22 +4174,22 @@
         <v>233</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>234</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J9" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>606</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -4144,10 +4197,10 @@
         <v>62</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>456</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>457</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>135</v>
@@ -4156,22 +4209,22 @@
         <v>184</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J10" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>606</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -4179,10 +4232,10 @@
         <v>84</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>506</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>507</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>152</v>
@@ -4191,22 +4244,22 @@
         <v>195</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -4214,10 +4267,10 @@
         <v>85</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>135</v>
@@ -4226,22 +4279,22 @@
         <v>135</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -4252,7 +4305,7 @@
         <v>336</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>337</v>
@@ -4264,16 +4317,16 @@
         <v>335</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -4281,10 +4334,10 @@
         <v>82</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>501</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>502</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>150</v>
@@ -4299,16 +4352,16 @@
         <v>25</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J14" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="K14" s="1" t="s">
         <v>615</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -4316,10 +4369,10 @@
         <v>83</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>505</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>151</v>
@@ -4334,16 +4387,16 @@
         <v>26</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J15" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="K15" s="1" t="s">
         <v>615</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -4351,10 +4404,10 @@
         <v>87</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>509</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>510</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>153</v>
@@ -4369,16 +4422,16 @@
         <v>27</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -4386,10 +4439,10 @@
         <v>73</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>479</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>480</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>144</v>
@@ -4404,16 +4457,16 @@
         <v>21</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J17" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="K17" s="1" t="s">
         <v>611</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -4421,10 +4474,10 @@
         <v>74</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>481</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>482</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>145</v>
@@ -4439,16 +4492,16 @@
         <v>21</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J18" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="K18" s="1" t="s">
         <v>611</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -4456,10 +4509,10 @@
         <v>70</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>472</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>473</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>141</v>
@@ -4474,16 +4527,16 @@
         <v>19</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J19" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="K19" s="1" t="s">
         <v>611</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -4491,10 +4544,10 @@
         <v>72</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>477</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>478</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>143</v>
@@ -4509,16 +4562,16 @@
         <v>20</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J20" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="K20" s="1" t="s">
         <v>611</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -4526,10 +4579,10 @@
         <v>71</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>475</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>476</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>142</v>
@@ -4544,16 +4597,16 @@
         <v>20</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J21" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="K21" s="1" t="s">
         <v>611</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -4573,22 +4626,22 @@
         <v>273</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>274</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -4599,7 +4652,7 @@
         <v>258</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>259</v>
@@ -4608,27 +4661,27 @@
         <v>260</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>261</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>294</v>
@@ -4643,22 +4696,22 @@
         <v>297</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>298</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -4678,27 +4731,27 @@
         <v>278</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>279</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>299</v>
@@ -4713,33 +4766,33 @@
         <v>297</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>302</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>283</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>280</v>
@@ -4748,27 +4801,27 @@
         <v>281</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>282</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>284</v>
@@ -4783,22 +4836,22 @@
         <v>273</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>285</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -4818,27 +4871,27 @@
         <v>265</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>266</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>291</v>
@@ -4853,27 +4906,27 @@
         <v>273</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>292</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>286</v>
@@ -4888,22 +4941,22 @@
         <v>273</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>287</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -4914,28 +4967,28 @@
         <v>267</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>268</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>269</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -4943,10 +4996,10 @@
         <v>79</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>492</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>493</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>135</v>
@@ -4961,16 +5014,16 @@
         <v>12</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -4978,16 +5031,16 @@
         <v>80</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>495</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>496</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>135</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>362</v>
@@ -4996,16 +5049,16 @@
         <v>12</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -5013,16 +5066,16 @@
         <v>81</v>
       </c>
       <c r="B35" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>499</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>135</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>363</v>
@@ -5031,16 +5084,16 @@
         <v>12</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -5048,10 +5101,10 @@
         <v>109</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>550</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>551</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>135</v>
@@ -5066,16 +5119,16 @@
         <v>12</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="I36" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="J36" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="J36" s="1" t="s">
-        <v>601</v>
-      </c>
       <c r="K36" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -5083,10 +5136,10 @@
         <v>103</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>163</v>
@@ -5101,16 +5154,16 @@
         <v>37</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="I37" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="J37" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="J37" s="1" t="s">
-        <v>601</v>
-      </c>
       <c r="K37" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -5118,10 +5171,10 @@
         <v>104</v>
       </c>
       <c r="B38" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>542</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>543</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>164</v>
@@ -5136,16 +5189,16 @@
         <v>38</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="I38" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="J38" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="J38" s="1" t="s">
-        <v>601</v>
-      </c>
       <c r="K38" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -5153,10 +5206,10 @@
         <v>101</v>
       </c>
       <c r="B39" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>537</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>538</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>162</v>
@@ -5171,16 +5224,16 @@
         <v>35</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="I39" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="J39" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="J39" s="1" t="s">
-        <v>601</v>
-      </c>
       <c r="K39" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -5200,22 +5253,22 @@
         <v>239</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>240</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -5223,10 +5276,10 @@
         <v>50</v>
       </c>
       <c r="B41" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>431</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>432</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>125</v>
@@ -5241,16 +5294,16 @@
         <v>9</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -5258,16 +5311,16 @@
         <v>251</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D42" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>667</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>668</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>346</v>
@@ -5276,16 +5329,16 @@
         <v>9</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -5293,10 +5346,10 @@
         <v>51</v>
       </c>
       <c r="B43" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>434</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>435</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>126</v>
@@ -5311,16 +5364,16 @@
         <v>9</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -5328,10 +5381,10 @@
         <v>52</v>
       </c>
       <c r="B44" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>436</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>437</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>127</v>
@@ -5346,16 +5399,16 @@
         <v>9</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -5363,10 +5416,10 @@
         <v>53</v>
       </c>
       <c r="B45" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>438</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>439</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>128</v>
@@ -5381,16 +5434,16 @@
         <v>9</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -5398,10 +5451,10 @@
         <v>54</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>129</v>
@@ -5410,22 +5463,22 @@
         <v>181</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -5433,34 +5486,34 @@
         <v>55</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>130</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -5468,10 +5521,10 @@
         <v>107</v>
       </c>
       <c r="B48" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>548</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>549</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>167</v>
@@ -5486,16 +5539,16 @@
         <v>12</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="I48" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="J48" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="J48" s="1" t="s">
-        <v>601</v>
-      </c>
       <c r="K48" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -5506,7 +5559,7 @@
         <v>332</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>333</v>
@@ -5521,16 +5574,16 @@
         <v>335</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="I49" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="J49" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="J49" s="1" t="s">
-        <v>601</v>
-      </c>
       <c r="K49" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -5538,10 +5591,10 @@
         <v>106</v>
       </c>
       <c r="B50" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>546</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>547</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>166</v>
@@ -5556,16 +5609,16 @@
         <v>39</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="I50" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="J50" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="J50" s="1" t="s">
-        <v>601</v>
-      </c>
       <c r="K50" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -5573,10 +5626,10 @@
         <v>75</v>
       </c>
       <c r="B51" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>483</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>484</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>146</v>
@@ -5591,16 +5644,16 @@
         <v>22</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="I51" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="J51" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="J51" s="1" t="s">
-        <v>601</v>
-      </c>
       <c r="K51" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -5608,10 +5661,10 @@
         <v>76</v>
       </c>
       <c r="B52" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>486</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>487</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>147</v>
@@ -5626,16 +5679,16 @@
         <v>22</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="I52" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="J52" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="J52" s="1" t="s">
-        <v>601</v>
-      </c>
       <c r="K52" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -5643,10 +5696,10 @@
         <v>78</v>
       </c>
       <c r="B53" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="C53" s="1" t="s">
         <v>490</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>491</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>149</v>
@@ -5661,16 +5714,16 @@
         <v>24</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="I53" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="J53" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="J53" s="1" t="s">
-        <v>601</v>
-      </c>
       <c r="K53" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -5678,10 +5731,10 @@
         <v>77</v>
       </c>
       <c r="B54" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="C54" s="1" t="s">
         <v>488</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>489</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>148</v>
@@ -5690,57 +5743,57 @@
         <v>192</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>23</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="I54" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="J54" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="J54" s="1" t="s">
-        <v>601</v>
-      </c>
       <c r="K54" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="55" spans="1:11">
       <c r="A55" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>698</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="C55" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="D55" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="E55" s="1" t="s">
         <v>701</v>
       </c>
-      <c r="E55" s="1" t="s">
+      <c r="F55" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="G55" s="7" t="s">
         <v>702</v>
       </c>
-      <c r="F55" s="1" t="s">
-        <v>705</v>
-      </c>
-      <c r="G55" s="7" t="s">
-        <v>703</v>
-      </c>
       <c r="H55" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="I55" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="J55" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="J55" s="1" t="s">
-        <v>601</v>
-      </c>
       <c r="K55" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -5748,10 +5801,10 @@
         <v>59</v>
       </c>
       <c r="B56" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>449</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>450</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>134</v>
@@ -5766,16 +5819,16 @@
         <v>13</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I56" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="J56" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="J56" s="1" t="s">
-        <v>601</v>
-      </c>
       <c r="K56" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -5783,10 +5836,10 @@
         <v>60</v>
       </c>
       <c r="B57" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>451</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>452</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>134</v>
@@ -5801,16 +5854,16 @@
         <v>13</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I57" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="J57" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="J57" s="1" t="s">
-        <v>601</v>
-      </c>
       <c r="K57" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -5818,16 +5871,16 @@
         <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C58" s="1" t="s">
         <v>444</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>445</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>132</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>348</v>
@@ -5836,16 +5889,16 @@
         <v>11</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I58" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="J58" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="J58" s="1" t="s">
-        <v>601</v>
-      </c>
       <c r="K58" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -5853,10 +5906,10 @@
         <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="C59" s="1" t="s">
         <v>447</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>448</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>133</v>
@@ -5871,16 +5924,16 @@
         <v>12</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I59" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="J59" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="J59" s="1" t="s">
-        <v>601</v>
-      </c>
       <c r="K59" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -5888,10 +5941,10 @@
         <v>56</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>131</v>
@@ -5906,16 +5959,16 @@
         <v>10</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I60" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="J60" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="J60" s="1" t="s">
-        <v>601</v>
-      </c>
       <c r="K60" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -5923,10 +5976,10 @@
         <v>102</v>
       </c>
       <c r="B61" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="C61" s="1" t="s">
         <v>539</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>540</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>163</v>
@@ -5941,16 +5994,16 @@
         <v>36</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="I61" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="J61" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="J61" s="1" t="s">
-        <v>601</v>
-      </c>
       <c r="K61" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -5958,10 +6011,10 @@
         <v>98</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>160</v>
@@ -5976,16 +6029,16 @@
         <v>33</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="I62" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="J62" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="J62" s="1" t="s">
-        <v>601</v>
-      </c>
       <c r="K62" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -5993,10 +6046,10 @@
         <v>46</v>
       </c>
       <c r="B63" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>421</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>422</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>121</v>
@@ -6011,16 +6064,16 @@
         <v>5</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="I63" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="J63" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="J63" s="1" t="s">
-        <v>601</v>
-      </c>
       <c r="K63" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -6028,10 +6081,10 @@
         <v>45</v>
       </c>
       <c r="B64" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>418</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>419</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>120</v>
@@ -6046,16 +6099,16 @@
         <v>4</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="I64" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="J64" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="J64" s="1" t="s">
+      <c r="K64" s="1" t="s">
         <v>601</v>
-      </c>
-      <c r="K64" s="1" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -6063,10 +6116,10 @@
         <v>47</v>
       </c>
       <c r="B65" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C65" s="1" t="s">
         <v>424</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>425</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>122</v>
@@ -6081,27 +6134,27 @@
         <v>6</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="I65" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="J65" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="J65" s="1" t="s">
+      <c r="K65" s="1" t="s">
         <v>601</v>
-      </c>
-      <c r="K65" s="1" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="66" spans="1:11">
       <c r="A66" s="1" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B66" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>559</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>560</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>172</v>
@@ -6116,16 +6169,16 @@
         <v>43</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="I66" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="J66" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="J66" s="1" t="s">
+      <c r="K66" s="1" t="s">
         <v>601</v>
-      </c>
-      <c r="K66" s="1" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -6133,16 +6186,16 @@
         <v>48</v>
       </c>
       <c r="B67" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="C67" s="1" t="s">
         <v>426</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>427</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>123</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>344</v>
@@ -6151,16 +6204,16 @@
         <v>7</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="I67" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="J67" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="J67" s="1" t="s">
+      <c r="K67" s="1" t="s">
         <v>601</v>
-      </c>
-      <c r="K67" s="1" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -6168,16 +6221,16 @@
         <v>49</v>
       </c>
       <c r="B68" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C68" s="1" t="s">
         <v>429</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>430</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>124</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>345</v>
@@ -6186,16 +6239,16 @@
         <v>8</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="I68" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="J68" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="J68" s="1" t="s">
+      <c r="K68" s="1" t="s">
         <v>601</v>
-      </c>
-      <c r="K68" s="1" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -6203,10 +6256,10 @@
         <v>114</v>
       </c>
       <c r="B69" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="C69" s="1" t="s">
         <v>557</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>558</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>171</v>
@@ -6221,16 +6274,16 @@
         <v>42</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="I69" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="J69" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="J69" s="1" t="s">
+      <c r="K69" s="1" t="s">
         <v>601</v>
-      </c>
-      <c r="K69" s="1" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -6238,10 +6291,10 @@
         <v>113</v>
       </c>
       <c r="B70" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="C70" s="1" t="s">
         <v>555</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>556</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>170</v>
@@ -6256,16 +6309,16 @@
         <v>41</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="I70" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="J70" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="J70" s="1" t="s">
+      <c r="K70" s="1" t="s">
         <v>601</v>
-      </c>
-      <c r="K70" s="1" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -6273,10 +6326,10 @@
         <v>69</v>
       </c>
       <c r="B71" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="C71" s="1" t="s">
         <v>470</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>471</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>140</v>
@@ -6291,16 +6344,16 @@
         <v>18</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -6308,10 +6361,10 @@
         <v>68</v>
       </c>
       <c r="B72" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="C72" s="1" t="s">
         <v>468</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>469</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>139</v>
@@ -6326,16 +6379,16 @@
         <v>17</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -6343,10 +6396,10 @@
         <v>65</v>
       </c>
       <c r="B73" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="C73" s="1" t="s">
         <v>461</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>462</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>136</v>
@@ -6361,16 +6414,16 @@
         <v>14</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J73" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="K73" s="1" t="s">
         <v>608</v>
-      </c>
-      <c r="K73" s="1" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -6378,10 +6431,10 @@
         <v>66</v>
       </c>
       <c r="B74" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="C74" s="1" t="s">
         <v>464</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>465</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>137</v>
@@ -6396,16 +6449,16 @@
         <v>15</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J74" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="K74" s="1" t="s">
         <v>608</v>
-      </c>
-      <c r="K74" s="1" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -6413,10 +6466,10 @@
         <v>67</v>
       </c>
       <c r="B75" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C75" s="1" t="s">
         <v>466</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>467</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>138</v>
@@ -6431,16 +6484,16 @@
         <v>16</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J75" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="K75" s="1" t="s">
         <v>608</v>
-      </c>
-      <c r="K75" s="1" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -6448,10 +6501,10 @@
         <v>99</v>
       </c>
       <c r="B76" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C76" s="1" t="s">
         <v>531</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>532</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>135</v>
@@ -6466,16 +6519,16 @@
         <v>12</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="I76" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="J76" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="J76" s="1" t="s">
+      <c r="K76" s="1" t="s">
         <v>624</v>
-      </c>
-      <c r="K76" s="1" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -6486,7 +6539,7 @@
         <v>328</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>329</v>
@@ -6501,16 +6554,16 @@
         <v>331</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="I77" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="J77" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="J77" s="1" t="s">
-        <v>624</v>
-      </c>
       <c r="K77" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -6518,10 +6571,10 @@
         <v>105</v>
       </c>
       <c r="B78" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="C78" s="1" t="s">
         <v>544</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>545</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>165</v>
@@ -6536,16 +6589,16 @@
         <v>12</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="I78" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="J78" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="J78" s="1" t="s">
+      <c r="K78" s="1" t="s">
         <v>630</v>
-      </c>
-      <c r="K78" s="1" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -6553,10 +6606,10 @@
         <v>242</v>
       </c>
       <c r="B79" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="C79" s="1" t="s">
         <v>575</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>576</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>338</v>
@@ -6565,22 +6618,22 @@
         <v>339</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G79" s="5" t="s">
         <v>340</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="I79" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="J79" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="J79" s="1" t="s">
-        <v>630</v>
-      </c>
       <c r="K79" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -6591,7 +6644,7 @@
         <v>217</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>219</v>
@@ -6600,33 +6653,33 @@
         <v>221</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G80" s="4" t="s">
         <v>218</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="I80" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="J80" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="J80" s="1" t="s">
-        <v>630</v>
-      </c>
       <c r="K80" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="81" spans="1:11">
       <c r="A81" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>215</v>
@@ -6635,22 +6688,22 @@
         <v>216</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>214</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="I81" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="J81" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="J81" s="1" t="s">
-        <v>630</v>
-      </c>
       <c r="K81" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -6661,31 +6714,31 @@
         <v>224</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D82" s="6" t="s">
         <v>220</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="G82" s="4" t="s">
         <v>213</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="I82" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="J82" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="J82" s="1" t="s">
-        <v>630</v>
-      </c>
       <c r="K82" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -6693,32 +6746,32 @@
         <v>235</v>
       </c>
       <c r="B83" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C83" s="4" t="s">
         <v>670</v>
       </c>
-      <c r="C83" s="4" t="s">
+      <c r="D83" s="6" t="s">
         <v>671</v>
-      </c>
-      <c r="D83" s="6" t="s">
-        <v>672</v>
       </c>
       <c r="E83" s="6"/>
       <c r="F83" s="4" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="G83" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="I83" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="J83" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="J83" s="1" t="s">
-        <v>630</v>
-      </c>
       <c r="K83" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -6726,34 +6779,34 @@
         <v>242</v>
       </c>
       <c r="B84" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="C84" s="4" t="s">
         <v>676</v>
       </c>
-      <c r="C84" s="4" t="s">
+      <c r="D84" s="6" t="s">
         <v>677</v>
       </c>
-      <c r="D84" s="6" t="s">
+      <c r="E84" s="6" t="s">
         <v>678</v>
       </c>
-      <c r="E84" s="6" t="s">
+      <c r="F84" s="4" t="s">
         <v>679</v>
       </c>
-      <c r="F84" s="4" t="s">
-        <v>680</v>
-      </c>
       <c r="G84" s="8" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="I84" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="J84" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="J84" s="1" t="s">
-        <v>630</v>
-      </c>
       <c r="K84" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="85" spans="1:11" ht="34">
@@ -6761,34 +6814,34 @@
         <v>247</v>
       </c>
       <c r="B85" s="4" t="s">
+        <v>682</v>
+      </c>
+      <c r="C85" s="4" t="s">
         <v>683</v>
       </c>
-      <c r="C85" s="4" t="s">
+      <c r="D85" s="9" t="s">
+        <v>681</v>
+      </c>
+      <c r="E85" s="6" t="s">
         <v>684</v>
       </c>
-      <c r="D85" s="9" t="s">
-        <v>682</v>
-      </c>
-      <c r="E85" s="6" t="s">
+      <c r="F85" s="4" t="s">
         <v>685</v>
       </c>
-      <c r="F85" s="4" t="s">
-        <v>686</v>
-      </c>
       <c r="G85" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="I85" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="J85" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="J85" s="1" t="s">
-        <v>630</v>
-      </c>
       <c r="K85" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -6796,34 +6849,34 @@
         <v>248</v>
       </c>
       <c r="B86" s="4" t="s">
+        <v>687</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>689</v>
+      </c>
+      <c r="E86" s="6" t="s">
+        <v>678</v>
+      </c>
+      <c r="F86" s="4" t="s">
         <v>688</v>
       </c>
-      <c r="C86" s="4" t="s">
-        <v>691</v>
-      </c>
-      <c r="D86" s="6" t="s">
-        <v>690</v>
-      </c>
-      <c r="E86" s="6" t="s">
-        <v>679</v>
-      </c>
-      <c r="F86" s="4" t="s">
-        <v>689</v>
-      </c>
       <c r="G86" s="8" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="I86" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="J86" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="J86" s="1" t="s">
-        <v>630</v>
-      </c>
       <c r="K86" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -6831,34 +6884,34 @@
         <v>249</v>
       </c>
       <c r="B87" s="4" t="s">
+        <v>692</v>
+      </c>
+      <c r="C87" s="4" t="s">
         <v>693</v>
       </c>
-      <c r="C87" s="4" t="s">
+      <c r="D87" s="6" t="s">
         <v>694</v>
       </c>
-      <c r="D87" s="6" t="s">
+      <c r="E87" s="6" t="s">
+        <v>696</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>691</v>
+      </c>
+      <c r="G87" s="8" t="s">
         <v>695</v>
       </c>
-      <c r="E87" s="6" t="s">
-        <v>697</v>
-      </c>
-      <c r="F87" s="4" t="s">
-        <v>692</v>
-      </c>
-      <c r="G87" s="8" t="s">
-        <v>696</v>
-      </c>
       <c r="H87" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="I87" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="J87" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="J87" s="1" t="s">
-        <v>630</v>
-      </c>
       <c r="K87" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="88" spans="1:11">
@@ -6866,34 +6919,34 @@
         <v>222</v>
       </c>
       <c r="B88" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="C88" s="1" t="s">
         <v>565</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>566</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>210</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G88" s="1" t="s">
         <v>211</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="I88" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="J88" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="J88" s="1" t="s">
-        <v>630</v>
-      </c>
       <c r="K88" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="89" spans="1:11">
@@ -6901,30 +6954,30 @@
         <v>223</v>
       </c>
       <c r="B89" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="C89" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="C89" s="1" t="s">
-        <v>570</v>
-      </c>
       <c r="F89" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="I89" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="J89" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="J89" s="1" t="s">
-        <v>630</v>
-      </c>
       <c r="K89" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="90" spans="1:11">
       <c r="A90" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>323</v>
@@ -6939,7 +6992,7 @@
         <v>325</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>324</v>
@@ -6948,18 +7001,18 @@
         <v>307</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J90" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="K90" s="1" t="s">
         <v>638</v>
-      </c>
-      <c r="K90" s="1" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="91" spans="1:11">
       <c r="A91" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>308</v>
@@ -6974,7 +7027,7 @@
         <v>311</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>312</v>
@@ -6983,18 +7036,18 @@
         <v>307</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J91" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="K91" s="1" t="s">
         <v>638</v>
-      </c>
-      <c r="K91" s="1" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="92" spans="1:11">
       <c r="A92" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>313</v>
@@ -7009,7 +7062,7 @@
         <v>316</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>317</v>
@@ -7018,18 +7071,18 @@
         <v>307</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J92" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="K92" s="1" t="s">
         <v>638</v>
-      </c>
-      <c r="K92" s="1" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="34">
       <c r="A93" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>319</v>
@@ -7044,7 +7097,7 @@
         <v>322</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>318</v>
@@ -7053,13 +7106,13 @@
         <v>307</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J93" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="K93" s="1" t="s">
         <v>638</v>
-      </c>
-      <c r="K93" s="1" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="94" spans="1:11">
@@ -7070,1118 +7123,1223 @@
         <v>116</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>209</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>208</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="95" spans="1:11">
       <c r="A95" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>115</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>387</v>
+        <v>826</v>
       </c>
       <c r="G95" s="1" t="s">
         <v>117</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="96" spans="1:11">
       <c r="A96" s="1" t="s">
-        <v>706</v>
+        <v>820</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>709</v>
+        <v>821</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>710</v>
+        <v>823</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>711</v>
+        <v>824</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>244</v>
+        <v>825</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>713</v>
+        <v>827</v>
       </c>
       <c r="G96" s="7" t="s">
-        <v>712</v>
+        <v>828</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>708</v>
+        <v>561</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>707</v>
+        <v>634</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>708</v>
+        <v>819</v>
       </c>
     </row>
     <row r="97" spans="1:11">
       <c r="A97" s="1" t="s">
-        <v>90</v>
+        <v>822</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>652</v>
+        <v>829</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>515</v>
+        <v>830</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>135</v>
+        <v>831</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>135</v>
+        <v>832</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>654</v>
-      </c>
-      <c r="G97" s="1" t="s">
-        <v>12</v>
+        <v>833</v>
+      </c>
+      <c r="G97" s="7" t="s">
+        <v>834</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>516</v>
+        <v>561</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>614</v>
+        <v>628</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>619</v>
+        <v>634</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>620</v>
+        <v>819</v>
       </c>
     </row>
     <row r="98" spans="1:11">
       <c r="A98" s="1" t="s">
-        <v>91</v>
+        <v>705</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>517</v>
+        <v>708</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>518</v>
+        <v>709</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>135</v>
+        <v>710</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>199</v>
+        <v>244</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>646</v>
-      </c>
-      <c r="G98" s="1" t="s">
-        <v>12</v>
+        <v>712</v>
+      </c>
+      <c r="G98" s="7" t="s">
+        <v>711</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>516</v>
+        <v>707</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>614</v>
+        <v>628</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>619</v>
+        <v>706</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>620</v>
+        <v>707</v>
       </c>
     </row>
     <row r="99" spans="1:11">
       <c r="A99" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>526</v>
+        <v>651</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>527</v>
+        <v>514</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>135</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>201</v>
+        <v>135</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>522</v>
+        <v>12</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="J99" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="K99" s="1" t="s">
         <v>619</v>
-      </c>
-      <c r="K99" s="1" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="100" spans="1:11">
       <c r="A100" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>653</v>
+        <v>645</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="J100" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="K100" s="1" t="s">
         <v>619</v>
-      </c>
-      <c r="K100" s="1" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="101" spans="1:11">
       <c r="A101" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>30</v>
+        <v>525</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>368</v>
+        <v>645</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>31</v>
+        <v>521</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="J101" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="K101" s="1" t="s">
         <v>619</v>
-      </c>
-      <c r="K101" s="1" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="102" spans="1:11">
       <c r="A102" s="1" t="s">
-        <v>252</v>
+        <v>92</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>243</v>
+        <v>518</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>580</v>
+        <v>519</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>246</v>
+        <v>156</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>244</v>
+        <v>200</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="G102" s="2" t="s">
-        <v>245</v>
+        <v>652</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="J102" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="K102" s="1" t="s">
         <v>619</v>
-      </c>
-      <c r="K102" s="1" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="103" spans="1:11">
       <c r="A103" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>523</v>
+        <v>30</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>524</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>646</v>
+        <v>368</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>522</v>
+        <v>31</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="J103" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="K103" s="1" t="s">
         <v>619</v>
-      </c>
-      <c r="K103" s="1" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="104" spans="1:11">
       <c r="A104" s="1" t="s">
-        <v>93</v>
+        <v>252</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>655</v>
+        <v>243</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>521</v>
+        <v>579</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>135</v>
+        <v>246</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>135</v>
+        <v>244</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>646</v>
-      </c>
-      <c r="G104" s="1" t="s">
-        <v>522</v>
+        <v>396</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="J104" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="K104" s="1" t="s">
         <v>619</v>
-      </c>
-      <c r="K104" s="1" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="105" spans="1:11">
       <c r="A105" s="1" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>534</v>
+        <v>522</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>535</v>
+        <v>523</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>536</v>
+        <v>135</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>372</v>
+        <v>645</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>34</v>
+        <v>521</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>533</v>
+        <v>515</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="J105" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="K105" s="1" t="s">
         <v>619</v>
-      </c>
-      <c r="K105" s="1" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="106" spans="1:11">
       <c r="A106" s="1" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>552</v>
+        <v>654</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>553</v>
+        <v>520</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>168</v>
+        <v>135</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>206</v>
+        <v>135</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>661</v>
+        <v>645</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>40</v>
+        <v>521</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>533</v>
+        <v>515</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="J106" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="K106" s="1" t="s">
         <v>619</v>
-      </c>
-      <c r="K106" s="1" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="107" spans="1:11">
       <c r="A107" s="1" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>554</v>
+        <v>533</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>415</v>
+        <v>534</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>135</v>
+        <v>535</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>522</v>
+        <v>34</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="J107" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>633</v>
+        <v>621</v>
       </c>
     </row>
     <row r="108" spans="1:11">
       <c r="A108" s="1" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>528</v>
+        <v>551</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>529</v>
+        <v>552</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>369</v>
+        <v>660</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>423</v>
+        <v>532</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="J108" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="K108" s="1" t="s">
-        <v>621</v>
+        <v>632</v>
       </c>
     </row>
     <row r="109" spans="1:11">
       <c r="A109" s="1" t="s">
-        <v>660</v>
+        <v>111</v>
       </c>
       <c r="B109" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="H109" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="I109" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="J109" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="K109" s="1" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11">
+      <c r="A110" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H110" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="I110" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="J110" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="K110" s="1" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11">
+      <c r="A111" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="C111" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="C109" s="1" t="s">
+      <c r="D111" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="D109" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="F109" s="1" t="s">
+      <c r="F111" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="G111" s="7" t="s">
         <v>662</v>
       </c>
-      <c r="G109" s="7" t="s">
-        <v>663</v>
-      </c>
-      <c r="H109" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="I109" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="J109" s="1" t="s">
-        <v>606</v>
-      </c>
-      <c r="K109" s="1" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="110" spans="1:11" ht="17">
-      <c r="A110" s="10" t="s">
-        <v>717</v>
-      </c>
-      <c r="B110" s="11" t="s">
-        <v>718</v>
-      </c>
-      <c r="C110" s="12" t="s">
-        <v>719</v>
-      </c>
-      <c r="D110" s="11" t="s">
-        <v>720</v>
-      </c>
-      <c r="E110" s="13" t="s">
-        <v>721</v>
-      </c>
-      <c r="F110" s="11" t="s">
-        <v>722</v>
-      </c>
-      <c r="G110" s="14" t="s">
-        <v>723</v>
-      </c>
-      <c r="H110" s="1" t="s">
-        <v>716</v>
-      </c>
-      <c r="I110" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="J110" s="1" t="s">
-        <v>714</v>
-      </c>
-      <c r="K110" s="1" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="111" spans="1:11" ht="17">
-      <c r="A111" s="10" t="s">
-        <v>724</v>
-      </c>
-      <c r="B111" s="11" t="s">
-        <v>725</v>
-      </c>
-      <c r="C111" s="12" t="s">
-        <v>726</v>
-      </c>
-      <c r="D111" s="11" t="s">
-        <v>727</v>
-      </c>
-      <c r="E111" s="13" t="s">
-        <v>721</v>
-      </c>
-      <c r="F111" s="11" t="s">
-        <v>728</v>
-      </c>
-      <c r="G111" s="14" t="s">
-        <v>729</v>
-      </c>
       <c r="H111" s="1" t="s">
-        <v>716</v>
+        <v>432</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>629</v>
+        <v>599</v>
       </c>
       <c r="J111" s="1" t="s">
-        <v>714</v>
+        <v>605</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>715</v>
+        <v>603</v>
       </c>
     </row>
     <row r="112" spans="1:11" ht="17">
       <c r="A112" s="10" t="s">
-        <v>730</v>
+        <v>716</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>731</v>
+        <v>717</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>732</v>
+        <v>718</v>
       </c>
       <c r="D112" s="11" t="s">
-        <v>733</v>
+        <v>719</v>
       </c>
       <c r="E112" s="13" t="s">
+        <v>720</v>
+      </c>
+      <c r="F112" s="11" t="s">
         <v>721</v>
       </c>
-      <c r="F112" s="11" t="s">
-        <v>734</v>
-      </c>
       <c r="G112" s="14" t="s">
-        <v>735</v>
+        <v>722</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J112" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="K112" s="1" t="s">
         <v>714</v>
-      </c>
-      <c r="K112" s="1" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="113" spans="1:11" ht="17">
       <c r="A113" s="10" t="s">
-        <v>736</v>
-      </c>
-      <c r="B113" s="11" t="s">
-        <v>737</v>
-      </c>
-      <c r="C113" s="12" t="s">
-        <v>738</v>
+        <v>723</v>
+      </c>
+      <c r="B113" s="15" t="s">
+        <v>812</v>
+      </c>
+      <c r="C113" s="15" t="s">
+        <v>811</v>
       </c>
       <c r="D113" s="11" t="s">
-        <v>739</v>
+        <v>813</v>
       </c>
       <c r="E113" s="13" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="F113" s="11" t="s">
-        <v>740</v>
+        <v>724</v>
       </c>
       <c r="G113" s="14" t="s">
-        <v>741</v>
+        <v>725</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J113" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="K113" s="1" t="s">
         <v>714</v>
-      </c>
-      <c r="K113" s="1" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="114" spans="1:11" ht="17">
       <c r="A114" s="10" t="s">
-        <v>742</v>
+        <v>726</v>
       </c>
       <c r="B114" s="11" t="s">
-        <v>743</v>
+        <v>727</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>744</v>
+        <v>728</v>
       </c>
       <c r="D114" s="11" t="s">
-        <v>745</v>
+        <v>729</v>
       </c>
       <c r="E114" s="13" t="s">
-        <v>746</v>
+        <v>720</v>
       </c>
       <c r="F114" s="11" t="s">
-        <v>747</v>
+        <v>730</v>
       </c>
       <c r="G114" s="14" t="s">
-        <v>748</v>
+        <v>731</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J114" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="K114" s="1" t="s">
         <v>714</v>
-      </c>
-      <c r="K114" s="1" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="115" spans="1:11" ht="17">
       <c r="A115" s="10" t="s">
-        <v>749</v>
+        <v>732</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>750</v>
+        <v>733</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>751</v>
+        <v>734</v>
       </c>
       <c r="D115" s="11" t="s">
-        <v>752</v>
+        <v>735</v>
       </c>
       <c r="E115" s="13" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="F115" s="11" t="s">
-        <v>753</v>
+        <v>736</v>
       </c>
       <c r="G115" s="14" t="s">
-        <v>754</v>
+        <v>737</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J115" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="K115" s="1" t="s">
         <v>714</v>
-      </c>
-      <c r="K115" s="1" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="116" spans="1:11" ht="17">
       <c r="A116" s="10" t="s">
-        <v>755</v>
+        <v>738</v>
       </c>
       <c r="B116" s="11" t="s">
-        <v>756</v>
+        <v>739</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>757</v>
+        <v>740</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>758</v>
+        <v>741</v>
       </c>
       <c r="E116" s="13" t="s">
-        <v>721</v>
+        <v>742</v>
       </c>
       <c r="F116" s="11" t="s">
-        <v>759</v>
+        <v>743</v>
       </c>
       <c r="G116" s="14" t="s">
-        <v>760</v>
+        <v>744</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J116" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="K116" s="1" t="s">
         <v>714</v>
-      </c>
-      <c r="K116" s="1" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="117" spans="1:11" ht="17">
       <c r="A117" s="10" t="s">
-        <v>761</v>
+        <v>745</v>
       </c>
       <c r="B117" s="11" t="s">
-        <v>762</v>
+        <v>746</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>763</v>
+        <v>747</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>764</v>
+        <v>748</v>
       </c>
       <c r="E117" s="13" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="F117" s="11" t="s">
-        <v>765</v>
+        <v>749</v>
       </c>
       <c r="G117" s="14" t="s">
-        <v>766</v>
+        <v>750</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J117" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="K117" s="1" t="s">
         <v>714</v>
-      </c>
-      <c r="K117" s="1" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="118" spans="1:11" ht="17">
       <c r="A118" s="10" t="s">
-        <v>767</v>
+        <v>751</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>768</v>
+        <v>752</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>769</v>
+        <v>753</v>
       </c>
       <c r="D118" s="11" t="s">
-        <v>770</v>
+        <v>754</v>
       </c>
       <c r="E118" s="13" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="F118" s="11" t="s">
-        <v>771</v>
+        <v>755</v>
       </c>
       <c r="G118" s="14" t="s">
-        <v>772</v>
+        <v>756</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J118" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="K118" s="1" t="s">
         <v>714</v>
-      </c>
-      <c r="K118" s="1" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="119" spans="1:11" ht="17">
       <c r="A119" s="10" t="s">
-        <v>773</v>
+        <v>757</v>
       </c>
       <c r="B119" s="11" t="s">
-        <v>774</v>
+        <v>758</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>775</v>
+        <v>759</v>
       </c>
       <c r="D119" s="11" t="s">
-        <v>776</v>
+        <v>760</v>
       </c>
       <c r="E119" s="13" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="F119" s="11" t="s">
-        <v>777</v>
+        <v>761</v>
       </c>
       <c r="G119" s="14" t="s">
-        <v>778</v>
+        <v>762</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J119" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="K119" s="1" t="s">
         <v>714</v>
-      </c>
-      <c r="K119" s="1" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="120" spans="1:11" ht="17">
       <c r="A120" s="10" t="s">
-        <v>779</v>
+        <v>763</v>
       </c>
       <c r="B120" s="11" t="s">
-        <v>780</v>
+        <v>764</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>781</v>
+        <v>765</v>
       </c>
       <c r="D120" s="11" t="s">
-        <v>782</v>
+        <v>766</v>
       </c>
       <c r="E120" s="13" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="F120" s="11" t="s">
-        <v>783</v>
+        <v>767</v>
       </c>
       <c r="G120" s="14" t="s">
-        <v>784</v>
+        <v>768</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J120" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="K120" s="1" t="s">
         <v>714</v>
-      </c>
-      <c r="K120" s="1" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="121" spans="1:11" ht="17">
       <c r="A121" s="10" t="s">
-        <v>785</v>
+        <v>769</v>
       </c>
       <c r="B121" s="11" t="s">
-        <v>786</v>
+        <v>770</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>787</v>
+        <v>771</v>
       </c>
       <c r="D121" s="11" t="s">
-        <v>788</v>
+        <v>772</v>
       </c>
       <c r="E121" s="13" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="F121" s="11" t="s">
-        <v>789</v>
+        <v>773</v>
       </c>
       <c r="G121" s="14" t="s">
-        <v>790</v>
+        <v>774</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J121" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="K121" s="1" t="s">
         <v>714</v>
-      </c>
-      <c r="K121" s="1" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="122" spans="1:11" ht="17">
       <c r="A122" s="10" t="s">
-        <v>791</v>
+        <v>775</v>
       </c>
       <c r="B122" s="11" t="s">
-        <v>792</v>
+        <v>776</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>793</v>
+        <v>777</v>
       </c>
       <c r="D122" s="11" t="s">
-        <v>794</v>
+        <v>778</v>
       </c>
       <c r="E122" s="13" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="F122" s="11" t="s">
-        <v>795</v>
+        <v>779</v>
       </c>
       <c r="G122" s="14" t="s">
-        <v>796</v>
+        <v>780</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="I122" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J122" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="K122" s="1" t="s">
         <v>714</v>
-      </c>
-      <c r="K122" s="1" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="123" spans="1:11" ht="17">
       <c r="A123" s="10" t="s">
-        <v>797</v>
+        <v>781</v>
       </c>
       <c r="B123" s="11" t="s">
-        <v>798</v>
+        <v>782</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>799</v>
+        <v>783</v>
       </c>
       <c r="D123" s="11" t="s">
-        <v>800</v>
+        <v>784</v>
       </c>
       <c r="E123" s="13" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="F123" s="11" t="s">
-        <v>801</v>
+        <v>785</v>
       </c>
       <c r="G123" s="14" t="s">
-        <v>802</v>
+        <v>786</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="I123" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J123" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="K123" s="1" t="s">
         <v>714</v>
-      </c>
-      <c r="K123" s="1" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="124" spans="1:11" ht="17">
       <c r="A124" s="10" t="s">
-        <v>803</v>
+        <v>787</v>
       </c>
       <c r="B124" s="11" t="s">
-        <v>804</v>
+        <v>788</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>805</v>
+        <v>789</v>
       </c>
       <c r="D124" s="11" t="s">
-        <v>806</v>
+        <v>790</v>
       </c>
       <c r="E124" s="13" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="F124" s="11" t="s">
-        <v>807</v>
+        <v>791</v>
       </c>
       <c r="G124" s="14" t="s">
-        <v>808</v>
+        <v>792</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J124" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="K124" s="1" t="s">
         <v>714</v>
-      </c>
-      <c r="K124" s="1" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="125" spans="1:11" ht="17">
       <c r="A125" s="10" t="s">
+        <v>793</v>
+      </c>
+      <c r="B125" s="11" t="s">
+        <v>794</v>
+      </c>
+      <c r="C125" s="12" t="s">
+        <v>795</v>
+      </c>
+      <c r="D125" s="11" t="s">
+        <v>796</v>
+      </c>
+      <c r="E125" s="13" t="s">
+        <v>720</v>
+      </c>
+      <c r="F125" s="11" t="s">
+        <v>797</v>
+      </c>
+      <c r="G125" s="14" t="s">
+        <v>798</v>
+      </c>
+      <c r="H125" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="I125" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="J125" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="K125" s="1" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" ht="17">
+      <c r="A126" s="10" t="s">
+        <v>799</v>
+      </c>
+      <c r="B126" s="11" t="s">
+        <v>800</v>
+      </c>
+      <c r="C126" s="12" t="s">
+        <v>801</v>
+      </c>
+      <c r="D126" s="11" t="s">
+        <v>802</v>
+      </c>
+      <c r="E126" s="13" t="s">
+        <v>720</v>
+      </c>
+      <c r="F126" s="11" t="s">
+        <v>803</v>
+      </c>
+      <c r="G126" s="14" t="s">
+        <v>804</v>
+      </c>
+      <c r="H126" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="I126" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="J126" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="K126" s="1" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" ht="17">
+      <c r="A127" s="10" t="s">
+        <v>805</v>
+      </c>
+      <c r="B127" s="11" t="s">
+        <v>806</v>
+      </c>
+      <c r="C127" s="12" t="s">
+        <v>807</v>
+      </c>
+      <c r="D127" s="11" t="s">
+        <v>808</v>
+      </c>
+      <c r="E127" s="13" t="s">
+        <v>720</v>
+      </c>
+      <c r="F127" s="11" t="s">
         <v>809</v>
       </c>
-      <c r="B125" s="11" t="s">
+      <c r="G127" s="14" t="s">
         <v>810</v>
       </c>
-      <c r="C125" s="12" t="s">
-        <v>811</v>
-      </c>
-      <c r="D125" s="11" t="s">
-        <v>812</v>
-      </c>
-      <c r="E125" s="13" t="s">
-        <v>721</v>
-      </c>
-      <c r="F125" s="11" t="s">
-        <v>813</v>
-      </c>
-      <c r="G125" s="14" t="s">
+      <c r="H127" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="I127" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="J127" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="K127" s="1" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" ht="17">
+      <c r="A128" s="10" t="s">
         <v>814</v>
       </c>
-      <c r="H125" s="1" t="s">
-        <v>716</v>
-      </c>
-      <c r="I125" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="J125" s="1" t="s">
+      <c r="B128" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>816</v>
+      </c>
+      <c r="E128" s="13" t="s">
+        <v>720</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="G128" s="7" t="s">
+        <v>817</v>
+      </c>
+      <c r="H128" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="I128" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="J128" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="K128" s="1" t="s">
         <v>714</v>
       </c>
-      <c r="K125" s="1" t="s">
-        <v>715</v>
-      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K108">
-    <sortCondition ref="J2:J108"/>
-    <sortCondition ref="K2:K108"/>
-    <sortCondition ref="B2:B108"/>
-    <sortCondition ref="C2:C108"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K110">
+    <sortCondition ref="J2:J110"/>
+    <sortCondition ref="K2:K110"/>
+    <sortCondition ref="B2:B110"/>
+    <sortCondition ref="C2:C110"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="2">
@@ -8199,7 +8357,7 @@
     <hyperlink ref="G9" r:id="rId4" xr:uid="{57110EDF-FEA5-304D-BC8D-B61106C21880}"/>
     <hyperlink ref="G40" r:id="rId5" location="sale_active" xr:uid="{730FA5EB-C91B-144D-A783-4D831224B6A9}"/>
     <hyperlink ref="G6" r:id="rId6" xr:uid="{1F8F556A-7472-764F-A198-D7F42EFCC387}"/>
-    <hyperlink ref="G102" r:id="rId7" xr:uid="{D0E463C4-46AF-0146-87CD-46876FB5CA0D}"/>
+    <hyperlink ref="G104" r:id="rId7" xr:uid="{D0E463C4-46AF-0146-87CD-46876FB5CA0D}"/>
     <hyperlink ref="G23" r:id="rId8" xr:uid="{DF8FD8B1-A50B-9E4E-9410-150C09502DAB}"/>
     <hyperlink ref="G29" r:id="rId9" xr:uid="{FF011359-39BB-A040-AED2-D2D90A217A10}"/>
     <hyperlink ref="G32" r:id="rId10" xr:uid="{52BA0BCD-A138-3A42-93E9-9408D0B6CD41}"/>
@@ -8218,29 +8376,32 @@
     <hyperlink ref="G90" r:id="rId23" xr:uid="{40CF7C3F-7CEF-0245-8E88-7892E420529A}"/>
     <hyperlink ref="G77" r:id="rId24" xr:uid="{B2FAD3F1-82CD-564A-89EB-8DE0938B2D53}"/>
     <hyperlink ref="G79" r:id="rId25" xr:uid="{1FE5A63E-4D12-4C4C-A566-E71804C9006E}"/>
-    <hyperlink ref="G109" r:id="rId26" xr:uid="{237E6794-0DAA-2340-869C-73B873A6D324}"/>
+    <hyperlink ref="G111" r:id="rId26" xr:uid="{237E6794-0DAA-2340-869C-73B873A6D324}"/>
     <hyperlink ref="G84" r:id="rId27" xr:uid="{67CF96A7-8792-ED4D-852A-2AD878FBA0A7}"/>
     <hyperlink ref="G85" r:id="rId28" xr:uid="{DDD41264-2363-7B4D-BE34-303C44BC64C2}"/>
     <hyperlink ref="G86" r:id="rId29" xr:uid="{974EC1EA-84B1-4147-9488-B123C8DAB06A}"/>
     <hyperlink ref="G87" r:id="rId30" xr:uid="{76485F94-E942-EF4C-B260-4F0E2DC7AE4C}"/>
     <hyperlink ref="G55" r:id="rId31" xr:uid="{3F9A98AF-B9BE-D742-A02A-E7DAD28A7767}"/>
-    <hyperlink ref="G96" r:id="rId32" xr:uid="{259FD402-6D0D-3E43-9F73-244A8FA24539}"/>
-    <hyperlink ref="G110" r:id="rId33" xr:uid="{BE1E0B79-FD19-9E4A-8C0B-4EFB65F4A3B5}"/>
-    <hyperlink ref="G112" r:id="rId34" xr:uid="{397B14D3-85A6-954F-BE73-1F87B57618F0}"/>
-    <hyperlink ref="G113" r:id="rId35" xr:uid="{2D19773D-B9E1-CC49-A7AC-090ED1865969}"/>
-    <hyperlink ref="G114" r:id="rId36" xr:uid="{E81741AB-74EC-424F-B159-9E36EA9C2AAC}"/>
-    <hyperlink ref="G115" r:id="rId37" xr:uid="{511B6FEA-C9F1-4C40-A21D-F84B63AD6C4C}"/>
-    <hyperlink ref="G116" r:id="rId38" xr:uid="{67D718D4-7BBC-B344-A4AC-9FA1105EFD84}"/>
-    <hyperlink ref="G117" r:id="rId39" xr:uid="{22680253-E256-FE4D-B393-DDB53AB3EE72}"/>
-    <hyperlink ref="G118" r:id="rId40" xr:uid="{C1737EA1-C466-B64E-BCF7-00204A0E2AD0}"/>
-    <hyperlink ref="G119" r:id="rId41" xr:uid="{6F5E12E0-00B8-584D-BC78-83622C273538}"/>
-    <hyperlink ref="G120" r:id="rId42" xr:uid="{11B1E05E-648B-564A-94BC-978D811708BD}"/>
-    <hyperlink ref="G121" r:id="rId43" xr:uid="{5A565AA0-BF10-DF4A-A6DA-36EBE05F3C2F}"/>
-    <hyperlink ref="G122" r:id="rId44" xr:uid="{5BF47FC7-067E-C842-AA61-041B27521B5A}"/>
-    <hyperlink ref="G123" r:id="rId45" xr:uid="{E0151B3C-0DF4-1744-BE37-A53C6A17645B}"/>
-    <hyperlink ref="G124" r:id="rId46" xr:uid="{AFDB64F8-3083-6742-95DC-074AE7611AA4}"/>
-    <hyperlink ref="G125" r:id="rId47" xr:uid="{BA6B83AA-D235-604B-A845-E9B8182E0D9F}"/>
-    <hyperlink ref="G111" r:id="rId48" xr:uid="{9429C133-7A04-0B4D-A5C7-B68881A3FD4F}"/>
+    <hyperlink ref="G98" r:id="rId32" xr:uid="{259FD402-6D0D-3E43-9F73-244A8FA24539}"/>
+    <hyperlink ref="G112" r:id="rId33" xr:uid="{BE1E0B79-FD19-9E4A-8C0B-4EFB65F4A3B5}"/>
+    <hyperlink ref="G114" r:id="rId34" xr:uid="{397B14D3-85A6-954F-BE73-1F87B57618F0}"/>
+    <hyperlink ref="G115" r:id="rId35" xr:uid="{2D19773D-B9E1-CC49-A7AC-090ED1865969}"/>
+    <hyperlink ref="G116" r:id="rId36" xr:uid="{E81741AB-74EC-424F-B159-9E36EA9C2AAC}"/>
+    <hyperlink ref="G117" r:id="rId37" xr:uid="{511B6FEA-C9F1-4C40-A21D-F84B63AD6C4C}"/>
+    <hyperlink ref="G118" r:id="rId38" xr:uid="{67D718D4-7BBC-B344-A4AC-9FA1105EFD84}"/>
+    <hyperlink ref="G119" r:id="rId39" xr:uid="{22680253-E256-FE4D-B393-DDB53AB3EE72}"/>
+    <hyperlink ref="G120" r:id="rId40" xr:uid="{C1737EA1-C466-B64E-BCF7-00204A0E2AD0}"/>
+    <hyperlink ref="G121" r:id="rId41" xr:uid="{6F5E12E0-00B8-584D-BC78-83622C273538}"/>
+    <hyperlink ref="G122" r:id="rId42" xr:uid="{11B1E05E-648B-564A-94BC-978D811708BD}"/>
+    <hyperlink ref="G123" r:id="rId43" xr:uid="{5A565AA0-BF10-DF4A-A6DA-36EBE05F3C2F}"/>
+    <hyperlink ref="G124" r:id="rId44" xr:uid="{5BF47FC7-067E-C842-AA61-041B27521B5A}"/>
+    <hyperlink ref="G125" r:id="rId45" xr:uid="{E0151B3C-0DF4-1744-BE37-A53C6A17645B}"/>
+    <hyperlink ref="G126" r:id="rId46" xr:uid="{AFDB64F8-3083-6742-95DC-074AE7611AA4}"/>
+    <hyperlink ref="G127" r:id="rId47" xr:uid="{BA6B83AA-D235-604B-A845-E9B8182E0D9F}"/>
+    <hyperlink ref="G113" r:id="rId48" xr:uid="{9429C133-7A04-0B4D-A5C7-B68881A3FD4F}"/>
+    <hyperlink ref="G128" r:id="rId49" xr:uid="{536FA44E-6852-E944-AE54-FE2739629795}"/>
+    <hyperlink ref="G96" r:id="rId50" xr:uid="{C51B2851-1922-0449-92D7-27F16F0BD314}"/>
+    <hyperlink ref="G97" r:id="rId51" xr:uid="{102C7985-55DE-8F49-9440-EF311C0EB910}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait"/>

--- a/db/A7XLK-4401-DepartmentStore.xlsx
+++ b/db/A7XLK-4401-DepartmentStore.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4C03CA4-5F3E-7048-9249-485394B653EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A52F329-0EF3-AF48-9349-4C7E28C6C174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2020" yWindow="4560" windowWidth="37900" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1260" yWindow="1200" windowWidth="37900" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Shopping" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1399" uniqueCount="835">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="843">
   <si>
     <t>title</t>
   </si>
@@ -1311,9 +1311,6 @@
   </si>
   <si>
     <t>fig/XLK-411-Shopping/AiCity-913-晉茂-2.png</t>
-  </si>
-  <si>
-    <t>fig/XLK-411-Shopping/AiCity-913-特麗-2.jpg</t>
   </si>
   <si>
     <t>fig/XLK-411-Shopping/AiCity-913-華夏鎖店.jpeg</t>
@@ -3455,6 +3452,42 @@
   </si>
   <si>
     <t>https://picture-frame-shop-570.business.site/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>144</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃園市太極健身協會</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>健身協會</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃園市龜山區原住民集會所</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0968-520-355</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>05:30 - 07:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://taotaichi.weebly.com/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-411-Shopping/AiCity-913-特麗-2.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-411-Shopping/AiCity-913-太極協會.jpg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3863,7 +3896,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K128"/>
+  <dimension ref="A1:K129"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="4.6640625" style="1" customWidth="1"/>
@@ -3906,13 +3939,13 @@
         <v>3</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>584</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -3920,10 +3953,10 @@
         <v>89</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>512</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>513</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>155</v>
@@ -3932,19 +3965,19 @@
         <v>198</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>605</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -3952,10 +3985,10 @@
         <v>61</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>452</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>453</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>135</v>
@@ -3964,22 +3997,22 @@
         <v>135</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J3" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>605</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -3987,10 +4020,10 @@
         <v>88</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>510</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>511</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>154</v>
@@ -3999,22 +4032,22 @@
         <v>197</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J4" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>605</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -4025,7 +4058,7 @@
         <v>225</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>228</v>
@@ -4034,22 +4067,22 @@
         <v>227</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>226</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J5" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>605</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -4057,10 +4090,10 @@
         <v>64</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>135</v>
@@ -4069,22 +4102,22 @@
         <v>186</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>241</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J6" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>605</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -4092,10 +4125,10 @@
         <v>63</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>457</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>458</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>135</v>
@@ -4104,22 +4137,22 @@
         <v>185</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J7" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="K7" s="1" t="s">
         <v>605</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -4130,7 +4163,7 @@
         <v>303</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>304</v>
@@ -4139,22 +4172,22 @@
         <v>305</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>306</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J8" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>605</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="34">
@@ -4174,22 +4207,22 @@
         <v>233</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>234</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J9" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>605</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -4197,10 +4230,10 @@
         <v>62</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>455</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>456</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>135</v>
@@ -4209,22 +4242,22 @@
         <v>184</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J10" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>605</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -4232,10 +4265,10 @@
         <v>84</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>505</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>506</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>152</v>
@@ -4244,22 +4277,22 @@
         <v>195</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -4267,10 +4300,10 @@
         <v>85</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>135</v>
@@ -4279,22 +4312,22 @@
         <v>135</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -4305,7 +4338,7 @@
         <v>336</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>337</v>
@@ -4317,16 +4350,16 @@
         <v>335</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -4334,10 +4367,10 @@
         <v>82</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>500</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>501</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>150</v>
@@ -4352,16 +4385,16 @@
         <v>25</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J14" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="K14" s="1" t="s">
         <v>614</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -4369,10 +4402,10 @@
         <v>83</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>503</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>504</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>151</v>
@@ -4387,16 +4420,16 @@
         <v>26</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J15" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="K15" s="1" t="s">
         <v>614</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -4404,10 +4437,10 @@
         <v>87</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>508</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>509</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>153</v>
@@ -4422,16 +4455,16 @@
         <v>27</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -4439,10 +4472,10 @@
         <v>73</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>478</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>479</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>144</v>
@@ -4457,16 +4490,16 @@
         <v>21</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J17" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="K17" s="1" t="s">
         <v>610</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -4474,10 +4507,10 @@
         <v>74</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>480</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>481</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>145</v>
@@ -4492,16 +4525,16 @@
         <v>21</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J18" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="K18" s="1" t="s">
         <v>610</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -4509,10 +4542,10 @@
         <v>70</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>471</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>472</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>141</v>
@@ -4527,16 +4560,16 @@
         <v>19</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J19" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="K19" s="1" t="s">
         <v>610</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -4544,10 +4577,10 @@
         <v>72</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>476</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>477</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>143</v>
@@ -4562,16 +4595,16 @@
         <v>20</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J20" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="K20" s="1" t="s">
         <v>610</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -4579,10 +4612,10 @@
         <v>71</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>474</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>475</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>142</v>
@@ -4597,16 +4630,16 @@
         <v>20</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J21" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="K21" s="1" t="s">
         <v>610</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -4626,22 +4659,22 @@
         <v>273</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>274</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -4652,7 +4685,7 @@
         <v>258</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>259</v>
@@ -4661,27 +4694,27 @@
         <v>260</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>261</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>294</v>
@@ -4696,22 +4729,22 @@
         <v>297</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>298</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -4731,27 +4764,27 @@
         <v>278</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>279</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>299</v>
@@ -4766,33 +4799,33 @@
         <v>297</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>302</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>283</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>280</v>
@@ -4801,27 +4834,27 @@
         <v>281</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>282</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>284</v>
@@ -4836,22 +4869,22 @@
         <v>273</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>285</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -4871,27 +4904,27 @@
         <v>265</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>266</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>291</v>
@@ -4906,27 +4939,27 @@
         <v>273</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>292</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>286</v>
@@ -4941,22 +4974,22 @@
         <v>273</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>287</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -4967,28 +5000,28 @@
         <v>267</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>268</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>269</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -4996,10 +5029,10 @@
         <v>79</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>491</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>492</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>135</v>
@@ -5014,16 +5047,16 @@
         <v>12</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -5031,16 +5064,16 @@
         <v>80</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>494</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>495</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>135</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>362</v>
@@ -5049,16 +5082,16 @@
         <v>12</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -5066,16 +5099,16 @@
         <v>81</v>
       </c>
       <c r="B35" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>497</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>498</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>135</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>363</v>
@@ -5084,16 +5117,16 @@
         <v>12</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -5101,10 +5134,10 @@
         <v>109</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>549</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>550</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>135</v>
@@ -5113,22 +5146,22 @@
         <v>135</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="I36" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="J36" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="J36" s="1" t="s">
-        <v>600</v>
-      </c>
       <c r="K36" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -5136,10 +5169,10 @@
         <v>103</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>163</v>
@@ -5154,16 +5187,16 @@
         <v>37</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="I37" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="J37" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="J37" s="1" t="s">
-        <v>600</v>
-      </c>
       <c r="K37" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -5171,10 +5204,10 @@
         <v>104</v>
       </c>
       <c r="B38" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>541</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>542</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>164</v>
@@ -5189,16 +5222,16 @@
         <v>38</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="I38" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="J38" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="J38" s="1" t="s">
-        <v>600</v>
-      </c>
       <c r="K38" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -5206,10 +5239,10 @@
         <v>101</v>
       </c>
       <c r="B39" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>536</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>537</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>162</v>
@@ -5224,16 +5257,16 @@
         <v>35</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="I39" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="J39" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="J39" s="1" t="s">
-        <v>600</v>
-      </c>
       <c r="K39" s="1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -5253,22 +5286,22 @@
         <v>239</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>240</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -5276,10 +5309,10 @@
         <v>50</v>
       </c>
       <c r="B41" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>430</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>431</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>125</v>
@@ -5294,16 +5327,16 @@
         <v>9</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -5311,16 +5344,16 @@
         <v>251</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D42" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>666</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>667</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>346</v>
@@ -5329,16 +5362,16 @@
         <v>9</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -5346,10 +5379,10 @@
         <v>51</v>
       </c>
       <c r="B43" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>433</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>434</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>126</v>
@@ -5364,16 +5397,16 @@
         <v>9</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -5381,10 +5414,10 @@
         <v>52</v>
       </c>
       <c r="B44" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>435</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>436</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>127</v>
@@ -5399,16 +5432,16 @@
         <v>9</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -5416,10 +5449,10 @@
         <v>53</v>
       </c>
       <c r="B45" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>437</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>438</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>128</v>
@@ -5434,16 +5467,16 @@
         <v>9</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -5451,10 +5484,10 @@
         <v>54</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>129</v>
@@ -5463,22 +5496,22 @@
         <v>181</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -5486,34 +5519,34 @@
         <v>55</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>130</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -5521,10 +5554,10 @@
         <v>107</v>
       </c>
       <c r="B48" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>547</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>548</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>167</v>
@@ -5533,22 +5566,22 @@
         <v>205</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="I48" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="J48" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="J48" s="1" t="s">
-        <v>600</v>
-      </c>
       <c r="K48" s="1" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -5559,7 +5592,7 @@
         <v>332</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>333</v>
@@ -5568,22 +5601,22 @@
         <v>334</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>335</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="I49" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="J49" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="J49" s="1" t="s">
-        <v>600</v>
-      </c>
       <c r="K49" s="1" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -5591,10 +5624,10 @@
         <v>106</v>
       </c>
       <c r="B50" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>545</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>546</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>166</v>
@@ -5603,22 +5636,22 @@
         <v>204</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>39</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="I50" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="J50" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="J50" s="1" t="s">
-        <v>600</v>
-      </c>
       <c r="K50" s="1" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -5626,10 +5659,10 @@
         <v>75</v>
       </c>
       <c r="B51" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>482</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>483</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>146</v>
@@ -5644,16 +5677,16 @@
         <v>22</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="I51" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="J51" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="J51" s="1" t="s">
-        <v>600</v>
-      </c>
       <c r="K51" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -5661,10 +5694,10 @@
         <v>76</v>
       </c>
       <c r="B52" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>485</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>486</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>147</v>
@@ -5679,16 +5712,16 @@
         <v>22</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="I52" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="J52" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="J52" s="1" t="s">
-        <v>600</v>
-      </c>
       <c r="K52" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -5696,10 +5729,10 @@
         <v>78</v>
       </c>
       <c r="B53" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="C53" s="1" t="s">
         <v>489</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>490</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>149</v>
@@ -5714,16 +5747,16 @@
         <v>24</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="I53" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="J53" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="J53" s="1" t="s">
-        <v>600</v>
-      </c>
       <c r="K53" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -5731,10 +5764,10 @@
         <v>77</v>
       </c>
       <c r="B54" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="C54" s="1" t="s">
         <v>487</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>488</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>148</v>
@@ -5743,57 +5776,57 @@
         <v>192</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>23</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="I54" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="J54" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="J54" s="1" t="s">
-        <v>600</v>
-      </c>
       <c r="K54" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="55" spans="1:11">
       <c r="A55" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>697</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="C55" s="1" t="s">
         <v>698</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="D55" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="E55" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="E55" s="1" t="s">
+      <c r="F55" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="G55" s="7" t="s">
         <v>701</v>
       </c>
-      <c r="F55" s="1" t="s">
-        <v>704</v>
-      </c>
-      <c r="G55" s="7" t="s">
-        <v>702</v>
-      </c>
       <c r="H55" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="I55" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="J55" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="J55" s="1" t="s">
-        <v>600</v>
-      </c>
       <c r="K55" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -5801,10 +5834,10 @@
         <v>59</v>
       </c>
       <c r="B56" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>448</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>449</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>134</v>
@@ -5819,16 +5852,16 @@
         <v>13</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="I56" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="J56" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="J56" s="1" t="s">
-        <v>600</v>
-      </c>
       <c r="K56" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -5836,10 +5869,10 @@
         <v>60</v>
       </c>
       <c r="B57" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>450</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>451</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>134</v>
@@ -5854,16 +5887,16 @@
         <v>13</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="I57" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="J57" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="J57" s="1" t="s">
-        <v>600</v>
-      </c>
       <c r="K57" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -5871,16 +5904,16 @@
         <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="C58" s="1" t="s">
         <v>443</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>444</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>132</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>348</v>
@@ -5889,16 +5922,16 @@
         <v>11</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="I58" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="J58" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="J58" s="1" t="s">
-        <v>600</v>
-      </c>
       <c r="K58" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -5906,10 +5939,10 @@
         <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="C59" s="1" t="s">
         <v>446</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>447</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>133</v>
@@ -5924,16 +5957,16 @@
         <v>12</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="I59" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="J59" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="J59" s="1" t="s">
-        <v>600</v>
-      </c>
       <c r="K59" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -5941,10 +5974,10 @@
         <v>56</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>131</v>
@@ -5959,16 +5992,16 @@
         <v>10</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="I60" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="J60" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="J60" s="1" t="s">
-        <v>600</v>
-      </c>
       <c r="K60" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -5976,10 +6009,10 @@
         <v>102</v>
       </c>
       <c r="B61" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="C61" s="1" t="s">
         <v>538</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>539</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>163</v>
@@ -5994,16 +6027,16 @@
         <v>36</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="I61" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="J61" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="J61" s="1" t="s">
-        <v>600</v>
-      </c>
       <c r="K61" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -6011,10 +6044,10 @@
         <v>98</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>160</v>
@@ -6029,16 +6062,16 @@
         <v>33</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="I62" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="J62" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="J62" s="1" t="s">
-        <v>600</v>
-      </c>
       <c r="K62" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -6046,10 +6079,10 @@
         <v>46</v>
       </c>
       <c r="B63" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>420</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>421</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>121</v>
@@ -6064,16 +6097,16 @@
         <v>5</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="I63" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="J63" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="J63" s="1" t="s">
-        <v>600</v>
-      </c>
       <c r="K63" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -6081,10 +6114,10 @@
         <v>45</v>
       </c>
       <c r="B64" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>417</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>418</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>120</v>
@@ -6099,16 +6132,16 @@
         <v>4</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I64" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="J64" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="J64" s="1" t="s">
+      <c r="K64" s="1" t="s">
         <v>600</v>
-      </c>
-      <c r="K64" s="1" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -6116,10 +6149,10 @@
         <v>47</v>
       </c>
       <c r="B65" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C65" s="1" t="s">
         <v>423</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>424</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>122</v>
@@ -6134,27 +6167,27 @@
         <v>6</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I65" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="J65" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="J65" s="1" t="s">
+      <c r="K65" s="1" t="s">
         <v>600</v>
-      </c>
-      <c r="K65" s="1" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="66" spans="1:11">
       <c r="A66" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B66" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>558</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>559</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>172</v>
@@ -6163,22 +6196,22 @@
         <v>174</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I66" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="J66" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="J66" s="1" t="s">
+      <c r="K66" s="1" t="s">
         <v>600</v>
-      </c>
-      <c r="K66" s="1" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -6186,16 +6219,16 @@
         <v>48</v>
       </c>
       <c r="B67" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C67" s="1" t="s">
         <v>425</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>426</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>123</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>344</v>
@@ -6204,16 +6237,16 @@
         <v>7</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I67" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="J67" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="J67" s="1" t="s">
+      <c r="K67" s="1" t="s">
         <v>600</v>
-      </c>
-      <c r="K67" s="1" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -6221,16 +6254,16 @@
         <v>49</v>
       </c>
       <c r="B68" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C68" s="1" t="s">
         <v>428</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>429</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>124</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>345</v>
@@ -6239,16 +6272,16 @@
         <v>8</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I68" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="J68" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="J68" s="1" t="s">
+      <c r="K68" s="1" t="s">
         <v>600</v>
-      </c>
-      <c r="K68" s="1" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -6256,10 +6289,10 @@
         <v>114</v>
       </c>
       <c r="B69" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="C69" s="1" t="s">
         <v>556</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>557</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>171</v>
@@ -6268,22 +6301,22 @@
         <v>207</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>42</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I69" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="J69" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="J69" s="1" t="s">
+      <c r="K69" s="1" t="s">
         <v>600</v>
-      </c>
-      <c r="K69" s="1" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -6291,10 +6324,10 @@
         <v>113</v>
       </c>
       <c r="B70" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C70" s="1" t="s">
         <v>554</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>555</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>170</v>
@@ -6303,22 +6336,22 @@
         <v>174</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>41</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I70" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="J70" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="J70" s="1" t="s">
+      <c r="K70" s="1" t="s">
         <v>600</v>
-      </c>
-      <c r="K70" s="1" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -6326,10 +6359,10 @@
         <v>69</v>
       </c>
       <c r="B71" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="C71" s="1" t="s">
         <v>469</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>470</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>140</v>
@@ -6344,16 +6377,16 @@
         <v>18</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -6361,10 +6394,10 @@
         <v>68</v>
       </c>
       <c r="B72" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="C72" s="1" t="s">
         <v>467</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>468</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>139</v>
@@ -6379,16 +6412,16 @@
         <v>17</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -6396,10 +6429,10 @@
         <v>65</v>
       </c>
       <c r="B73" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="C73" s="1" t="s">
         <v>460</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>461</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>136</v>
@@ -6414,16 +6447,16 @@
         <v>14</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J73" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="K73" s="1" t="s">
         <v>607</v>
-      </c>
-      <c r="K73" s="1" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -6431,10 +6464,10 @@
         <v>66</v>
       </c>
       <c r="B74" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="C74" s="1" t="s">
         <v>463</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>464</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>137</v>
@@ -6449,16 +6482,16 @@
         <v>15</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J74" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="K74" s="1" t="s">
         <v>607</v>
-      </c>
-      <c r="K74" s="1" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -6466,10 +6499,10 @@
         <v>67</v>
       </c>
       <c r="B75" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="C75" s="1" t="s">
         <v>465</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>466</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>138</v>
@@ -6484,16 +6517,16 @@
         <v>16</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J75" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="K75" s="1" t="s">
         <v>607</v>
-      </c>
-      <c r="K75" s="1" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -6501,10 +6534,10 @@
         <v>99</v>
       </c>
       <c r="B76" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="C76" s="1" t="s">
         <v>530</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>531</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>135</v>
@@ -6519,16 +6552,16 @@
         <v>12</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="I76" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="J76" s="1" t="s">
         <v>622</v>
       </c>
-      <c r="J76" s="1" t="s">
+      <c r="K76" s="1" t="s">
         <v>623</v>
-      </c>
-      <c r="K76" s="1" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -6539,7 +6572,7 @@
         <v>328</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>329</v>
@@ -6548,1798 +6581,1833 @@
         <v>330</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>331</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="I77" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="J77" s="1" t="s">
         <v>622</v>
       </c>
-      <c r="J77" s="1" t="s">
-        <v>623</v>
-      </c>
       <c r="K77" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="78" spans="1:11">
       <c r="A78" s="1" t="s">
-        <v>105</v>
+        <v>834</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>543</v>
+        <v>835</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>544</v>
+        <v>837</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>165</v>
+        <v>838</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>192</v>
+        <v>839</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="G78" s="1" t="s">
-        <v>12</v>
+        <v>842</v>
+      </c>
+      <c r="G78" s="7" t="s">
+        <v>840</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>532</v>
+        <v>836</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>630</v>
+        <v>836</v>
       </c>
     </row>
     <row r="79" spans="1:11">
       <c r="A79" s="1" t="s">
-        <v>242</v>
+        <v>105</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>574</v>
+        <v>542</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>575</v>
+        <v>543</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="E79" s="6" t="s">
-        <v>339</v>
+        <v>165</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>192</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="G79" s="5" t="s">
-        <v>340</v>
+        <v>841</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>567</v>
+        <v>531</v>
       </c>
       <c r="I79" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="J79" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="J79" s="1" t="s">
+      <c r="K79" s="1" t="s">
         <v>629</v>
-      </c>
-      <c r="K79" s="1" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="80" spans="1:11">
       <c r="A80" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="B80" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="C80" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="D80" s="6" t="s">
-        <v>219</v>
+      <c r="C80" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>338</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="F80" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="F80" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="G80" s="4" t="s">
-        <v>218</v>
+      <c r="G80" s="5" t="s">
+        <v>340</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="I80" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="J80" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="J80" s="1" t="s">
-        <v>629</v>
-      </c>
       <c r="K80" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="81" spans="1:11">
       <c r="A81" s="1" t="s">
-        <v>588</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="F81" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="F81" s="4" t="s">
         <v>390</v>
       </c>
-      <c r="G81" s="2" t="s">
-        <v>214</v>
+      <c r="G81" s="4" t="s">
+        <v>218</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="I81" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="J81" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="J81" s="1" t="s">
-        <v>629</v>
-      </c>
       <c r="K81" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="82" spans="1:11">
       <c r="A82" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="B82" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="D82" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="E82" s="6" t="s">
-        <v>572</v>
-      </c>
-      <c r="F82" s="4" t="s">
-        <v>672</v>
-      </c>
-      <c r="G82" s="4" t="s">
-        <v>213</v>
+        <v>587</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>214</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="I82" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="J82" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="J82" s="1" t="s">
-        <v>629</v>
-      </c>
       <c r="K82" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="83" spans="1:11">
       <c r="A83" s="1" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>669</v>
+        <v>224</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>670</v>
+        <v>570</v>
       </c>
       <c r="D83" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="E83" s="6" t="s">
+        <v>571</v>
+      </c>
+      <c r="F83" s="4" t="s">
         <v>671</v>
       </c>
-      <c r="E83" s="6"/>
-      <c r="F83" s="4" t="s">
-        <v>673</v>
-      </c>
-      <c r="G83" s="1" t="s">
-        <v>12</v>
+      <c r="G83" s="4" t="s">
+        <v>213</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="I83" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="J83" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="J83" s="1" t="s">
-        <v>629</v>
-      </c>
       <c r="K83" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="84" spans="1:11">
       <c r="A84" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>670</v>
+      </c>
+      <c r="E84" s="6"/>
+      <c r="F84" s="4" t="s">
+        <v>672</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="J84" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11">
+      <c r="A85" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B84" s="4" t="s">
+      <c r="B85" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="C85" s="4" t="s">
         <v>675</v>
       </c>
-      <c r="C84" s="4" t="s">
+      <c r="D85" s="6" t="s">
         <v>676</v>
       </c>
-      <c r="D84" s="6" t="s">
+      <c r="E85" s="6" t="s">
         <v>677</v>
       </c>
-      <c r="E84" s="6" t="s">
+      <c r="F85" s="4" t="s">
         <v>678</v>
       </c>
-      <c r="F84" s="4" t="s">
+      <c r="G85" s="8" t="s">
+        <v>673</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="J85" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" ht="34">
+      <c r="A86" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>681</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>682</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>680</v>
+      </c>
+      <c r="E86" s="6" t="s">
+        <v>683</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>684</v>
+      </c>
+      <c r="G86" s="8" t="s">
         <v>679</v>
       </c>
-      <c r="G84" s="8" t="s">
-        <v>674</v>
-      </c>
-      <c r="H84" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="I84" s="1" t="s">
+      <c r="H86" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="J86" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="J84" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="K84" s="1" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" ht="34">
-      <c r="A85" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>682</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>683</v>
-      </c>
-      <c r="D85" s="9" t="s">
-        <v>681</v>
-      </c>
-      <c r="E85" s="6" t="s">
-        <v>684</v>
-      </c>
-      <c r="F85" s="4" t="s">
-        <v>685</v>
-      </c>
-      <c r="G85" s="8" t="s">
-        <v>680</v>
-      </c>
-      <c r="H85" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="I85" s="1" t="s">
-        <v>628</v>
-      </c>
-      <c r="J85" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="K85" s="1" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11">
-      <c r="A86" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="B86" s="4" t="s">
-        <v>687</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>690</v>
-      </c>
-      <c r="D86" s="6" t="s">
-        <v>689</v>
-      </c>
-      <c r="E86" s="6" t="s">
-        <v>678</v>
-      </c>
-      <c r="F86" s="4" t="s">
-        <v>688</v>
-      </c>
-      <c r="G86" s="8" t="s">
-        <v>686</v>
-      </c>
-      <c r="H86" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="I86" s="1" t="s">
-        <v>628</v>
-      </c>
-      <c r="J86" s="1" t="s">
-        <v>629</v>
-      </c>
       <c r="K86" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="87" spans="1:11">
       <c r="A87" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>696</v>
+        <v>677</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="G87" s="8" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="I87" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="J87" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="J87" s="1" t="s">
-        <v>629</v>
-      </c>
       <c r="K87" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="88" spans="1:11">
       <c r="A88" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>564</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="E88" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>691</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>692</v>
+      </c>
+      <c r="D88" s="6" t="s">
+        <v>693</v>
+      </c>
+      <c r="E88" s="6" t="s">
+        <v>695</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="G88" s="8" t="s">
+        <v>694</v>
+      </c>
+      <c r="H88" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="F88" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="G88" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="H88" s="1" t="s">
-        <v>567</v>
-      </c>
       <c r="I88" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="J88" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="J88" s="1" t="s">
-        <v>629</v>
-      </c>
       <c r="K88" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="89" spans="1:11">
       <c r="A89" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>569</v>
+        <v>564</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>565</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>211</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="I89" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="J89" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="J89" s="1" t="s">
-        <v>629</v>
-      </c>
       <c r="K89" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="90" spans="1:11">
       <c r="A90" s="1" t="s">
-        <v>598</v>
+        <v>223</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>323</v>
+        <v>567</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>325</v>
+        <v>568</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="G90" s="2" t="s">
-        <v>324</v>
+        <v>388</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>307</v>
+        <v>566</v>
       </c>
       <c r="I90" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="J90" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="J90" s="1" t="s">
-        <v>637</v>
-      </c>
       <c r="K90" s="1" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
     </row>
     <row r="91" spans="1:11">
       <c r="A91" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>310</v>
+        <v>327</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="H91" s="1" t="s">
         <v>307</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="J91" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="K91" s="1" t="s">
         <v>637</v>
-      </c>
-      <c r="K91" s="1" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="92" spans="1:11">
       <c r="A92" s="1" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="H92" s="1" t="s">
         <v>307</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="J92" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="K92" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="K92" s="1" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" ht="34">
+    </row>
+    <row r="93" spans="1:11">
       <c r="A93" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>320</v>
+        <v>313</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>314</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H93" s="1" t="s">
         <v>307</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="J93" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="K93" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="K93" s="1" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11">
+    </row>
+    <row r="94" spans="1:11" ht="34">
       <c r="A94" s="1" t="s">
-        <v>212</v>
+        <v>596</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>562</v>
+        <v>319</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>320</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>209</v>
+        <v>321</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>563</v>
+        <v>322</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>387</v>
+        <v>409</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>208</v>
+        <v>318</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>561</v>
+        <v>307</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>561</v>
+        <v>637</v>
       </c>
     </row>
     <row r="95" spans="1:11">
       <c r="A95" s="1" t="s">
-        <v>587</v>
+        <v>212</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>426</v>
+        <v>561</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>209</v>
       </c>
       <c r="E95" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="H95" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="F95" s="1" t="s">
-        <v>826</v>
-      </c>
-      <c r="G95" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="H95" s="1" t="s">
-        <v>561</v>
-      </c>
       <c r="I95" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="96" spans="1:11">
       <c r="A96" s="1" t="s">
-        <v>820</v>
+        <v>586</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>821</v>
+        <v>115</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>823</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>824</v>
+        <v>425</v>
       </c>
       <c r="E96" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="F96" s="1" t="s">
         <v>825</v>
       </c>
-      <c r="F96" s="1" t="s">
-        <v>827</v>
-      </c>
-      <c r="G96" s="7" t="s">
-        <v>828</v>
+      <c r="G96" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>819</v>
+        <v>560</v>
       </c>
     </row>
     <row r="97" spans="1:11">
       <c r="A97" s="1" t="s">
+        <v>819</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>820</v>
+      </c>
+      <c r="C97" s="1" t="s">
         <v>822</v>
       </c>
-      <c r="B97" s="1" t="s">
-        <v>829</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>830</v>
-      </c>
       <c r="D97" s="1" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>834</v>
+        <v>827</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="98" spans="1:11">
       <c r="A98" s="1" t="s">
-        <v>705</v>
+        <v>821</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>708</v>
+        <v>828</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>709</v>
+        <v>829</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>710</v>
+        <v>830</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>244</v>
+        <v>831</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>712</v>
+        <v>832</v>
       </c>
       <c r="G98" s="7" t="s">
-        <v>711</v>
+        <v>833</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>707</v>
+        <v>560</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>706</v>
+        <v>633</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>707</v>
+        <v>818</v>
       </c>
     </row>
     <row r="99" spans="1:11">
       <c r="A99" s="1" t="s">
-        <v>90</v>
+        <v>704</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>651</v>
+        <v>707</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>514</v>
+        <v>708</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>135</v>
+        <v>709</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>135</v>
+        <v>244</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="G99" s="1" t="s">
-        <v>12</v>
+        <v>711</v>
+      </c>
+      <c r="G99" s="7" t="s">
+        <v>710</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>515</v>
+        <v>706</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>613</v>
+        <v>627</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>618</v>
+        <v>705</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>619</v>
+        <v>706</v>
       </c>
     </row>
     <row r="100" spans="1:11">
       <c r="A100" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>516</v>
+        <v>650</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>135</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>199</v>
+        <v>135</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>645</v>
+        <v>652</v>
       </c>
       <c r="G100" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="J100" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="K100" s="1" t="s">
         <v>618</v>
-      </c>
-      <c r="K100" s="1" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="101" spans="1:11">
       <c r="A101" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>526</v>
+        <v>516</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>135</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>521</v>
+        <v>12</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="J101" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="K101" s="1" t="s">
         <v>618</v>
-      </c>
-      <c r="K101" s="1" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="102" spans="1:11">
       <c r="A102" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>652</v>
+        <v>644</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>29</v>
+        <v>520</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="J102" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="K102" s="1" t="s">
         <v>618</v>
-      </c>
-      <c r="K102" s="1" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="103" spans="1:11">
       <c r="A103" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>30</v>
+        <v>517</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>368</v>
+        <v>651</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="J103" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="K103" s="1" t="s">
         <v>618</v>
-      </c>
-      <c r="K103" s="1" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="104" spans="1:11">
       <c r="A104" s="1" t="s">
-        <v>252</v>
+        <v>95</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>243</v>
+        <v>30</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>579</v>
+        <v>523</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>246</v>
+        <v>158</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>244</v>
+        <v>177</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="G104" s="2" t="s">
-        <v>245</v>
+        <v>368</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="J104" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="K104" s="1" t="s">
         <v>618</v>
-      </c>
-      <c r="K104" s="1" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="105" spans="1:11">
       <c r="A105" s="1" t="s">
-        <v>94</v>
+        <v>252</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>522</v>
+        <v>243</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>523</v>
+        <v>578</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>157</v>
+        <v>246</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>135</v>
+        <v>244</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>645</v>
-      </c>
-      <c r="G105" s="1" t="s">
-        <v>521</v>
+        <v>395</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="J105" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="K105" s="1" t="s">
         <v>618</v>
-      </c>
-      <c r="K105" s="1" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="106" spans="1:11">
       <c r="A106" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>654</v>
+        <v>521</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>135</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="J106" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="K106" s="1" t="s">
         <v>618</v>
-      </c>
-      <c r="K106" s="1" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="107" spans="1:11">
       <c r="A107" s="1" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>533</v>
+        <v>653</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>534</v>
+        <v>519</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>161</v>
+        <v>135</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>535</v>
+        <v>135</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>372</v>
+        <v>644</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>34</v>
+        <v>520</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>532</v>
+        <v>514</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="J107" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="K107" s="1" t="s">
         <v>618</v>
-      </c>
-      <c r="K107" s="1" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="108" spans="1:11">
       <c r="A108" s="1" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>551</v>
+        <v>532</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>552</v>
+        <v>533</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>206</v>
+        <v>534</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>660</v>
+        <v>372</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="J108" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="K108" s="1" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
     </row>
     <row r="109" spans="1:11">
       <c r="A109" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>414</v>
+        <v>551</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>135</v>
+        <v>206</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>382</v>
+        <v>659</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>521</v>
+        <v>40</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="J109" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="110" spans="1:11">
       <c r="A110" s="1" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>527</v>
+        <v>552</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>528</v>
+        <v>413</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>198</v>
+        <v>135</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>32</v>
+        <v>520</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>422</v>
+        <v>531</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="J110" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>620</v>
+        <v>631</v>
       </c>
     </row>
     <row r="111" spans="1:11">
       <c r="A111" s="1" t="s">
-        <v>659</v>
+        <v>97</v>
       </c>
       <c r="B111" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H111" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="I111" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="J111" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="K111" s="1" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11">
+      <c r="A112" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="C112" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="C111" s="1" t="s">
+      <c r="D112" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="D111" s="1" t="s">
-        <v>665</v>
-      </c>
-      <c r="F111" s="1" t="s">
+      <c r="F112" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="G112" s="7" t="s">
         <v>661</v>
       </c>
-      <c r="G111" s="7" t="s">
-        <v>662</v>
-      </c>
-      <c r="H111" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="I111" s="1" t="s">
-        <v>599</v>
-      </c>
-      <c r="J111" s="1" t="s">
-        <v>605</v>
-      </c>
-      <c r="K111" s="1" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11" ht="17">
-      <c r="A112" s="10" t="s">
-        <v>716</v>
-      </c>
-      <c r="B112" s="11" t="s">
-        <v>717</v>
-      </c>
-      <c r="C112" s="12" t="s">
-        <v>718</v>
-      </c>
-      <c r="D112" s="11" t="s">
-        <v>719</v>
-      </c>
-      <c r="E112" s="13" t="s">
-        <v>720</v>
-      </c>
-      <c r="F112" s="11" t="s">
-        <v>721</v>
-      </c>
-      <c r="G112" s="14" t="s">
-        <v>722</v>
-      </c>
       <c r="H112" s="1" t="s">
-        <v>715</v>
+        <v>431</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>628</v>
+        <v>598</v>
       </c>
       <c r="J112" s="1" t="s">
-        <v>713</v>
+        <v>604</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>714</v>
+        <v>602</v>
       </c>
     </row>
     <row r="113" spans="1:11" ht="17">
       <c r="A113" s="10" t="s">
-        <v>723</v>
-      </c>
-      <c r="B113" s="15" t="s">
-        <v>812</v>
-      </c>
-      <c r="C113" s="15" t="s">
-        <v>811</v>
+        <v>715</v>
+      </c>
+      <c r="B113" s="11" t="s">
+        <v>716</v>
+      </c>
+      <c r="C113" s="12" t="s">
+        <v>717</v>
       </c>
       <c r="D113" s="11" t="s">
-        <v>813</v>
+        <v>718</v>
       </c>
       <c r="E113" s="13" t="s">
+        <v>719</v>
+      </c>
+      <c r="F113" s="11" t="s">
         <v>720</v>
       </c>
-      <c r="F113" s="11" t="s">
-        <v>724</v>
-      </c>
       <c r="G113" s="14" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="J113" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="K113" s="1" t="s">
         <v>713</v>
-      </c>
-      <c r="K113" s="1" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="114" spans="1:11" ht="17">
       <c r="A114" s="10" t="s">
-        <v>726</v>
-      </c>
-      <c r="B114" s="11" t="s">
-        <v>727</v>
-      </c>
-      <c r="C114" s="12" t="s">
-        <v>728</v>
+        <v>722</v>
+      </c>
+      <c r="B114" s="15" t="s">
+        <v>811</v>
+      </c>
+      <c r="C114" s="15" t="s">
+        <v>810</v>
       </c>
       <c r="D114" s="11" t="s">
-        <v>729</v>
+        <v>812</v>
       </c>
       <c r="E114" s="13" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="F114" s="11" t="s">
-        <v>730</v>
+        <v>723</v>
       </c>
       <c r="G114" s="14" t="s">
-        <v>731</v>
+        <v>724</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="J114" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="K114" s="1" t="s">
         <v>713</v>
-      </c>
-      <c r="K114" s="1" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="115" spans="1:11" ht="17">
       <c r="A115" s="10" t="s">
-        <v>732</v>
+        <v>725</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>733</v>
+        <v>726</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>734</v>
+        <v>727</v>
       </c>
       <c r="D115" s="11" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="E115" s="13" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="F115" s="11" t="s">
-        <v>736</v>
+        <v>729</v>
       </c>
       <c r="G115" s="14" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="J115" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="K115" s="1" t="s">
         <v>713</v>
-      </c>
-      <c r="K115" s="1" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="116" spans="1:11" ht="17">
       <c r="A116" s="10" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="B116" s="11" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>741</v>
+        <v>734</v>
       </c>
       <c r="E116" s="13" t="s">
-        <v>742</v>
+        <v>719</v>
       </c>
       <c r="F116" s="11" t="s">
-        <v>743</v>
+        <v>735</v>
       </c>
       <c r="G116" s="14" t="s">
-        <v>744</v>
+        <v>736</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="J116" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="K116" s="1" t="s">
         <v>713</v>
-      </c>
-      <c r="K116" s="1" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="117" spans="1:11" ht="17">
       <c r="A117" s="10" t="s">
-        <v>745</v>
+        <v>737</v>
       </c>
       <c r="B117" s="11" t="s">
-        <v>746</v>
+        <v>738</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>747</v>
+        <v>739</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>748</v>
+        <v>740</v>
       </c>
       <c r="E117" s="13" t="s">
-        <v>720</v>
+        <v>741</v>
       </c>
       <c r="F117" s="11" t="s">
-        <v>749</v>
+        <v>742</v>
       </c>
       <c r="G117" s="14" t="s">
-        <v>750</v>
+        <v>743</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="J117" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="K117" s="1" t="s">
         <v>713</v>
-      </c>
-      <c r="K117" s="1" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="118" spans="1:11" ht="17">
       <c r="A118" s="10" t="s">
-        <v>751</v>
+        <v>744</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="D118" s="11" t="s">
-        <v>754</v>
+        <v>747</v>
       </c>
       <c r="E118" s="13" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="F118" s="11" t="s">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="G118" s="14" t="s">
-        <v>756</v>
+        <v>749</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="J118" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="K118" s="1" t="s">
         <v>713</v>
-      </c>
-      <c r="K118" s="1" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="119" spans="1:11" ht="17">
       <c r="A119" s="10" t="s">
-        <v>757</v>
+        <v>750</v>
       </c>
       <c r="B119" s="11" t="s">
-        <v>758</v>
+        <v>751</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="D119" s="11" t="s">
-        <v>760</v>
+        <v>753</v>
       </c>
       <c r="E119" s="13" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="F119" s="11" t="s">
-        <v>761</v>
+        <v>754</v>
       </c>
       <c r="G119" s="14" t="s">
-        <v>762</v>
+        <v>755</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="J119" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="K119" s="1" t="s">
         <v>713</v>
-      </c>
-      <c r="K119" s="1" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="120" spans="1:11" ht="17">
       <c r="A120" s="10" t="s">
-        <v>763</v>
+        <v>756</v>
       </c>
       <c r="B120" s="11" t="s">
-        <v>764</v>
+        <v>757</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="D120" s="11" t="s">
-        <v>766</v>
+        <v>759</v>
       </c>
       <c r="E120" s="13" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="F120" s="11" t="s">
-        <v>767</v>
+        <v>760</v>
       </c>
       <c r="G120" s="14" t="s">
-        <v>768</v>
+        <v>761</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="J120" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="K120" s="1" t="s">
         <v>713</v>
-      </c>
-      <c r="K120" s="1" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="121" spans="1:11" ht="17">
       <c r="A121" s="10" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B121" s="11" t="s">
-        <v>770</v>
+        <v>763</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
       <c r="D121" s="11" t="s">
-        <v>772</v>
+        <v>765</v>
       </c>
       <c r="E121" s="13" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="F121" s="11" t="s">
-        <v>773</v>
+        <v>766</v>
       </c>
       <c r="G121" s="14" t="s">
-        <v>774</v>
+        <v>767</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="J121" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="K121" s="1" t="s">
         <v>713</v>
-      </c>
-      <c r="K121" s="1" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="122" spans="1:11" ht="17">
       <c r="A122" s="10" t="s">
-        <v>775</v>
+        <v>768</v>
       </c>
       <c r="B122" s="11" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="D122" s="11" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="E122" s="13" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="F122" s="11" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="G122" s="14" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="I122" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="J122" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="K122" s="1" t="s">
         <v>713</v>
-      </c>
-      <c r="K122" s="1" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="123" spans="1:11" ht="17">
       <c r="A123" s="10" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="B123" s="11" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="D123" s="11" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="E123" s="13" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="F123" s="11" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
       <c r="G123" s="14" t="s">
-        <v>786</v>
+        <v>779</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="I123" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="J123" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="K123" s="1" t="s">
         <v>713</v>
-      </c>
-      <c r="K123" s="1" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="124" spans="1:11" ht="17">
       <c r="A124" s="10" t="s">
-        <v>787</v>
+        <v>780</v>
       </c>
       <c r="B124" s="11" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>789</v>
+        <v>782</v>
       </c>
       <c r="D124" s="11" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="E124" s="13" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="F124" s="11" t="s">
-        <v>791</v>
+        <v>784</v>
       </c>
       <c r="G124" s="14" t="s">
-        <v>792</v>
+        <v>785</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="J124" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="K124" s="1" t="s">
         <v>713</v>
-      </c>
-      <c r="K124" s="1" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="125" spans="1:11" ht="17">
       <c r="A125" s="10" t="s">
-        <v>793</v>
+        <v>786</v>
       </c>
       <c r="B125" s="11" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>795</v>
+        <v>788</v>
       </c>
       <c r="D125" s="11" t="s">
-        <v>796</v>
+        <v>789</v>
       </c>
       <c r="E125" s="13" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="F125" s="11" t="s">
-        <v>797</v>
+        <v>790</v>
       </c>
       <c r="G125" s="14" t="s">
-        <v>798</v>
+        <v>791</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="I125" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="J125" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="K125" s="1" t="s">
         <v>713</v>
-      </c>
-      <c r="K125" s="1" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="126" spans="1:11" ht="17">
       <c r="A126" s="10" t="s">
-        <v>799</v>
+        <v>792</v>
       </c>
       <c r="B126" s="11" t="s">
-        <v>800</v>
+        <v>793</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>801</v>
+        <v>794</v>
       </c>
       <c r="D126" s="11" t="s">
-        <v>802</v>
+        <v>795</v>
       </c>
       <c r="E126" s="13" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="F126" s="11" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="G126" s="14" t="s">
-        <v>804</v>
+        <v>797</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="J126" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="K126" s="1" t="s">
         <v>713</v>
-      </c>
-      <c r="K126" s="1" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="127" spans="1:11" ht="17">
       <c r="A127" s="10" t="s">
-        <v>805</v>
+        <v>798</v>
       </c>
       <c r="B127" s="11" t="s">
-        <v>806</v>
+        <v>799</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>807</v>
+        <v>800</v>
       </c>
       <c r="D127" s="11" t="s">
-        <v>808</v>
+        <v>801</v>
       </c>
       <c r="E127" s="13" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="F127" s="11" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="G127" s="14" t="s">
-        <v>810</v>
+        <v>803</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="I127" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="J127" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="K127" s="1" t="s">
         <v>713</v>
-      </c>
-      <c r="K127" s="1" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="128" spans="1:11" ht="17">
       <c r="A128" s="10" t="s">
+        <v>804</v>
+      </c>
+      <c r="B128" s="11" t="s">
+        <v>805</v>
+      </c>
+      <c r="C128" s="12" t="s">
+        <v>806</v>
+      </c>
+      <c r="D128" s="11" t="s">
+        <v>807</v>
+      </c>
+      <c r="E128" s="13" t="s">
+        <v>719</v>
+      </c>
+      <c r="F128" s="11" t="s">
+        <v>808</v>
+      </c>
+      <c r="G128" s="14" t="s">
+        <v>809</v>
+      </c>
+      <c r="H128" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="I128" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="J128" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="K128" s="1" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" ht="17">
+      <c r="A129" s="10" t="s">
+        <v>813</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>814</v>
       </c>
-      <c r="B128" s="1" t="s">
+      <c r="C129" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D129" s="1" t="s">
         <v>815</v>
       </c>
-      <c r="C128" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="D128" s="1" t="s">
+      <c r="E129" s="13" t="s">
+        <v>719</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="G129" s="7" t="s">
         <v>816</v>
       </c>
-      <c r="E128" s="13" t="s">
-        <v>720</v>
-      </c>
-      <c r="F128" s="1" t="s">
-        <v>818</v>
-      </c>
-      <c r="G128" s="7" t="s">
-        <v>817</v>
-      </c>
-      <c r="H128" s="1" t="s">
-        <v>715</v>
-      </c>
-      <c r="I128" s="1" t="s">
-        <v>628</v>
-      </c>
-      <c r="J128" s="1" t="s">
+      <c r="H129" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="I129" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="J129" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="K129" s="1" t="s">
         <v>713</v>
       </c>
-      <c r="K128" s="1" t="s">
-        <v>714</v>
-      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K110">
-    <sortCondition ref="J2:J110"/>
-    <sortCondition ref="K2:K110"/>
-    <sortCondition ref="B2:B110"/>
-    <sortCondition ref="C2:C110"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K111">
+    <sortCondition ref="J2:J111"/>
+    <sortCondition ref="K2:K111"/>
+    <sortCondition ref="B2:B111"/>
+    <sortCondition ref="C2:C111"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="2">
@@ -8351,13 +8419,13 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="G94" r:id="rId1" xr:uid="{A39B8C40-8D45-EB49-A4FC-B32617C3743A}"/>
-    <hyperlink ref="G81" r:id="rId2" xr:uid="{B5DCC527-C34A-A84A-863F-C7614151FE6F}"/>
+    <hyperlink ref="G95" r:id="rId1" xr:uid="{A39B8C40-8D45-EB49-A4FC-B32617C3743A}"/>
+    <hyperlink ref="G82" r:id="rId2" xr:uid="{B5DCC527-C34A-A84A-863F-C7614151FE6F}"/>
     <hyperlink ref="G5" r:id="rId3" xr:uid="{9F3F15C4-C0FD-AE4F-A261-C94D2C5C5CDD}"/>
     <hyperlink ref="G9" r:id="rId4" xr:uid="{57110EDF-FEA5-304D-BC8D-B61106C21880}"/>
     <hyperlink ref="G40" r:id="rId5" location="sale_active" xr:uid="{730FA5EB-C91B-144D-A783-4D831224B6A9}"/>
     <hyperlink ref="G6" r:id="rId6" xr:uid="{1F8F556A-7472-764F-A198-D7F42EFCC387}"/>
-    <hyperlink ref="G104" r:id="rId7" xr:uid="{D0E463C4-46AF-0146-87CD-46876FB5CA0D}"/>
+    <hyperlink ref="G105" r:id="rId7" xr:uid="{D0E463C4-46AF-0146-87CD-46876FB5CA0D}"/>
     <hyperlink ref="G23" r:id="rId8" xr:uid="{DF8FD8B1-A50B-9E4E-9410-150C09502DAB}"/>
     <hyperlink ref="G29" r:id="rId9" xr:uid="{FF011359-39BB-A040-AED2-D2D90A217A10}"/>
     <hyperlink ref="G32" r:id="rId10" xr:uid="{52BA0BCD-A138-3A42-93E9-9408D0B6CD41}"/>
@@ -8370,38 +8438,39 @@
     <hyperlink ref="G24" r:id="rId17" xr:uid="{645725E7-FD7F-7841-BD5D-4F55FBCDAB8D}"/>
     <hyperlink ref="G26" r:id="rId18" xr:uid="{D8E83196-8EED-474F-A39D-4B8A53066F90}"/>
     <hyperlink ref="G8" r:id="rId19" xr:uid="{D8074921-21AA-094E-B1E8-1A2B5D8215AB}"/>
-    <hyperlink ref="G91" r:id="rId20" xr:uid="{67DB94DD-4F2A-2B47-90EF-FED3ED8F2017}"/>
-    <hyperlink ref="G92" r:id="rId21" xr:uid="{F6F3D17A-11C3-804A-89D9-3C231334A22A}"/>
-    <hyperlink ref="G93" r:id="rId22" xr:uid="{D5F7639A-8FC0-444F-B0B1-291456215366}"/>
-    <hyperlink ref="G90" r:id="rId23" xr:uid="{40CF7C3F-7CEF-0245-8E88-7892E420529A}"/>
+    <hyperlink ref="G92" r:id="rId20" xr:uid="{67DB94DD-4F2A-2B47-90EF-FED3ED8F2017}"/>
+    <hyperlink ref="G93" r:id="rId21" xr:uid="{F6F3D17A-11C3-804A-89D9-3C231334A22A}"/>
+    <hyperlink ref="G94" r:id="rId22" xr:uid="{D5F7639A-8FC0-444F-B0B1-291456215366}"/>
+    <hyperlink ref="G91" r:id="rId23" xr:uid="{40CF7C3F-7CEF-0245-8E88-7892E420529A}"/>
     <hyperlink ref="G77" r:id="rId24" xr:uid="{B2FAD3F1-82CD-564A-89EB-8DE0938B2D53}"/>
-    <hyperlink ref="G79" r:id="rId25" xr:uid="{1FE5A63E-4D12-4C4C-A566-E71804C9006E}"/>
-    <hyperlink ref="G111" r:id="rId26" xr:uid="{237E6794-0DAA-2340-869C-73B873A6D324}"/>
-    <hyperlink ref="G84" r:id="rId27" xr:uid="{67CF96A7-8792-ED4D-852A-2AD878FBA0A7}"/>
-    <hyperlink ref="G85" r:id="rId28" xr:uid="{DDD41264-2363-7B4D-BE34-303C44BC64C2}"/>
-    <hyperlink ref="G86" r:id="rId29" xr:uid="{974EC1EA-84B1-4147-9488-B123C8DAB06A}"/>
-    <hyperlink ref="G87" r:id="rId30" xr:uid="{76485F94-E942-EF4C-B260-4F0E2DC7AE4C}"/>
+    <hyperlink ref="G80" r:id="rId25" xr:uid="{1FE5A63E-4D12-4C4C-A566-E71804C9006E}"/>
+    <hyperlink ref="G112" r:id="rId26" xr:uid="{237E6794-0DAA-2340-869C-73B873A6D324}"/>
+    <hyperlink ref="G85" r:id="rId27" xr:uid="{67CF96A7-8792-ED4D-852A-2AD878FBA0A7}"/>
+    <hyperlink ref="G86" r:id="rId28" xr:uid="{DDD41264-2363-7B4D-BE34-303C44BC64C2}"/>
+    <hyperlink ref="G87" r:id="rId29" xr:uid="{974EC1EA-84B1-4147-9488-B123C8DAB06A}"/>
+    <hyperlink ref="G88" r:id="rId30" xr:uid="{76485F94-E942-EF4C-B260-4F0E2DC7AE4C}"/>
     <hyperlink ref="G55" r:id="rId31" xr:uid="{3F9A98AF-B9BE-D742-A02A-E7DAD28A7767}"/>
-    <hyperlink ref="G98" r:id="rId32" xr:uid="{259FD402-6D0D-3E43-9F73-244A8FA24539}"/>
-    <hyperlink ref="G112" r:id="rId33" xr:uid="{BE1E0B79-FD19-9E4A-8C0B-4EFB65F4A3B5}"/>
-    <hyperlink ref="G114" r:id="rId34" xr:uid="{397B14D3-85A6-954F-BE73-1F87B57618F0}"/>
-    <hyperlink ref="G115" r:id="rId35" xr:uid="{2D19773D-B9E1-CC49-A7AC-090ED1865969}"/>
-    <hyperlink ref="G116" r:id="rId36" xr:uid="{E81741AB-74EC-424F-B159-9E36EA9C2AAC}"/>
-    <hyperlink ref="G117" r:id="rId37" xr:uid="{511B6FEA-C9F1-4C40-A21D-F84B63AD6C4C}"/>
-    <hyperlink ref="G118" r:id="rId38" xr:uid="{67D718D4-7BBC-B344-A4AC-9FA1105EFD84}"/>
-    <hyperlink ref="G119" r:id="rId39" xr:uid="{22680253-E256-FE4D-B393-DDB53AB3EE72}"/>
-    <hyperlink ref="G120" r:id="rId40" xr:uid="{C1737EA1-C466-B64E-BCF7-00204A0E2AD0}"/>
-    <hyperlink ref="G121" r:id="rId41" xr:uid="{6F5E12E0-00B8-584D-BC78-83622C273538}"/>
-    <hyperlink ref="G122" r:id="rId42" xr:uid="{11B1E05E-648B-564A-94BC-978D811708BD}"/>
-    <hyperlink ref="G123" r:id="rId43" xr:uid="{5A565AA0-BF10-DF4A-A6DA-36EBE05F3C2F}"/>
-    <hyperlink ref="G124" r:id="rId44" xr:uid="{5BF47FC7-067E-C842-AA61-041B27521B5A}"/>
-    <hyperlink ref="G125" r:id="rId45" xr:uid="{E0151B3C-0DF4-1744-BE37-A53C6A17645B}"/>
-    <hyperlink ref="G126" r:id="rId46" xr:uid="{AFDB64F8-3083-6742-95DC-074AE7611AA4}"/>
-    <hyperlink ref="G127" r:id="rId47" xr:uid="{BA6B83AA-D235-604B-A845-E9B8182E0D9F}"/>
-    <hyperlink ref="G113" r:id="rId48" xr:uid="{9429C133-7A04-0B4D-A5C7-B68881A3FD4F}"/>
-    <hyperlink ref="G128" r:id="rId49" xr:uid="{536FA44E-6852-E944-AE54-FE2739629795}"/>
-    <hyperlink ref="G96" r:id="rId50" xr:uid="{C51B2851-1922-0449-92D7-27F16F0BD314}"/>
-    <hyperlink ref="G97" r:id="rId51" xr:uid="{102C7985-55DE-8F49-9440-EF311C0EB910}"/>
+    <hyperlink ref="G99" r:id="rId32" xr:uid="{259FD402-6D0D-3E43-9F73-244A8FA24539}"/>
+    <hyperlink ref="G113" r:id="rId33" xr:uid="{BE1E0B79-FD19-9E4A-8C0B-4EFB65F4A3B5}"/>
+    <hyperlink ref="G115" r:id="rId34" xr:uid="{397B14D3-85A6-954F-BE73-1F87B57618F0}"/>
+    <hyperlink ref="G116" r:id="rId35" xr:uid="{2D19773D-B9E1-CC49-A7AC-090ED1865969}"/>
+    <hyperlink ref="G117" r:id="rId36" xr:uid="{E81741AB-74EC-424F-B159-9E36EA9C2AAC}"/>
+    <hyperlink ref="G118" r:id="rId37" xr:uid="{511B6FEA-C9F1-4C40-A21D-F84B63AD6C4C}"/>
+    <hyperlink ref="G119" r:id="rId38" xr:uid="{67D718D4-7BBC-B344-A4AC-9FA1105EFD84}"/>
+    <hyperlink ref="G120" r:id="rId39" xr:uid="{22680253-E256-FE4D-B393-DDB53AB3EE72}"/>
+    <hyperlink ref="G121" r:id="rId40" xr:uid="{C1737EA1-C466-B64E-BCF7-00204A0E2AD0}"/>
+    <hyperlink ref="G122" r:id="rId41" xr:uid="{6F5E12E0-00B8-584D-BC78-83622C273538}"/>
+    <hyperlink ref="G123" r:id="rId42" xr:uid="{11B1E05E-648B-564A-94BC-978D811708BD}"/>
+    <hyperlink ref="G124" r:id="rId43" xr:uid="{5A565AA0-BF10-DF4A-A6DA-36EBE05F3C2F}"/>
+    <hyperlink ref="G125" r:id="rId44" xr:uid="{5BF47FC7-067E-C842-AA61-041B27521B5A}"/>
+    <hyperlink ref="G126" r:id="rId45" xr:uid="{E0151B3C-0DF4-1744-BE37-A53C6A17645B}"/>
+    <hyperlink ref="G127" r:id="rId46" xr:uid="{AFDB64F8-3083-6742-95DC-074AE7611AA4}"/>
+    <hyperlink ref="G128" r:id="rId47" xr:uid="{BA6B83AA-D235-604B-A845-E9B8182E0D9F}"/>
+    <hyperlink ref="G114" r:id="rId48" xr:uid="{9429C133-7A04-0B4D-A5C7-B68881A3FD4F}"/>
+    <hyperlink ref="G129" r:id="rId49" xr:uid="{536FA44E-6852-E944-AE54-FE2739629795}"/>
+    <hyperlink ref="G97" r:id="rId50" xr:uid="{C51B2851-1922-0449-92D7-27F16F0BD314}"/>
+    <hyperlink ref="G98" r:id="rId51" xr:uid="{102C7985-55DE-8F49-9440-EF311C0EB910}"/>
+    <hyperlink ref="G78" r:id="rId52" xr:uid="{B65946DF-0810-DA40-A9CD-7B7A7AD2406F}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait"/>

--- a/db/A7XLK-4401-DepartmentStore.xlsx
+++ b/db/A7XLK-4401-DepartmentStore.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11010"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11114"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A52F329-0EF3-AF48-9349-4C7E28C6C174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A5B9419-DA81-3746-AF60-9D812BA2C4DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1260" yWindow="1200" windowWidth="37900" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8580" yWindow="2060" windowWidth="37900" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Shopping" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="843">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1420" uniqueCount="850">
   <si>
     <t>title</t>
   </si>
@@ -1239,9 +1239,6 @@
   </si>
   <si>
     <t>fig/XLK-411-Shopping/AiCity-913-Samsung-2.png</t>
-  </si>
-  <si>
-    <t>fig/XLK-411-Shopping/AiCity-913-集雅社-2.jpg</t>
   </si>
   <si>
     <t>fig/XLK-411-Shopping/AiCity-913-燦坤-2.jpg</t>
@@ -3488,6 +3485,38 @@
   </si>
   <si>
     <t>fig/XLK-411-Shopping/AiCity-913-太極協會.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>145</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>旅行社</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://yytour.com.tw/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新北市林口區麗園一街6巷2號15樓之2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-77098688</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>埜雲旅行社</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-411-Shopping/AiCity-913-集雅社-2.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-411-Shopping/AiCity-913-埜雲旅行社.jpeg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3896,7 +3925,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K129"/>
+  <dimension ref="A1:K130"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="4.6640625" style="1" customWidth="1"/>
@@ -3939,13 +3968,13 @@
         <v>3</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>583</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -3953,10 +3982,10 @@
         <v>89</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>511</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>512</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>155</v>
@@ -3965,19 +3994,19 @@
         <v>198</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>604</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -3985,10 +4014,10 @@
         <v>61</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>451</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>452</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>135</v>
@@ -3997,22 +4026,22 @@
         <v>135</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J3" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>604</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -4020,10 +4049,10 @@
         <v>88</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>509</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>510</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>154</v>
@@ -4032,22 +4061,22 @@
         <v>197</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J4" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>604</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -4058,7 +4087,7 @@
         <v>225</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>228</v>
@@ -4067,22 +4096,22 @@
         <v>227</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>226</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J5" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>604</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -4090,10 +4119,10 @@
         <v>64</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>135</v>
@@ -4102,22 +4131,22 @@
         <v>186</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>241</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J6" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>604</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -4125,10 +4154,10 @@
         <v>63</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>456</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>457</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>135</v>
@@ -4137,22 +4166,22 @@
         <v>185</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J7" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="K7" s="1" t="s">
         <v>604</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -4163,7 +4192,7 @@
         <v>303</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>304</v>
@@ -4172,22 +4201,22 @@
         <v>305</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>306</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J8" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>604</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="34">
@@ -4207,22 +4236,22 @@
         <v>233</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>234</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J9" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>604</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -4230,10 +4259,10 @@
         <v>62</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>454</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>455</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>135</v>
@@ -4242,22 +4271,22 @@
         <v>184</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J10" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>604</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -4265,10 +4294,10 @@
         <v>84</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>505</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>152</v>
@@ -4277,22 +4306,22 @@
         <v>195</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -4300,10 +4329,10 @@
         <v>85</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>135</v>
@@ -4312,22 +4341,22 @@
         <v>135</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -4338,28 +4367,28 @@
         <v>336</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>337</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>335</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -4367,10 +4396,10 @@
         <v>82</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>499</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>500</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>150</v>
@@ -4379,22 +4408,22 @@
         <v>189</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>25</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J14" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="K14" s="1" t="s">
         <v>613</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -4402,10 +4431,10 @@
         <v>83</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>502</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>503</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>151</v>
@@ -4414,22 +4443,22 @@
         <v>194</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J15" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="K15" s="1" t="s">
         <v>613</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -4437,10 +4466,10 @@
         <v>87</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>507</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>508</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>153</v>
@@ -4449,22 +4478,22 @@
         <v>196</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -4472,10 +4501,10 @@
         <v>73</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>477</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>478</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>144</v>
@@ -4484,22 +4513,22 @@
         <v>189</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>21</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J17" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="K17" s="1" t="s">
         <v>609</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -4507,10 +4536,10 @@
         <v>74</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>479</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>480</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>145</v>
@@ -4519,22 +4548,22 @@
         <v>189</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>21</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J18" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="K18" s="1" t="s">
         <v>609</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -4542,10 +4571,10 @@
         <v>70</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>470</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>471</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>141</v>
@@ -4554,22 +4583,22 @@
         <v>189</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>19</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J19" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="K19" s="1" t="s">
         <v>609</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -4577,10 +4606,10 @@
         <v>72</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>475</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>476</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>143</v>
@@ -4589,22 +4618,22 @@
         <v>191</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J20" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="K20" s="1" t="s">
         <v>609</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -4612,10 +4641,10 @@
         <v>71</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>473</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>474</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>142</v>
@@ -4624,22 +4653,22 @@
         <v>191</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J21" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="K21" s="1" t="s">
         <v>609</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -4659,22 +4688,22 @@
         <v>273</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>274</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -4685,7 +4714,7 @@
         <v>258</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>259</v>
@@ -4694,27 +4723,27 @@
         <v>260</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>261</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>294</v>
@@ -4729,22 +4758,22 @@
         <v>297</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>298</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -4764,27 +4793,27 @@
         <v>278</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>279</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>299</v>
@@ -4799,33 +4828,33 @@
         <v>297</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>302</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>283</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>280</v>
@@ -4834,27 +4863,27 @@
         <v>281</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>282</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>284</v>
@@ -4869,22 +4898,22 @@
         <v>273</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>285</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -4904,27 +4933,27 @@
         <v>265</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>266</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>291</v>
@@ -4939,27 +4968,27 @@
         <v>273</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>292</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>286</v>
@@ -4974,22 +5003,22 @@
         <v>273</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>287</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -5000,28 +5029,28 @@
         <v>267</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>268</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>269</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -5029,10 +5058,10 @@
         <v>79</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>490</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>491</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>135</v>
@@ -5041,22 +5070,22 @@
         <v>193</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -5064,34 +5093,34 @@
         <v>80</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>493</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>494</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>135</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -5099,34 +5128,34 @@
         <v>81</v>
       </c>
       <c r="B35" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>496</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>497</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>135</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -5134,10 +5163,10 @@
         <v>109</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>548</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>549</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>135</v>
@@ -5146,22 +5175,22 @@
         <v>135</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="I36" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="J36" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="J36" s="1" t="s">
-        <v>599</v>
-      </c>
       <c r="K36" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -5169,10 +5198,10 @@
         <v>103</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>163</v>
@@ -5181,22 +5210,22 @@
         <v>203</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>37</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="I37" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="J37" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="J37" s="1" t="s">
-        <v>599</v>
-      </c>
       <c r="K37" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -5204,10 +5233,10 @@
         <v>104</v>
       </c>
       <c r="B38" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>540</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>541</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>164</v>
@@ -5216,22 +5245,22 @@
         <v>135</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>38</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="I38" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="J38" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="J38" s="1" t="s">
-        <v>599</v>
-      </c>
       <c r="K38" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -5239,10 +5268,10 @@
         <v>101</v>
       </c>
       <c r="B39" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>535</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>536</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>162</v>
@@ -5251,22 +5280,22 @@
         <v>202</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>35</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="I39" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="J39" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="J39" s="1" t="s">
-        <v>599</v>
-      </c>
       <c r="K39" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -5286,22 +5315,22 @@
         <v>239</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>240</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -5309,10 +5338,10 @@
         <v>50</v>
       </c>
       <c r="B41" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>429</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>430</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>125</v>
@@ -5327,16 +5356,16 @@
         <v>9</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -5344,16 +5373,16 @@
         <v>251</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D42" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>665</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>666</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>346</v>
@@ -5362,16 +5391,16 @@
         <v>9</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -5379,10 +5408,10 @@
         <v>51</v>
       </c>
       <c r="B43" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>432</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>433</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>126</v>
@@ -5397,16 +5426,16 @@
         <v>9</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -5414,10 +5443,10 @@
         <v>52</v>
       </c>
       <c r="B44" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>434</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>435</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>127</v>
@@ -5432,16 +5461,16 @@
         <v>9</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -5449,10 +5478,10 @@
         <v>53</v>
       </c>
       <c r="B45" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>436</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>437</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>128</v>
@@ -5467,16 +5496,16 @@
         <v>9</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -5484,10 +5513,10 @@
         <v>54</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>129</v>
@@ -5496,22 +5525,22 @@
         <v>181</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -5519,34 +5548,34 @@
         <v>55</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>130</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -5554,10 +5583,10 @@
         <v>107</v>
       </c>
       <c r="B48" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>546</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>547</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>167</v>
@@ -5566,22 +5595,22 @@
         <v>205</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="I48" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="J48" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="J48" s="1" t="s">
-        <v>599</v>
-      </c>
       <c r="K48" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -5592,7 +5621,7 @@
         <v>332</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>333</v>
@@ -5601,22 +5630,22 @@
         <v>334</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>335</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="I49" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="J49" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="J49" s="1" t="s">
-        <v>599</v>
-      </c>
       <c r="K49" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -5624,10 +5653,10 @@
         <v>106</v>
       </c>
       <c r="B50" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>544</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>545</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>166</v>
@@ -5636,22 +5665,22 @@
         <v>204</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>39</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="I50" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="J50" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="J50" s="1" t="s">
-        <v>599</v>
-      </c>
       <c r="K50" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -5659,10 +5688,10 @@
         <v>75</v>
       </c>
       <c r="B51" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>481</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>482</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>146</v>
@@ -5671,22 +5700,22 @@
         <v>192</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="I51" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="J51" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="J51" s="1" t="s">
-        <v>599</v>
-      </c>
       <c r="K51" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -5694,10 +5723,10 @@
         <v>76</v>
       </c>
       <c r="B52" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>484</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>485</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>147</v>
@@ -5706,22 +5735,22 @@
         <v>192</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="I52" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="J52" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="J52" s="1" t="s">
-        <v>599</v>
-      </c>
       <c r="K52" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -5729,10 +5758,10 @@
         <v>78</v>
       </c>
       <c r="B53" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="C53" s="1" t="s">
         <v>488</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>489</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>149</v>
@@ -5741,22 +5770,22 @@
         <v>192</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="I53" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="J53" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="J53" s="1" t="s">
-        <v>599</v>
-      </c>
       <c r="K53" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -5764,10 +5793,10 @@
         <v>77</v>
       </c>
       <c r="B54" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C54" s="1" t="s">
         <v>486</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>487</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>148</v>
@@ -5776,57 +5805,57 @@
         <v>192</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>23</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="I54" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="J54" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="J54" s="1" t="s">
-        <v>599</v>
-      </c>
       <c r="K54" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="55" spans="1:11">
       <c r="A55" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>696</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="C55" s="1" t="s">
         <v>697</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="D55" s="1" t="s">
         <v>698</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="E55" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="E55" s="1" t="s">
+      <c r="F55" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="G55" s="7" t="s">
         <v>700</v>
       </c>
-      <c r="F55" s="1" t="s">
-        <v>703</v>
-      </c>
-      <c r="G55" s="7" t="s">
-        <v>701</v>
-      </c>
       <c r="H55" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="I55" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="J55" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="J55" s="1" t="s">
-        <v>599</v>
-      </c>
       <c r="K55" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -5834,10 +5863,10 @@
         <v>59</v>
       </c>
       <c r="B56" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>447</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>448</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>134</v>
@@ -5852,16 +5881,16 @@
         <v>13</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I56" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="J56" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="J56" s="1" t="s">
-        <v>599</v>
-      </c>
       <c r="K56" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -5869,10 +5898,10 @@
         <v>60</v>
       </c>
       <c r="B57" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>449</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>450</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>134</v>
@@ -5887,16 +5916,16 @@
         <v>13</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I57" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="J57" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="J57" s="1" t="s">
-        <v>599</v>
-      </c>
       <c r="K57" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -5904,16 +5933,16 @@
         <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="C58" s="1" t="s">
         <v>442</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>443</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>132</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>348</v>
@@ -5922,16 +5951,16 @@
         <v>11</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I58" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="J58" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="J58" s="1" t="s">
-        <v>599</v>
-      </c>
       <c r="K58" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -5939,10 +5968,10 @@
         <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="C59" s="1" t="s">
         <v>445</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>446</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>133</v>
@@ -5957,16 +5986,16 @@
         <v>12</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I59" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="J59" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="J59" s="1" t="s">
-        <v>599</v>
-      </c>
       <c r="K59" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -5974,10 +6003,10 @@
         <v>56</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>131</v>
@@ -5992,16 +6021,16 @@
         <v>10</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I60" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="J60" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="J60" s="1" t="s">
-        <v>599</v>
-      </c>
       <c r="K60" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -6009,10 +6038,10 @@
         <v>102</v>
       </c>
       <c r="B61" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C61" s="1" t="s">
         <v>537</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>538</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>163</v>
@@ -6021,22 +6050,22 @@
         <v>203</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>36</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="I61" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="J61" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="J61" s="1" t="s">
-        <v>599</v>
-      </c>
       <c r="K61" s="1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -6044,10 +6073,10 @@
         <v>98</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>160</v>
@@ -6056,22 +6085,22 @@
         <v>177</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I62" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="J62" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="J62" s="1" t="s">
-        <v>599</v>
-      </c>
       <c r="K62" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -6079,10 +6108,10 @@
         <v>46</v>
       </c>
       <c r="B63" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>419</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>420</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>121</v>
@@ -6097,16 +6126,16 @@
         <v>5</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I63" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="J63" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="J63" s="1" t="s">
-        <v>599</v>
-      </c>
       <c r="K63" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -6114,10 +6143,10 @@
         <v>45</v>
       </c>
       <c r="B64" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>416</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>417</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>120</v>
@@ -6132,16 +6161,16 @@
         <v>4</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="I64" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="J64" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="J64" s="1" t="s">
+      <c r="K64" s="1" t="s">
         <v>599</v>
-      </c>
-      <c r="K64" s="1" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -6149,10 +6178,10 @@
         <v>47</v>
       </c>
       <c r="B65" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="C65" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>423</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>122</v>
@@ -6167,27 +6196,27 @@
         <v>6</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="I65" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="J65" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="J65" s="1" t="s">
+      <c r="K65" s="1" t="s">
         <v>599</v>
-      </c>
-      <c r="K65" s="1" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="66" spans="1:11">
       <c r="A66" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B66" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>557</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>558</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>172</v>
@@ -6196,22 +6225,22 @@
         <v>174</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="I66" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="J66" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="J66" s="1" t="s">
+      <c r="K66" s="1" t="s">
         <v>599</v>
-      </c>
-      <c r="K66" s="1" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -6219,16 +6248,16 @@
         <v>48</v>
       </c>
       <c r="B67" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C67" s="1" t="s">
         <v>424</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>425</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>123</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>344</v>
@@ -6237,16 +6266,16 @@
         <v>7</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="I67" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="J67" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="J67" s="1" t="s">
+      <c r="K67" s="1" t="s">
         <v>599</v>
-      </c>
-      <c r="K67" s="1" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -6254,16 +6283,16 @@
         <v>49</v>
       </c>
       <c r="B68" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C68" s="1" t="s">
         <v>427</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>428</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>124</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>345</v>
@@ -6272,16 +6301,16 @@
         <v>8</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="I68" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="J68" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="J68" s="1" t="s">
+      <c r="K68" s="1" t="s">
         <v>599</v>
-      </c>
-      <c r="K68" s="1" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -6289,10 +6318,10 @@
         <v>114</v>
       </c>
       <c r="B69" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="C69" s="1" t="s">
         <v>555</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>556</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>171</v>
@@ -6301,22 +6330,22 @@
         <v>207</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>42</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="I69" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="J69" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="J69" s="1" t="s">
+      <c r="K69" s="1" t="s">
         <v>599</v>
-      </c>
-      <c r="K69" s="1" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -6324,10 +6353,10 @@
         <v>113</v>
       </c>
       <c r="B70" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="C70" s="1" t="s">
         <v>553</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>554</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>170</v>
@@ -6336,22 +6365,22 @@
         <v>174</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>41</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="I70" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="J70" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="J70" s="1" t="s">
+      <c r="K70" s="1" t="s">
         <v>599</v>
-      </c>
-      <c r="K70" s="1" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -6359,10 +6388,10 @@
         <v>69</v>
       </c>
       <c r="B71" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="C71" s="1" t="s">
         <v>468</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>469</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>140</v>
@@ -6371,22 +6400,22 @@
         <v>190</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>18</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -6394,10 +6423,10 @@
         <v>68</v>
       </c>
       <c r="B72" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C72" s="1" t="s">
         <v>466</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>467</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>139</v>
@@ -6406,22 +6435,22 @@
         <v>177</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -6429,10 +6458,10 @@
         <v>65</v>
       </c>
       <c r="B73" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C73" s="1" t="s">
         <v>459</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>460</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>136</v>
@@ -6447,16 +6476,16 @@
         <v>14</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J73" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="K73" s="1" t="s">
         <v>606</v>
-      </c>
-      <c r="K73" s="1" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -6464,10 +6493,10 @@
         <v>66</v>
       </c>
       <c r="B74" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C74" s="1" t="s">
         <v>462</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>463</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>137</v>
@@ -6482,16 +6511,16 @@
         <v>15</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J74" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="K74" s="1" t="s">
         <v>606</v>
-      </c>
-      <c r="K74" s="1" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -6499,10 +6528,10 @@
         <v>67</v>
       </c>
       <c r="B75" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="C75" s="1" t="s">
         <v>464</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>465</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>138</v>
@@ -6511,1903 +6540,1935 @@
         <v>189</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>353</v>
+        <v>848</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J75" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="K75" s="1" t="s">
         <v>606</v>
-      </c>
-      <c r="K75" s="1" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="76" spans="1:11">
       <c r="A76" s="1" t="s">
-        <v>99</v>
+        <v>842</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>529</v>
+        <v>847</v>
       </c>
       <c r="C76" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>846</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>849</v>
+      </c>
+      <c r="G76" s="7" t="s">
+        <v>844</v>
+      </c>
+      <c r="H76" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="D76" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="G76" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H76" s="1" t="s">
-        <v>531</v>
-      </c>
       <c r="I76" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="J76" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="J76" s="1" t="s">
-        <v>622</v>
-      </c>
       <c r="K76" s="1" t="s">
-        <v>623</v>
+        <v>843</v>
       </c>
     </row>
     <row r="77" spans="1:11">
       <c r="A77" s="1" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>328</v>
+        <v>528</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>414</v>
+        <v>529</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>329</v>
+        <v>135</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>330</v>
+        <v>135</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="G77" s="2" t="s">
-        <v>331</v>
+        <v>370</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="I77" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="J77" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="J77" s="1" t="s">
+      <c r="K77" s="1" t="s">
         <v>622</v>
-      </c>
-      <c r="K77" s="1" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="78" spans="1:11">
       <c r="A78" s="1" t="s">
-        <v>834</v>
+        <v>112</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>835</v>
+        <v>328</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>837</v>
+        <v>413</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>838</v>
+        <v>329</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>839</v>
+        <v>330</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>842</v>
-      </c>
-      <c r="G78" s="7" t="s">
-        <v>840</v>
+        <v>381</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>836</v>
+        <v>530</v>
       </c>
       <c r="I78" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="J78" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="J78" s="1" t="s">
-        <v>622</v>
-      </c>
       <c r="K78" s="1" t="s">
-        <v>836</v>
+        <v>631</v>
       </c>
     </row>
     <row r="79" spans="1:11">
       <c r="A79" s="1" t="s">
-        <v>105</v>
+        <v>833</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>542</v>
+        <v>834</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>543</v>
+        <v>836</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>165</v>
+        <v>837</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>192</v>
+        <v>838</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>841</v>
       </c>
-      <c r="G79" s="1" t="s">
-        <v>12</v>
+      <c r="G79" s="7" t="s">
+        <v>839</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>531</v>
+        <v>835</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>627</v>
+        <v>620</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>629</v>
+        <v>835</v>
       </c>
     </row>
     <row r="80" spans="1:11">
       <c r="A80" s="1" t="s">
-        <v>242</v>
+        <v>105</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>573</v>
+        <v>541</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>574</v>
+        <v>542</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="E80" s="6" t="s">
-        <v>339</v>
+        <v>165</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>192</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="G80" s="5" t="s">
-        <v>340</v>
+        <v>840</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>566</v>
+        <v>530</v>
       </c>
       <c r="I80" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="J80" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="J80" s="1" t="s">
+      <c r="K80" s="1" t="s">
         <v>628</v>
-      </c>
-      <c r="K80" s="1" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="81" spans="1:11">
       <c r="A81" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="B81" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="C81" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="D81" s="6" t="s">
-        <v>219</v>
+      <c r="C81" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>338</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="F81" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="F81" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="G81" s="4" t="s">
-        <v>218</v>
+      <c r="G81" s="5" t="s">
+        <v>340</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="I81" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="J81" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="J81" s="1" t="s">
-        <v>628</v>
-      </c>
       <c r="K81" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="82" spans="1:11">
       <c r="A82" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>569</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="F82" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="F82" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="G82" s="2" t="s">
-        <v>214</v>
+      <c r="G82" s="4" t="s">
+        <v>218</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="I82" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="J82" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="J82" s="1" t="s">
-        <v>628</v>
-      </c>
       <c r="K82" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="83" spans="1:11">
       <c r="A83" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="B83" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>570</v>
-      </c>
-      <c r="D83" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="E83" s="6" t="s">
-        <v>571</v>
-      </c>
-      <c r="F83" s="4" t="s">
-        <v>671</v>
-      </c>
-      <c r="G83" s="4" t="s">
-        <v>213</v>
+        <v>586</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>214</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="I83" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="J83" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="J83" s="1" t="s">
-        <v>628</v>
-      </c>
       <c r="K83" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="84" spans="1:11">
       <c r="A84" s="1" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>668</v>
+        <v>224</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>669</v>
+        <v>569</v>
       </c>
       <c r="D84" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="E84" s="6" t="s">
+        <v>570</v>
+      </c>
+      <c r="F84" s="4" t="s">
         <v>670</v>
       </c>
-      <c r="E84" s="6"/>
-      <c r="F84" s="4" t="s">
-        <v>672</v>
-      </c>
-      <c r="G84" s="1" t="s">
-        <v>12</v>
+      <c r="G84" s="4" t="s">
+        <v>213</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="I84" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="J84" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="J84" s="1" t="s">
-        <v>628</v>
-      </c>
       <c r="K84" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="85" spans="1:11">
       <c r="A85" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>667</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="D85" s="6" t="s">
+        <v>669</v>
+      </c>
+      <c r="E85" s="6"/>
+      <c r="F85" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="J85" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11">
+      <c r="A86" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B85" s="4" t="s">
+      <c r="B86" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="C86" s="4" t="s">
         <v>674</v>
       </c>
-      <c r="C85" s="4" t="s">
+      <c r="D86" s="6" t="s">
         <v>675</v>
       </c>
-      <c r="D85" s="6" t="s">
+      <c r="E86" s="6" t="s">
         <v>676</v>
       </c>
-      <c r="E85" s="6" t="s">
+      <c r="F86" s="4" t="s">
         <v>677</v>
       </c>
-      <c r="F85" s="4" t="s">
+      <c r="G86" s="8" t="s">
+        <v>672</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="J86" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" ht="34">
+      <c r="A87" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>680</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>681</v>
+      </c>
+      <c r="D87" s="9" t="s">
+        <v>679</v>
+      </c>
+      <c r="E87" s="6" t="s">
+        <v>682</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>683</v>
+      </c>
+      <c r="G87" s="8" t="s">
         <v>678</v>
       </c>
-      <c r="G85" s="8" t="s">
-        <v>673</v>
-      </c>
-      <c r="H85" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="I85" s="1" t="s">
+      <c r="H87" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="J87" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="J85" s="1" t="s">
-        <v>628</v>
-      </c>
-      <c r="K85" s="1" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" ht="34">
-      <c r="A86" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="B86" s="4" t="s">
-        <v>681</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>682</v>
-      </c>
-      <c r="D86" s="9" t="s">
-        <v>680</v>
-      </c>
-      <c r="E86" s="6" t="s">
-        <v>683</v>
-      </c>
-      <c r="F86" s="4" t="s">
-        <v>684</v>
-      </c>
-      <c r="G86" s="8" t="s">
-        <v>679</v>
-      </c>
-      <c r="H86" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="I86" s="1" t="s">
-        <v>627</v>
-      </c>
-      <c r="J86" s="1" t="s">
-        <v>628</v>
-      </c>
-      <c r="K86" s="1" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11">
-      <c r="A87" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="B87" s="4" t="s">
-        <v>686</v>
-      </c>
-      <c r="C87" s="4" t="s">
-        <v>689</v>
-      </c>
-      <c r="D87" s="6" t="s">
-        <v>688</v>
-      </c>
-      <c r="E87" s="6" t="s">
-        <v>677</v>
-      </c>
-      <c r="F87" s="4" t="s">
-        <v>687</v>
-      </c>
-      <c r="G87" s="8" t="s">
-        <v>685</v>
-      </c>
-      <c r="H87" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="I87" s="1" t="s">
-        <v>627</v>
-      </c>
-      <c r="J87" s="1" t="s">
-        <v>628</v>
-      </c>
       <c r="K87" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="88" spans="1:11">
       <c r="A88" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>695</v>
+        <v>676</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="G88" s="8" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="I88" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="J88" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="J88" s="1" t="s">
-        <v>628</v>
-      </c>
       <c r="K88" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="89" spans="1:11">
       <c r="A89" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>564</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="E89" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>691</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>692</v>
+      </c>
+      <c r="E89" s="6" t="s">
+        <v>694</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>689</v>
+      </c>
+      <c r="G89" s="8" t="s">
+        <v>693</v>
+      </c>
+      <c r="H89" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="F89" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="G89" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="H89" s="1" t="s">
-        <v>566</v>
-      </c>
       <c r="I89" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="J89" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="J89" s="1" t="s">
-        <v>628</v>
-      </c>
       <c r="K89" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="90" spans="1:11">
       <c r="A90" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>568</v>
+        <v>563</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>564</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>211</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="I90" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="J90" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="J90" s="1" t="s">
-        <v>628</v>
-      </c>
       <c r="K90" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="91" spans="1:11">
       <c r="A91" s="1" t="s">
-        <v>597</v>
+        <v>223</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>323</v>
+        <v>566</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>325</v>
+        <v>567</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="G91" s="2" t="s">
-        <v>324</v>
+        <v>387</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>307</v>
+        <v>565</v>
       </c>
       <c r="I91" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="J91" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="J91" s="1" t="s">
-        <v>636</v>
-      </c>
       <c r="K91" s="1" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
     </row>
     <row r="92" spans="1:11">
       <c r="A92" s="1" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>310</v>
+        <v>327</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="H92" s="1" t="s">
         <v>307</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="J92" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="K92" s="1" t="s">
         <v>636</v>
-      </c>
-      <c r="K92" s="1" t="s">
-        <v>637</v>
       </c>
     </row>
     <row r="93" spans="1:11">
       <c r="A93" s="1" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="H93" s="1" t="s">
         <v>307</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="J93" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="K93" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="K93" s="1" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" ht="34">
+    </row>
+    <row r="94" spans="1:11">
       <c r="A94" s="1" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>320</v>
+        <v>313</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>314</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H94" s="1" t="s">
         <v>307</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="J94" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="K94" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="K94" s="1" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11">
+    </row>
+    <row r="95" spans="1:11" ht="34">
       <c r="A95" s="1" t="s">
-        <v>212</v>
+        <v>595</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>561</v>
+        <v>319</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>320</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>209</v>
+        <v>321</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>562</v>
+        <v>322</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>386</v>
+        <v>408</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>208</v>
+        <v>318</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>560</v>
+        <v>307</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>560</v>
+        <v>636</v>
       </c>
     </row>
     <row r="96" spans="1:11">
       <c r="A96" s="1" t="s">
-        <v>586</v>
+        <v>212</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>425</v>
+        <v>560</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>209</v>
       </c>
       <c r="E96" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="H96" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="F96" s="1" t="s">
-        <v>825</v>
-      </c>
-      <c r="G96" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="H96" s="1" t="s">
-        <v>560</v>
-      </c>
       <c r="I96" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="97" spans="1:11">
       <c r="A97" s="1" t="s">
-        <v>819</v>
+        <v>585</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>820</v>
+        <v>115</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>822</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>823</v>
+        <v>424</v>
       </c>
       <c r="E97" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="F97" s="1" t="s">
         <v>824</v>
       </c>
-      <c r="F97" s="1" t="s">
-        <v>826</v>
-      </c>
-      <c r="G97" s="7" t="s">
-        <v>827</v>
+      <c r="G97" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>818</v>
+        <v>559</v>
       </c>
     </row>
     <row r="98" spans="1:11">
       <c r="A98" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>819</v>
+      </c>
+      <c r="C98" s="1" t="s">
         <v>821</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>828</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>829</v>
-      </c>
       <c r="D98" s="1" t="s">
-        <v>830</v>
+        <v>822</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>832</v>
+        <v>825</v>
       </c>
       <c r="G98" s="7" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="99" spans="1:11">
       <c r="A99" s="1" t="s">
-        <v>704</v>
+        <v>820</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>707</v>
+        <v>827</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>708</v>
+        <v>828</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>709</v>
+        <v>829</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>244</v>
+        <v>830</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>711</v>
+        <v>831</v>
       </c>
       <c r="G99" s="7" t="s">
-        <v>710</v>
+        <v>832</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>706</v>
+        <v>559</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>705</v>
+        <v>632</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>706</v>
+        <v>817</v>
       </c>
     </row>
     <row r="100" spans="1:11">
       <c r="A100" s="1" t="s">
-        <v>90</v>
+        <v>703</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>650</v>
+        <v>706</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>513</v>
+        <v>707</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>135</v>
+        <v>708</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>135</v>
+        <v>244</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="G100" s="1" t="s">
-        <v>12</v>
+        <v>710</v>
+      </c>
+      <c r="G100" s="7" t="s">
+        <v>709</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>514</v>
+        <v>705</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>612</v>
+        <v>626</v>
       </c>
       <c r="J100" s="1" t="s">
-        <v>617</v>
+        <v>704</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>618</v>
+        <v>705</v>
       </c>
     </row>
     <row r="101" spans="1:11">
       <c r="A101" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>515</v>
+        <v>649</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>135</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>199</v>
+        <v>135</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>644</v>
+        <v>651</v>
       </c>
       <c r="G101" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="J101" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="K101" s="1" t="s">
         <v>617</v>
-      </c>
-      <c r="K101" s="1" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="102" spans="1:11">
       <c r="A102" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>524</v>
+        <v>514</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>135</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>520</v>
+        <v>12</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="J102" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="K102" s="1" t="s">
         <v>617</v>
-      </c>
-      <c r="K102" s="1" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="103" spans="1:11">
       <c r="A103" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>651</v>
+        <v>643</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>29</v>
+        <v>519</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="J103" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="K103" s="1" t="s">
         <v>617</v>
-      </c>
-      <c r="K103" s="1" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="104" spans="1:11">
       <c r="A104" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>30</v>
+        <v>516</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>368</v>
+        <v>650</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="J104" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="K104" s="1" t="s">
         <v>617</v>
-      </c>
-      <c r="K104" s="1" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="105" spans="1:11">
       <c r="A105" s="1" t="s">
-        <v>252</v>
+        <v>95</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>243</v>
+        <v>30</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>578</v>
+        <v>522</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>246</v>
+        <v>158</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>244</v>
+        <v>177</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="G105" s="2" t="s">
-        <v>245</v>
+        <v>367</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="J105" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="K105" s="1" t="s">
         <v>617</v>
-      </c>
-      <c r="K105" s="1" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="106" spans="1:11">
       <c r="A106" s="1" t="s">
-        <v>94</v>
+        <v>252</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>521</v>
+        <v>243</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>522</v>
+        <v>577</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>157</v>
+        <v>246</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>135</v>
+        <v>244</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>644</v>
-      </c>
-      <c r="G106" s="1" t="s">
-        <v>520</v>
+        <v>394</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="J106" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="K106" s="1" t="s">
         <v>617</v>
-      </c>
-      <c r="K106" s="1" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="107" spans="1:11">
       <c r="A107" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>653</v>
+        <v>520</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>135</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="J107" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="K107" s="1" t="s">
         <v>617</v>
-      </c>
-      <c r="K107" s="1" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="108" spans="1:11">
       <c r="A108" s="1" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>532</v>
+        <v>652</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>533</v>
+        <v>518</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>161</v>
+        <v>135</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>534</v>
+        <v>135</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>372</v>
+        <v>643</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>34</v>
+        <v>519</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>531</v>
+        <v>513</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="J108" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="K108" s="1" t="s">
         <v>617</v>
-      </c>
-      <c r="K108" s="1" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="109" spans="1:11">
       <c r="A109" s="1" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>550</v>
+        <v>531</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>551</v>
+        <v>532</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>206</v>
+        <v>533</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>659</v>
+        <v>371</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="J109" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>631</v>
+        <v>619</v>
       </c>
     </row>
     <row r="110" spans="1:11">
       <c r="A110" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>413</v>
+        <v>550</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>135</v>
+        <v>206</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>381</v>
+        <v>658</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>520</v>
+        <v>40</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="J110" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="111" spans="1:11">
       <c r="A111" s="1" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>526</v>
+        <v>551</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>527</v>
+        <v>412</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>198</v>
+        <v>135</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>32</v>
+        <v>519</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>421</v>
+        <v>530</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="J111" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>619</v>
+        <v>630</v>
       </c>
     </row>
     <row r="112" spans="1:11">
       <c r="A112" s="1" t="s">
-        <v>658</v>
+        <v>97</v>
       </c>
       <c r="B112" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="G112" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H112" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="I112" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="J112" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="K112" s="1" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11">
+      <c r="A113" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="C113" s="1" t="s">
         <v>662</v>
       </c>
-      <c r="C112" s="1" t="s">
+      <c r="D113" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="D112" s="1" t="s">
-        <v>664</v>
-      </c>
-      <c r="F112" s="1" t="s">
+      <c r="F113" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="G113" s="7" t="s">
         <v>660</v>
       </c>
-      <c r="G112" s="7" t="s">
-        <v>661</v>
-      </c>
-      <c r="H112" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="I112" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="J112" s="1" t="s">
-        <v>604</v>
-      </c>
-      <c r="K112" s="1" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11" ht="17">
-      <c r="A113" s="10" t="s">
-        <v>715</v>
-      </c>
-      <c r="B113" s="11" t="s">
-        <v>716</v>
-      </c>
-      <c r="C113" s="12" t="s">
-        <v>717</v>
-      </c>
-      <c r="D113" s="11" t="s">
-        <v>718</v>
-      </c>
-      <c r="E113" s="13" t="s">
-        <v>719</v>
-      </c>
-      <c r="F113" s="11" t="s">
-        <v>720</v>
-      </c>
-      <c r="G113" s="14" t="s">
-        <v>721</v>
-      </c>
       <c r="H113" s="1" t="s">
-        <v>714</v>
+        <v>430</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>627</v>
+        <v>597</v>
       </c>
       <c r="J113" s="1" t="s">
-        <v>712</v>
+        <v>603</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>713</v>
+        <v>601</v>
       </c>
     </row>
     <row r="114" spans="1:11" ht="17">
       <c r="A114" s="10" t="s">
-        <v>722</v>
-      </c>
-      <c r="B114" s="15" t="s">
-        <v>811</v>
-      </c>
-      <c r="C114" s="15" t="s">
-        <v>810</v>
+        <v>714</v>
+      </c>
+      <c r="B114" s="11" t="s">
+        <v>715</v>
+      </c>
+      <c r="C114" s="12" t="s">
+        <v>716</v>
       </c>
       <c r="D114" s="11" t="s">
-        <v>812</v>
+        <v>717</v>
       </c>
       <c r="E114" s="13" t="s">
+        <v>718</v>
+      </c>
+      <c r="F114" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="F114" s="11" t="s">
-        <v>723</v>
-      </c>
       <c r="G114" s="14" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="J114" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="K114" s="1" t="s">
         <v>712</v>
-      </c>
-      <c r="K114" s="1" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="115" spans="1:11" ht="17">
       <c r="A115" s="10" t="s">
-        <v>725</v>
-      </c>
-      <c r="B115" s="11" t="s">
-        <v>726</v>
-      </c>
-      <c r="C115" s="12" t="s">
-        <v>727</v>
+        <v>721</v>
+      </c>
+      <c r="B115" s="15" t="s">
+        <v>810</v>
+      </c>
+      <c r="C115" s="15" t="s">
+        <v>809</v>
       </c>
       <c r="D115" s="11" t="s">
-        <v>728</v>
+        <v>811</v>
       </c>
       <c r="E115" s="13" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="F115" s="11" t="s">
-        <v>729</v>
+        <v>722</v>
       </c>
       <c r="G115" s="14" t="s">
-        <v>730</v>
+        <v>723</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="J115" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="K115" s="1" t="s">
         <v>712</v>
-      </c>
-      <c r="K115" s="1" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="116" spans="1:11" ht="17">
       <c r="A116" s="10" t="s">
-        <v>731</v>
+        <v>724</v>
       </c>
       <c r="B116" s="11" t="s">
-        <v>732</v>
+        <v>725</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>733</v>
+        <v>726</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>734</v>
+        <v>727</v>
       </c>
       <c r="E116" s="13" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="F116" s="11" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="G116" s="14" t="s">
-        <v>736</v>
+        <v>729</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="J116" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="K116" s="1" t="s">
         <v>712</v>
-      </c>
-      <c r="K116" s="1" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="117" spans="1:11" ht="17">
       <c r="A117" s="10" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="B117" s="11" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="E117" s="13" t="s">
-        <v>741</v>
+        <v>718</v>
       </c>
       <c r="F117" s="11" t="s">
-        <v>742</v>
+        <v>734</v>
       </c>
       <c r="G117" s="14" t="s">
-        <v>743</v>
+        <v>735</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="J117" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="K117" s="1" t="s">
         <v>712</v>
-      </c>
-      <c r="K117" s="1" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="118" spans="1:11" ht="17">
       <c r="A118" s="10" t="s">
-        <v>744</v>
+        <v>736</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>745</v>
+        <v>737</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>746</v>
+        <v>738</v>
       </c>
       <c r="D118" s="11" t="s">
-        <v>747</v>
+        <v>739</v>
       </c>
       <c r="E118" s="13" t="s">
-        <v>719</v>
+        <v>740</v>
       </c>
       <c r="F118" s="11" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="G118" s="14" t="s">
-        <v>749</v>
+        <v>742</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="J118" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="K118" s="1" t="s">
         <v>712</v>
-      </c>
-      <c r="K118" s="1" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="119" spans="1:11" ht="17">
       <c r="A119" s="10" t="s">
-        <v>750</v>
+        <v>743</v>
       </c>
       <c r="B119" s="11" t="s">
-        <v>751</v>
+        <v>744</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="D119" s="11" t="s">
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="E119" s="13" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="F119" s="11" t="s">
-        <v>754</v>
+        <v>747</v>
       </c>
       <c r="G119" s="14" t="s">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="J119" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="K119" s="1" t="s">
         <v>712</v>
-      </c>
-      <c r="K119" s="1" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="120" spans="1:11" ht="17">
       <c r="A120" s="10" t="s">
-        <v>756</v>
+        <v>749</v>
       </c>
       <c r="B120" s="11" t="s">
-        <v>757</v>
+        <v>750</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>758</v>
+        <v>751</v>
       </c>
       <c r="D120" s="11" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="E120" s="13" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="F120" s="11" t="s">
-        <v>760</v>
+        <v>753</v>
       </c>
       <c r="G120" s="14" t="s">
-        <v>761</v>
+        <v>754</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="J120" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="K120" s="1" t="s">
         <v>712</v>
-      </c>
-      <c r="K120" s="1" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="121" spans="1:11" ht="17">
       <c r="A121" s="10" t="s">
-        <v>762</v>
+        <v>755</v>
       </c>
       <c r="B121" s="11" t="s">
-        <v>763</v>
+        <v>756</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>764</v>
+        <v>757</v>
       </c>
       <c r="D121" s="11" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="E121" s="13" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="F121" s="11" t="s">
-        <v>766</v>
+        <v>759</v>
       </c>
       <c r="G121" s="14" t="s">
-        <v>767</v>
+        <v>760</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="J121" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="K121" s="1" t="s">
         <v>712</v>
-      </c>
-      <c r="K121" s="1" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="122" spans="1:11" ht="17">
       <c r="A122" s="10" t="s">
-        <v>768</v>
+        <v>761</v>
       </c>
       <c r="B122" s="11" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>770</v>
+        <v>763</v>
       </c>
       <c r="D122" s="11" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
       <c r="E122" s="13" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="F122" s="11" t="s">
-        <v>772</v>
+        <v>765</v>
       </c>
       <c r="G122" s="14" t="s">
-        <v>773</v>
+        <v>766</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="I122" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="J122" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="K122" s="1" t="s">
         <v>712</v>
-      </c>
-      <c r="K122" s="1" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="123" spans="1:11" ht="17">
       <c r="A123" s="10" t="s">
-        <v>774</v>
+        <v>767</v>
       </c>
       <c r="B123" s="11" t="s">
-        <v>775</v>
+        <v>768</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="D123" s="11" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="E123" s="13" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="F123" s="11" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="G123" s="14" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="I123" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="J123" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="K123" s="1" t="s">
         <v>712</v>
-      </c>
-      <c r="K123" s="1" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="124" spans="1:11" ht="17">
       <c r="A124" s="10" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="B124" s="11" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="D124" s="11" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="E124" s="13" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="F124" s="11" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="G124" s="14" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="J124" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="K124" s="1" t="s">
         <v>712</v>
-      </c>
-      <c r="K124" s="1" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="125" spans="1:11" ht="17">
       <c r="A125" s="10" t="s">
-        <v>786</v>
+        <v>779</v>
       </c>
       <c r="B125" s="11" t="s">
-        <v>787</v>
+        <v>780</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="D125" s="11" t="s">
-        <v>789</v>
+        <v>782</v>
       </c>
       <c r="E125" s="13" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="F125" s="11" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="G125" s="14" t="s">
-        <v>791</v>
+        <v>784</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="I125" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="J125" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="K125" s="1" t="s">
         <v>712</v>
-      </c>
-      <c r="K125" s="1" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="126" spans="1:11" ht="17">
       <c r="A126" s="10" t="s">
-        <v>792</v>
+        <v>785</v>
       </c>
       <c r="B126" s="11" t="s">
-        <v>793</v>
+        <v>786</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="D126" s="11" t="s">
-        <v>795</v>
+        <v>788</v>
       </c>
       <c r="E126" s="13" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="F126" s="11" t="s">
-        <v>796</v>
+        <v>789</v>
       </c>
       <c r="G126" s="14" t="s">
-        <v>797</v>
+        <v>790</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="J126" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="K126" s="1" t="s">
         <v>712</v>
-      </c>
-      <c r="K126" s="1" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="127" spans="1:11" ht="17">
       <c r="A127" s="10" t="s">
-        <v>798</v>
+        <v>791</v>
       </c>
       <c r="B127" s="11" t="s">
-        <v>799</v>
+        <v>792</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>800</v>
+        <v>793</v>
       </c>
       <c r="D127" s="11" t="s">
-        <v>801</v>
+        <v>794</v>
       </c>
       <c r="E127" s="13" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="F127" s="11" t="s">
-        <v>802</v>
+        <v>795</v>
       </c>
       <c r="G127" s="14" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="I127" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="J127" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="K127" s="1" t="s">
         <v>712</v>
-      </c>
-      <c r="K127" s="1" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="128" spans="1:11" ht="17">
       <c r="A128" s="10" t="s">
-        <v>804</v>
+        <v>797</v>
       </c>
       <c r="B128" s="11" t="s">
-        <v>805</v>
+        <v>798</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>806</v>
+        <v>799</v>
       </c>
       <c r="D128" s="11" t="s">
-        <v>807</v>
+        <v>800</v>
       </c>
       <c r="E128" s="13" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="F128" s="11" t="s">
-        <v>808</v>
+        <v>801</v>
       </c>
       <c r="G128" s="14" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="J128" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="K128" s="1" t="s">
         <v>712</v>
-      </c>
-      <c r="K128" s="1" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="129" spans="1:11" ht="17">
       <c r="A129" s="10" t="s">
+        <v>803</v>
+      </c>
+      <c r="B129" s="11" t="s">
+        <v>804</v>
+      </c>
+      <c r="C129" s="12" t="s">
+        <v>805</v>
+      </c>
+      <c r="D129" s="11" t="s">
+        <v>806</v>
+      </c>
+      <c r="E129" s="13" t="s">
+        <v>718</v>
+      </c>
+      <c r="F129" s="11" t="s">
+        <v>807</v>
+      </c>
+      <c r="G129" s="14" t="s">
+        <v>808</v>
+      </c>
+      <c r="H129" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="I129" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="J129" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="K129" s="1" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" ht="17">
+      <c r="A130" s="10" t="s">
+        <v>812</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>813</v>
       </c>
-      <c r="B129" s="1" t="s">
+      <c r="C130" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="D130" s="1" t="s">
         <v>814</v>
       </c>
-      <c r="C129" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="D129" s="1" t="s">
+      <c r="E130" s="13" t="s">
+        <v>718</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>816</v>
+      </c>
+      <c r="G130" s="7" t="s">
         <v>815</v>
       </c>
-      <c r="E129" s="13" t="s">
-        <v>719</v>
-      </c>
-      <c r="F129" s="1" t="s">
-        <v>817</v>
-      </c>
-      <c r="G129" s="7" t="s">
-        <v>816</v>
-      </c>
-      <c r="H129" s="1" t="s">
-        <v>714</v>
-      </c>
-      <c r="I129" s="1" t="s">
-        <v>627</v>
-      </c>
-      <c r="J129" s="1" t="s">
+      <c r="H130" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="I130" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="J130" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="K130" s="1" t="s">
         <v>712</v>
       </c>
-      <c r="K129" s="1" t="s">
-        <v>713</v>
-      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K111">
-    <sortCondition ref="J2:J111"/>
-    <sortCondition ref="K2:K111"/>
-    <sortCondition ref="B2:B111"/>
-    <sortCondition ref="C2:C111"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K112">
+    <sortCondition ref="J2:J112"/>
+    <sortCondition ref="K2:K112"/>
+    <sortCondition ref="B2:B112"/>
+    <sortCondition ref="C2:C112"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="2">
@@ -8419,13 +8480,13 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="G95" r:id="rId1" xr:uid="{A39B8C40-8D45-EB49-A4FC-B32617C3743A}"/>
-    <hyperlink ref="G82" r:id="rId2" xr:uid="{B5DCC527-C34A-A84A-863F-C7614151FE6F}"/>
+    <hyperlink ref="G96" r:id="rId1" xr:uid="{A39B8C40-8D45-EB49-A4FC-B32617C3743A}"/>
+    <hyperlink ref="G83" r:id="rId2" xr:uid="{B5DCC527-C34A-A84A-863F-C7614151FE6F}"/>
     <hyperlink ref="G5" r:id="rId3" xr:uid="{9F3F15C4-C0FD-AE4F-A261-C94D2C5C5CDD}"/>
     <hyperlink ref="G9" r:id="rId4" xr:uid="{57110EDF-FEA5-304D-BC8D-B61106C21880}"/>
     <hyperlink ref="G40" r:id="rId5" location="sale_active" xr:uid="{730FA5EB-C91B-144D-A783-4D831224B6A9}"/>
     <hyperlink ref="G6" r:id="rId6" xr:uid="{1F8F556A-7472-764F-A198-D7F42EFCC387}"/>
-    <hyperlink ref="G105" r:id="rId7" xr:uid="{D0E463C4-46AF-0146-87CD-46876FB5CA0D}"/>
+    <hyperlink ref="G106" r:id="rId7" xr:uid="{D0E463C4-46AF-0146-87CD-46876FB5CA0D}"/>
     <hyperlink ref="G23" r:id="rId8" xr:uid="{DF8FD8B1-A50B-9E4E-9410-150C09502DAB}"/>
     <hyperlink ref="G29" r:id="rId9" xr:uid="{FF011359-39BB-A040-AED2-D2D90A217A10}"/>
     <hyperlink ref="G32" r:id="rId10" xr:uid="{52BA0BCD-A138-3A42-93E9-9408D0B6CD41}"/>
@@ -8438,39 +8499,40 @@
     <hyperlink ref="G24" r:id="rId17" xr:uid="{645725E7-FD7F-7841-BD5D-4F55FBCDAB8D}"/>
     <hyperlink ref="G26" r:id="rId18" xr:uid="{D8E83196-8EED-474F-A39D-4B8A53066F90}"/>
     <hyperlink ref="G8" r:id="rId19" xr:uid="{D8074921-21AA-094E-B1E8-1A2B5D8215AB}"/>
-    <hyperlink ref="G92" r:id="rId20" xr:uid="{67DB94DD-4F2A-2B47-90EF-FED3ED8F2017}"/>
-    <hyperlink ref="G93" r:id="rId21" xr:uid="{F6F3D17A-11C3-804A-89D9-3C231334A22A}"/>
-    <hyperlink ref="G94" r:id="rId22" xr:uid="{D5F7639A-8FC0-444F-B0B1-291456215366}"/>
-    <hyperlink ref="G91" r:id="rId23" xr:uid="{40CF7C3F-7CEF-0245-8E88-7892E420529A}"/>
-    <hyperlink ref="G77" r:id="rId24" xr:uid="{B2FAD3F1-82CD-564A-89EB-8DE0938B2D53}"/>
-    <hyperlink ref="G80" r:id="rId25" xr:uid="{1FE5A63E-4D12-4C4C-A566-E71804C9006E}"/>
-    <hyperlink ref="G112" r:id="rId26" xr:uid="{237E6794-0DAA-2340-869C-73B873A6D324}"/>
-    <hyperlink ref="G85" r:id="rId27" xr:uid="{67CF96A7-8792-ED4D-852A-2AD878FBA0A7}"/>
-    <hyperlink ref="G86" r:id="rId28" xr:uid="{DDD41264-2363-7B4D-BE34-303C44BC64C2}"/>
-    <hyperlink ref="G87" r:id="rId29" xr:uid="{974EC1EA-84B1-4147-9488-B123C8DAB06A}"/>
-    <hyperlink ref="G88" r:id="rId30" xr:uid="{76485F94-E942-EF4C-B260-4F0E2DC7AE4C}"/>
+    <hyperlink ref="G93" r:id="rId20" xr:uid="{67DB94DD-4F2A-2B47-90EF-FED3ED8F2017}"/>
+    <hyperlink ref="G94" r:id="rId21" xr:uid="{F6F3D17A-11C3-804A-89D9-3C231334A22A}"/>
+    <hyperlink ref="G95" r:id="rId22" xr:uid="{D5F7639A-8FC0-444F-B0B1-291456215366}"/>
+    <hyperlink ref="G92" r:id="rId23" xr:uid="{40CF7C3F-7CEF-0245-8E88-7892E420529A}"/>
+    <hyperlink ref="G78" r:id="rId24" xr:uid="{B2FAD3F1-82CD-564A-89EB-8DE0938B2D53}"/>
+    <hyperlink ref="G81" r:id="rId25" xr:uid="{1FE5A63E-4D12-4C4C-A566-E71804C9006E}"/>
+    <hyperlink ref="G113" r:id="rId26" xr:uid="{237E6794-0DAA-2340-869C-73B873A6D324}"/>
+    <hyperlink ref="G86" r:id="rId27" xr:uid="{67CF96A7-8792-ED4D-852A-2AD878FBA0A7}"/>
+    <hyperlink ref="G87" r:id="rId28" xr:uid="{DDD41264-2363-7B4D-BE34-303C44BC64C2}"/>
+    <hyperlink ref="G88" r:id="rId29" xr:uid="{974EC1EA-84B1-4147-9488-B123C8DAB06A}"/>
+    <hyperlink ref="G89" r:id="rId30" xr:uid="{76485F94-E942-EF4C-B260-4F0E2DC7AE4C}"/>
     <hyperlink ref="G55" r:id="rId31" xr:uid="{3F9A98AF-B9BE-D742-A02A-E7DAD28A7767}"/>
-    <hyperlink ref="G99" r:id="rId32" xr:uid="{259FD402-6D0D-3E43-9F73-244A8FA24539}"/>
-    <hyperlink ref="G113" r:id="rId33" xr:uid="{BE1E0B79-FD19-9E4A-8C0B-4EFB65F4A3B5}"/>
-    <hyperlink ref="G115" r:id="rId34" xr:uid="{397B14D3-85A6-954F-BE73-1F87B57618F0}"/>
-    <hyperlink ref="G116" r:id="rId35" xr:uid="{2D19773D-B9E1-CC49-A7AC-090ED1865969}"/>
-    <hyperlink ref="G117" r:id="rId36" xr:uid="{E81741AB-74EC-424F-B159-9E36EA9C2AAC}"/>
-    <hyperlink ref="G118" r:id="rId37" xr:uid="{511B6FEA-C9F1-4C40-A21D-F84B63AD6C4C}"/>
-    <hyperlink ref="G119" r:id="rId38" xr:uid="{67D718D4-7BBC-B344-A4AC-9FA1105EFD84}"/>
-    <hyperlink ref="G120" r:id="rId39" xr:uid="{22680253-E256-FE4D-B393-DDB53AB3EE72}"/>
-    <hyperlink ref="G121" r:id="rId40" xr:uid="{C1737EA1-C466-B64E-BCF7-00204A0E2AD0}"/>
-    <hyperlink ref="G122" r:id="rId41" xr:uid="{6F5E12E0-00B8-584D-BC78-83622C273538}"/>
-    <hyperlink ref="G123" r:id="rId42" xr:uid="{11B1E05E-648B-564A-94BC-978D811708BD}"/>
-    <hyperlink ref="G124" r:id="rId43" xr:uid="{5A565AA0-BF10-DF4A-A6DA-36EBE05F3C2F}"/>
-    <hyperlink ref="G125" r:id="rId44" xr:uid="{5BF47FC7-067E-C842-AA61-041B27521B5A}"/>
-    <hyperlink ref="G126" r:id="rId45" xr:uid="{E0151B3C-0DF4-1744-BE37-A53C6A17645B}"/>
-    <hyperlink ref="G127" r:id="rId46" xr:uid="{AFDB64F8-3083-6742-95DC-074AE7611AA4}"/>
-    <hyperlink ref="G128" r:id="rId47" xr:uid="{BA6B83AA-D235-604B-A845-E9B8182E0D9F}"/>
-    <hyperlink ref="G114" r:id="rId48" xr:uid="{9429C133-7A04-0B4D-A5C7-B68881A3FD4F}"/>
-    <hyperlink ref="G129" r:id="rId49" xr:uid="{536FA44E-6852-E944-AE54-FE2739629795}"/>
-    <hyperlink ref="G97" r:id="rId50" xr:uid="{C51B2851-1922-0449-92D7-27F16F0BD314}"/>
-    <hyperlink ref="G98" r:id="rId51" xr:uid="{102C7985-55DE-8F49-9440-EF311C0EB910}"/>
-    <hyperlink ref="G78" r:id="rId52" xr:uid="{B65946DF-0810-DA40-A9CD-7B7A7AD2406F}"/>
+    <hyperlink ref="G100" r:id="rId32" xr:uid="{259FD402-6D0D-3E43-9F73-244A8FA24539}"/>
+    <hyperlink ref="G114" r:id="rId33" xr:uid="{BE1E0B79-FD19-9E4A-8C0B-4EFB65F4A3B5}"/>
+    <hyperlink ref="G116" r:id="rId34" xr:uid="{397B14D3-85A6-954F-BE73-1F87B57618F0}"/>
+    <hyperlink ref="G117" r:id="rId35" xr:uid="{2D19773D-B9E1-CC49-A7AC-090ED1865969}"/>
+    <hyperlink ref="G118" r:id="rId36" xr:uid="{E81741AB-74EC-424F-B159-9E36EA9C2AAC}"/>
+    <hyperlink ref="G119" r:id="rId37" xr:uid="{511B6FEA-C9F1-4C40-A21D-F84B63AD6C4C}"/>
+    <hyperlink ref="G120" r:id="rId38" xr:uid="{67D718D4-7BBC-B344-A4AC-9FA1105EFD84}"/>
+    <hyperlink ref="G121" r:id="rId39" xr:uid="{22680253-E256-FE4D-B393-DDB53AB3EE72}"/>
+    <hyperlink ref="G122" r:id="rId40" xr:uid="{C1737EA1-C466-B64E-BCF7-00204A0E2AD0}"/>
+    <hyperlink ref="G123" r:id="rId41" xr:uid="{6F5E12E0-00B8-584D-BC78-83622C273538}"/>
+    <hyperlink ref="G124" r:id="rId42" xr:uid="{11B1E05E-648B-564A-94BC-978D811708BD}"/>
+    <hyperlink ref="G125" r:id="rId43" xr:uid="{5A565AA0-BF10-DF4A-A6DA-36EBE05F3C2F}"/>
+    <hyperlink ref="G126" r:id="rId44" xr:uid="{5BF47FC7-067E-C842-AA61-041B27521B5A}"/>
+    <hyperlink ref="G127" r:id="rId45" xr:uid="{E0151B3C-0DF4-1744-BE37-A53C6A17645B}"/>
+    <hyperlink ref="G128" r:id="rId46" xr:uid="{AFDB64F8-3083-6742-95DC-074AE7611AA4}"/>
+    <hyperlink ref="G129" r:id="rId47" xr:uid="{BA6B83AA-D235-604B-A845-E9B8182E0D9F}"/>
+    <hyperlink ref="G115" r:id="rId48" xr:uid="{9429C133-7A04-0B4D-A5C7-B68881A3FD4F}"/>
+    <hyperlink ref="G130" r:id="rId49" xr:uid="{536FA44E-6852-E944-AE54-FE2739629795}"/>
+    <hyperlink ref="G98" r:id="rId50" xr:uid="{C51B2851-1922-0449-92D7-27F16F0BD314}"/>
+    <hyperlink ref="G99" r:id="rId51" xr:uid="{102C7985-55DE-8F49-9440-EF311C0EB910}"/>
+    <hyperlink ref="G79" r:id="rId52" xr:uid="{B65946DF-0810-DA40-A9CD-7B7A7AD2406F}"/>
+    <hyperlink ref="G76" r:id="rId53" xr:uid="{00AAD2C9-EB0A-F146-A0C2-49FE883131EE}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait"/>
